--- a/reports/JSWINFRA/JSW_Infrastructure_Ltd_ERIP_Model.xlsx
+++ b/reports/JSWINFRA/JSW_Infrastructure_Ltd_ERIP_Model.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="318">
   <si>
     <t xml:space="preserve">JSW Infrastructure Ltd - three-statement model</t>
   </si>
@@ -765,7 +765,7 @@
     <t xml:space="preserve">JSW Infrastructure Ltd - DCF</t>
   </si>
   <si>
-    <t xml:space="preserve">FCFF from the linked statements; mid-year discounting; Gordon terminal value; exit-multiple target</t>
+    <t xml:space="preserve">FCFF from the linked statements; stub-period discounting from the balance-sheet date; exit-multiple target</t>
   </si>
   <si>
     <t xml:space="preserve">    NOPAT  (EBIT x (1 - tax rate))</t>
@@ -780,10 +780,28 @@
     <t xml:space="preserve">    Less: increase in net operating assets</t>
   </si>
   <si>
-    <t xml:space="preserve">Discounting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Discount period (mid-year)</t>
+    <t xml:space="preserve">Timing and discounting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Balance-sheet date (date of the net debt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash flows before it are inside net debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    First forecast year ends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Valuation date (cover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Share of the first year counted (stub)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Share of year counted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Discount period (years from balance-sheet date, mid-year)</t>
   </si>
   <si>
     <t xml:space="preserve">    Discount factor</t>
@@ -792,19 +810,28 @@
     <t xml:space="preserve">    Present value of FCFF</t>
   </si>
   <si>
-    <t xml:space="preserve">Valuation: perpetuity growth</t>
+    <t xml:space="preserve">Valuation: perpetuity</t>
   </si>
   <si>
     <t xml:space="preserve">    WACC</t>
   </si>
   <si>
+    <t xml:space="preserve">    Return on new invested capital in perpetuity (RONIC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assumptions.json terminal_ronic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Terminal reinvestment rate  (g / RONIC, share of NOPAT)</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Sum of PV of FCFF</t>
   </si>
   <si>
-    <t xml:space="preserve">    Terminal value  (FCFF N x (1 + g) / (WACC - g))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PV of terminal value  (discounted at N - 0.5)</t>
+    <t xml:space="preserve">    Terminal value  (NOPAT N x (1 + g) x (1 - g / RONIC) / (WACC - g))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PV of terminal value  (at the final cash flow's period)</t>
   </si>
   <si>
     <t xml:space="preserve">Enterprise value</t>
@@ -813,10 +840,10 @@
     <t xml:space="preserve">    Terminal value as % of EV</t>
   </si>
   <si>
-    <t xml:space="preserve">    Net debt  (negative = net cash)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net debt at the valuation date (assumptions.json)</t>
+    <t xml:space="preserve">    Net debt at the balance-sheet date  (negative = net cash)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assumptions.json net_debt, as at the balance-sheet date</t>
   </si>
   <si>
     <t xml:space="preserve">    Non-operating assets</t>
@@ -825,7 +852,16 @@
     <t xml:space="preserve">Treasury investments and stakes not in FCFF</t>
   </si>
   <si>
-    <t xml:space="preserve">Equity value</t>
+    <t xml:space="preserve">    Equity value at the balance-sheet date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cost of equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Roll-forward to the valuation date  ((1 + ke) ^ years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity value at the valuation date</t>
   </si>
   <si>
     <t xml:space="preserve">    Shares outstanding (Cr)</t>
@@ -955,7 +991,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\)"/>
@@ -969,9 +1005,10 @@
     <numFmt numFmtId="174" formatCode="#,##0.000;\(#,##0.000\)"/>
     <numFmt numFmtId="175" formatCode="0.00"/>
     <numFmt numFmtId="176" formatCode="0.00%"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="178" formatCode="0.000"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0.0000"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1228,7 +1265,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1505,11 +1542,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1521,6 +1558,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="175" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1529,15 +1570,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="180" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="180" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2254,10 +2295,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="11"/>
   </cols>
   <sheetData>
@@ -2726,367 +2767,394 @@
         <v>250</v>
       </c>
       <c r="B17" s="68" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C17" s="69" t="n">
-        <f aca="false">B17+1</f>
-        <v>1.5</v>
-      </c>
-      <c r="D17" s="69" t="n">
-        <f aca="false">C17+1</f>
-        <v>2.5</v>
-      </c>
-      <c r="E17" s="69" t="n">
-        <f aca="false">D17+1</f>
-        <v>3.5</v>
-      </c>
-      <c r="F17" s="69" t="n">
-        <f aca="false">E17+1</f>
-        <v>4.5</v>
-      </c>
-      <c r="G17" s="69" t="n">
-        <f aca="false">F17+1</f>
-        <v>5.5</v>
-      </c>
-      <c r="H17" s="69" t="n">
-        <f aca="false">G17+1</f>
-        <v>6.5</v>
-      </c>
-      <c r="I17" s="69" t="n">
-        <f aca="false">H17+1</f>
-        <v>7.5</v>
-      </c>
-      <c r="J17" s="69" t="n">
-        <f aca="false">I17+1</f>
-        <v>8.5</v>
-      </c>
-      <c r="K17" s="69" t="n">
-        <f aca="false">J17+1</f>
-        <v>9.5</v>
+        <v>46203</v>
+      </c>
+      <c r="C17" s="62" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^B17</f>
-        <v>0.946998061410397</v>
-      </c>
-      <c r="C18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^C17</f>
-        <v>0.849272907376867</v>
-      </c>
-      <c r="D18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^D17</f>
-        <v>0.761632468529188</v>
-      </c>
-      <c r="E18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^E17</f>
-        <v>0.68303605599472</v>
-      </c>
-      <c r="F18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^F17</f>
-        <v>0.612550374447362</v>
-      </c>
-      <c r="G18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^G17</f>
-        <v>0.549338439665773</v>
-      </c>
-      <c r="H18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^H17</f>
-        <v>0.492649639740541</v>
-      </c>
-      <c r="I18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^I17</f>
-        <v>0.441810821911807</v>
-      </c>
-      <c r="J18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^J17</f>
-        <v>0.39621829919776</v>
-      </c>
-      <c r="K18" s="70" t="n">
-        <f aca="false">1/(1+WACC!$B$18)^K17</f>
-        <v>0.355330681896478</v>
+        <v>252</v>
+      </c>
+      <c r="B18" s="68" t="n">
+        <v>46477</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B19" s="43" t="n">
-        <f aca="false">B14*B18</f>
-        <v>-4835.67530886638</v>
-      </c>
-      <c r="C19" s="43" t="n">
-        <f aca="false">C14*C18</f>
-        <v>-4396.78878926336</v>
-      </c>
-      <c r="D19" s="43" t="n">
-        <f aca="false">D14*D18</f>
-        <v>565.83948343072</v>
-      </c>
-      <c r="E19" s="43" t="n">
-        <f aca="false">E14*E18</f>
-        <v>1999.51636839124</v>
-      </c>
-      <c r="F19" s="43" t="n">
-        <f aca="false">F14*F18</f>
-        <v>2202.98404502115</v>
-      </c>
-      <c r="G19" s="43" t="n">
-        <f aca="false">G14*G18</f>
-        <v>2083.05312635143</v>
-      </c>
-      <c r="H19" s="43" t="n">
-        <f aca="false">H14*H18</f>
-        <v>1948.23716355807</v>
-      </c>
-      <c r="I19" s="43" t="n">
-        <f aca="false">I14*I18</f>
-        <v>1838.2121663441</v>
-      </c>
-      <c r="J19" s="43" t="n">
-        <f aca="false">J14*J18</f>
-        <v>1729.59648378028</v>
-      </c>
-      <c r="K19" s="43" t="n">
-        <f aca="false">K14*K18</f>
-        <v>1626.69967043695</v>
+        <v>253</v>
+      </c>
+      <c r="B19" s="68" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B20" s="69" t="n">
+        <f aca="false">MIN(1,MAX(0,(B18-B17)/365.25))</f>
+        <v>0.750171115674196</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30" t="s">
-        <v>253</v>
+      <c r="A21" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B21" s="69" t="n">
+        <f aca="false">$B$20</f>
+        <v>0.750171115674196</v>
+      </c>
+      <c r="C21" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B22" s="71" t="n">
+        <v>256</v>
+      </c>
+      <c r="B22" s="64" t="n">
+        <f aca="false">$B$20*0.5</f>
+        <v>0.375085557837098</v>
+      </c>
+      <c r="C22" s="64" t="n">
+        <f aca="false">$B$20+0.5</f>
+        <v>1.2501711156742</v>
+      </c>
+      <c r="D22" s="64" t="n">
+        <f aca="false">C22+1</f>
+        <v>2.2501711156742</v>
+      </c>
+      <c r="E22" s="64" t="n">
+        <f aca="false">D22+1</f>
+        <v>3.2501711156742</v>
+      </c>
+      <c r="F22" s="64" t="n">
+        <f aca="false">E22+1</f>
+        <v>4.2501711156742</v>
+      </c>
+      <c r="G22" s="64" t="n">
+        <f aca="false">F22+1</f>
+        <v>5.2501711156742</v>
+      </c>
+      <c r="H22" s="64" t="n">
+        <f aca="false">G22+1</f>
+        <v>6.2501711156742</v>
+      </c>
+      <c r="I22" s="64" t="n">
+        <f aca="false">H22+1</f>
+        <v>7.2501711156742</v>
+      </c>
+      <c r="J22" s="64" t="n">
+        <f aca="false">I22+1</f>
+        <v>8.2501711156742</v>
+      </c>
+      <c r="K22" s="64" t="n">
+        <f aca="false">J22+1</f>
+        <v>9.2501711156742</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^B22</f>
+        <v>0.959970241613785</v>
+      </c>
+      <c r="C23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^C22</f>
+        <v>0.87269930645706</v>
+      </c>
+      <c r="D23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^D22</f>
+        <v>0.78264138804754</v>
+      </c>
+      <c r="E23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^E22</f>
+        <v>0.70187696696092</v>
+      </c>
+      <c r="F23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^F22</f>
+        <v>0.629447003792159</v>
+      </c>
+      <c r="G23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^G22</f>
+        <v>0.564491426892752</v>
+      </c>
+      <c r="H23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^H22</f>
+        <v>0.506238919425585</v>
+      </c>
+      <c r="I23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^I22</f>
+        <v>0.453997760341318</v>
+      </c>
+      <c r="J23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^J22</f>
+        <v>0.407147610517193</v>
+      </c>
+      <c r="K23" s="69" t="n">
+        <f aca="false">1/(1+WACC!$B$18)^K22</f>
+        <v>0.365132146522559</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" s="43" t="n">
+        <f aca="false">B14*B21*B23</f>
+        <v>-3677.2753553481</v>
+      </c>
+      <c r="C24" s="43" t="n">
+        <f aca="false">C14*C21*C23</f>
+        <v>-4518.07009701959</v>
+      </c>
+      <c r="D24" s="43" t="n">
+        <f aca="false">D14*D21*D23</f>
+        <v>581.447636521486</v>
+      </c>
+      <c r="E24" s="43" t="n">
+        <f aca="false">E14*E21*E23</f>
+        <v>2054.67115786638</v>
+      </c>
+      <c r="F24" s="43" t="n">
+        <f aca="false">F14*F21*F23</f>
+        <v>2263.75130011394</v>
+      </c>
+      <c r="G24" s="43" t="n">
+        <f aca="false">G14*G21*G23</f>
+        <v>2140.51219918807</v>
+      </c>
+      <c r="H24" s="43" t="n">
+        <f aca="false">H14*H21*H23</f>
+        <v>2001.97746411392</v>
+      </c>
+      <c r="I24" s="43" t="n">
+        <f aca="false">I14*I21*I23</f>
+        <v>1888.91753022512</v>
+      </c>
+      <c r="J24" s="43" t="n">
+        <f aca="false">J14*J21*J23</f>
+        <v>1777.3057856134</v>
+      </c>
+      <c r="K24" s="43" t="n">
+        <f aca="false">K14*K21*K23</f>
+        <v>1671.57065988248</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B27" s="71" t="n">
         <f aca="false">WACC!$B$18</f>
         <v>0.1150692</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B28" s="18" t="n">
         <f aca="false">Scenarios!$B$39</f>
         <v>0.04</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B24" s="43" t="n">
-        <f aca="false">SUM(B19:K19)</f>
-        <v>4761.67440918421</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B25" s="43" t="n">
-        <f aca="false">K14*(1+B23)/(B22-B23)</f>
-        <v>63422.9182238854</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B26" s="43" t="n">
-        <f aca="false">B25/(1+B22)^K17</f>
-        <v>22536.1087803578</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B27" s="54" t="n">
-        <f aca="false">B24+B26</f>
-        <v>27297.783189542</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B28" s="34" t="n">
-        <f aca="false">B26/B27</f>
-        <v>0.82556552756971</v>
-      </c>
-    </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B29" s="72" t="n">
-        <v>-2769</v>
+        <v>261</v>
+      </c>
+      <c r="B29" s="31" t="n">
+        <v>0.12</v>
       </c>
       <c r="C29" s="62" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B30" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="62" t="s">
         <v>263</v>
       </c>
+      <c r="B30" s="34" t="n">
+        <f aca="false">$B$28/$B$29</f>
+        <v>0.333333333333333</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B31" s="54" t="n">
-        <f aca="false">B27-B29+B30</f>
-        <v>30066.783189542</v>
+      <c r="B31" s="43" t="n">
+        <f aca="false">SUM(B24:K24)</f>
+        <v>6184.80828115711</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B32" s="73" t="n">
+      <c r="B32" s="43" t="n">
+        <f aca="false">K10*(1+$B$28)*(1-$B$28/$B$29)/($B$27-$B$28)</f>
+        <v>50281.0283946773</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B33" s="43" t="n">
+        <f aca="false">$B$32/(1+$B$27)^K22</f>
+        <v>18359.2198271103</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B34" s="54" t="n">
+        <f aca="false">$B$31+$B$33</f>
+        <v>24544.0281082674</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B35" s="34" t="n">
+        <f aca="false">$B$33/$B$34</f>
+        <v>0.748011685210146</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B36" s="72" t="n">
+        <v>-2769</v>
+      </c>
+      <c r="C36" s="62" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B37" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="62" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B38" s="43" t="n">
+        <f aca="false">$B$34-$B$36+$B$37</f>
+        <v>27313.0281082674</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B39" s="18" t="n">
+        <f aca="false">WACC!$B$10</f>
+        <v>0.123315</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B40" s="73" t="n">
+        <f aca="false">(1+$B$39)^((B19-B17)/365.25)</f>
+        <v>1.03005096417884</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B41" s="54" t="n">
+        <f aca="false">$B$38*$B$40</f>
+        <v>28133.8109375647</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B42" s="74" t="n">
         <f aca="false">Schedules!K23</f>
         <v>232.35</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B33" s="38" t="n">
-        <f aca="false">B31/B32</f>
-        <v>129.40298338516</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B34" s="74" t="n">
-        <v>357.45</v>
-      </c>
-      <c r="C34" s="62" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B35" s="34" t="n">
-        <f aca="false">B33/B34-1</f>
-        <v>-0.637982981157756</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="30" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B38" s="43" t="n">
-        <f aca="false">K7</f>
-        <v>8935.70507202225</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B39" s="75" t="n">
-        <f aca="false">B25/B38</f>
-        <v>7.09769600861861</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B40" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="C40" s="62" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B41" s="43" t="n">
-        <f aca="false">B40*B38</f>
-        <v>89357.0507202225</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B42" s="43" t="n">
-        <f aca="false">B41/(1+B22)^K17</f>
-        <v>31751.3017646748</v>
-      </c>
-    </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B43" s="38" t="n">
-        <f aca="false">(B24+B42-B29+B30)/B32</f>
-        <v>169.063809657237</v>
+        <f aca="false">$B$41/$B$42</f>
+        <v>121.083756994038</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B44" s="26" t="n">
-        <v>5</v>
+        <v>279</v>
+      </c>
+      <c r="B44" s="75" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="C44" s="62" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B45" s="38" t="n">
-        <f aca="false">ROUND(B43/B44,0)*B44</f>
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B46" s="34" t="n">
-        <f aca="false">B45/B34-1</f>
-        <v>-0.524409008252903</v>
+      <c r="A45" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B45" s="34" t="n">
+        <f aca="false">$B$43/$B$44-1</f>
+        <v>-0.661256799569064</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B47" s="31" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C47" s="62" t="s">
+      <c r="A47" s="30" t="s">
         <v>282</v>
       </c>
     </row>
@@ -3094,40 +3162,133 @@
       <c r="A48" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B48" s="31" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C48" s="62" t="s">
-        <v>282</v>
+      <c r="B48" s="43" t="n">
+        <f aca="false">K7</f>
+        <v>8935.70507202225</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B49" s="27" t="str">
-        <f aca="false">IF(B46&gt;B47,"BUY",IF(B46&lt;B48,"SELL","HOLD"))</f>
-        <v>SELL</v>
+      <c r="B49" s="76" t="n">
+        <f aca="false">$B$32/$B$48</f>
+        <v>5.62697940334977</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B50" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" s="62" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B51" s="76" t="n">
-        <v>14</v>
-      </c>
-      <c r="C51" s="62" t="s">
-        <v>286</v>
+        <v>287</v>
+      </c>
+      <c r="B51" s="43" t="n">
+        <f aca="false">$B$50*$B$48</f>
+        <v>89357.0507202225</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B52" s="37" t="n">
-        <f aca="false">(B24+B51*B38/(1+B22)^K17-B29+B30)/B32</f>
-        <v>223.724970431371</v>
+        <v>288</v>
+      </c>
+      <c r="B52" s="43" t="n">
+        <f aca="false">$B$51/(1+$B$27)^K22</f>
+        <v>32627.1317364001</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B53" s="38" t="n">
+        <f aca="false">($B$31+$B$52-$B$36+$B$37)*$B$40/$B$42</f>
+        <v>184.336076421551</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B54" s="26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B55" s="38" t="n">
+        <f aca="false">ROUND($B$53/$B$54,0)*$B$54</f>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B56" s="34" t="n">
+        <f aca="false">$B$55/$B$44-1</f>
+        <v>-0.482445097216394</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B57" s="31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C57" s="62" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B58" s="31" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C58" s="62" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B59" s="27" t="str">
+        <f aca="false">IF($B$56&gt;$B$57,"BUY",IF($B$56&lt;$B$58,"SELL","HOLD"))</f>
+        <v>SELL</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B61" s="77" t="n">
+        <v>14</v>
+      </c>
+      <c r="C61" s="62" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B62" s="37" t="n">
+        <f aca="false">($B$31+$B$61*$B$48/(1+$B$27)^K22-$B$36+$B$37)*$B$40/$B$42</f>
+        <v>242.192944944847</v>
       </c>
     </row>
   </sheetData>
@@ -3155,17 +3316,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B4" s="31" t="n">
         <v>0.005</v>
@@ -3173,330 +3334,330 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B5" s="76" t="n">
+        <v>303</v>
+      </c>
+      <c r="B5" s="77" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B8" s="65" t="n">
-        <f aca="false">DCF!$B$23+(-2)*$B$4</f>
+        <f aca="false">DCF!$B$28+(-2)*$B$4</f>
         <v>0.03</v>
       </c>
       <c r="C8" s="65" t="n">
-        <f aca="false">DCF!$B$23+(-1)*$B$4</f>
+        <f aca="false">DCF!$B$28+(-1)*$B$4</f>
         <v>0.035</v>
       </c>
       <c r="D8" s="65" t="n">
-        <f aca="false">DCF!$B$23+(0)*$B$4</f>
+        <f aca="false">DCF!$B$28+(0)*$B$4</f>
         <v>0.04</v>
       </c>
       <c r="E8" s="65" t="n">
-        <f aca="false">DCF!$B$23+(1)*$B$4</f>
+        <f aca="false">DCF!$B$28+(1)*$B$4</f>
         <v>0.045</v>
       </c>
       <c r="F8" s="65" t="n">
-        <f aca="false">DCF!$B$23+(2)*$B$4</f>
+        <f aca="false">DCF!$B$28+(2)*$B$4</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="66" t="n">
-        <f aca="false">DCF!$B$22+(-2)*$B$4</f>
+        <f aca="false">DCF!$B$27+(-2)*$B$4</f>
         <v>0.1050692</v>
       </c>
       <c r="B9" s="37" t="n">
-        <f aca="false">IF(B$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A9)^DCF!$B$17:$K$17)+DCF!$K$14*(1+B$8)/($A9-B$8)/(1+$A9)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>140.157178523675</v>
+        <f aca="false">IF(B$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A9-B$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>141.481278112723</v>
       </c>
       <c r="C9" s="37" t="n">
-        <f aca="false">IF(C$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A9)^DCF!$B$17:$K$17)+DCF!$K$14*(1+C$8)/($A9-C$8)/(1+$A9)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>148.16846968373</v>
+        <f aca="false">IF(C$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A9-C$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>143.132215753428</v>
       </c>
       <c r="D9" s="37" t="n">
-        <f aca="false">IF(D$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A9)^DCF!$B$17:$K$17)+DCF!$K$14*(1+D$8)/($A9-D$8)/(1+$A9)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>157.410956426344</v>
+        <f aca="false">IF(D$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A9-D$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>144.97554083931</v>
       </c>
       <c r="E9" s="37" t="n">
-        <f aca="false">IF(E$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A9)^DCF!$B$17:$K$17)+DCF!$K$14*(1+E$8)/($A9-E$8)/(1+$A9)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>168.192083061384</v>
+        <f aca="false">IF(E$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A9-E$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>147.059294823852</v>
       </c>
       <c r="F9" s="37" t="n">
-        <f aca="false">IF(F$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A9)^DCF!$B$17:$K$17)+DCF!$K$14*(1+F$8)/($A9-F$8)/(1+$A9)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>180.930951344212</v>
+        <f aca="false">IF(F$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A9-F$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>149.448966827652</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="66" t="n">
-        <f aca="false">DCF!$B$22+(-1)*$B$4</f>
+        <f aca="false">DCF!$B$27+(-1)*$B$4</f>
         <v>0.1100692</v>
       </c>
       <c r="B10" s="37" t="n">
-        <f aca="false">IF(B$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A10)^DCF!$B$17:$K$17)+DCF!$K$14*(1+B$8)/($A10-B$8)/(1+$A10)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>127.922346957083</v>
+        <f aca="false">IF(B$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A10-B$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>129.905471348028</v>
       </c>
       <c r="C10" s="37" t="n">
-        <f aca="false">IF(C$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A10)^DCF!$B$17:$K$17)+DCF!$K$14*(1+C$8)/($A10-C$8)/(1+$A10)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>134.66916923646</v>
+        <f aca="false">IF(C$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A10-C$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>130.990241483892</v>
       </c>
       <c r="D10" s="37" t="n">
-        <f aca="false">IF(D$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A10)^DCF!$B$17:$K$17)+DCF!$K$14*(1+D$8)/($A10-D$8)/(1+$A10)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>142.378871394497</v>
+        <f aca="false">IF(D$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A10-D$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>132.175198939132</v>
       </c>
       <c r="E10" s="37" t="n">
-        <f aca="false">IF(E$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A10)^DCF!$B$17:$K$17)+DCF!$K$14*(1+E$8)/($A10-E$8)/(1+$A10)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>151.273420170908</v>
+        <f aca="false">IF(E$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A10-E$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>133.483439276481</v>
       </c>
       <c r="F10" s="37" t="n">
-        <f aca="false">IF(F$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A10)^DCF!$B$17:$K$17)+DCF!$K$14*(1+F$8)/($A10-F$8)/(1+$A10)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>161.648685983073</v>
+        <f aca="false">IF(F$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A10-F$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>134.945747710853</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="66" t="n">
-        <f aca="false">DCF!$B$22+(0)*$B$4</f>
+        <f aca="false">DCF!$B$27+(0)*$B$4</f>
         <v>0.1150692</v>
       </c>
       <c r="B11" s="37" t="n">
-        <f aca="false">IF(B$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A11)^DCF!$B$17:$K$17)+DCF!$K$14*(1+B$8)/($A11-B$8)/(1+$A11)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>117.178447335938</v>
+        <f aca="false">IF(B$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A11-B$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>119.717140280606</v>
       </c>
       <c r="C11" s="37" t="n">
-        <f aca="false">IF(C$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A11)^DCF!$B$17:$K$17)+DCF!$K$14*(1+C$8)/($A11-C$8)/(1+$A11)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>122.909028767913</v>
+        <f aca="false">IF(C$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A11-C$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>120.380707675442</v>
       </c>
       <c r="D11" s="38" t="n">
-        <f aca="false">IF(D$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A11)^DCF!$B$17:$K$17)+DCF!$K$14*(1+D$8)/($A11-D$8)/(1+$A11)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>129.40298338516</v>
+        <f aca="false">IF(D$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A11-D$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>121.083756994038</v>
       </c>
       <c r="E11" s="37" t="n">
-        <f aca="false">IF(E$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A11)^DCF!$B$17:$K$17)+DCF!$K$14*(1+E$8)/($A11-E$8)/(1+$A11)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>136.823729605172</v>
+        <f aca="false">IF(E$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A11-E$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>121.834740293165</v>
       </c>
       <c r="F11" s="37" t="n">
-        <f aca="false">IF(F$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A11)^DCF!$B$17:$K$17)+DCF!$K$14*(1+F$8)/($A11-F$8)/(1+$A11)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>145.384914960753</v>
+        <f aca="false">IF(F$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A11-F$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>122.644707496719</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="66" t="n">
-        <f aca="false">DCF!$B$22+(1)*$B$4</f>
+        <f aca="false">DCF!$B$27+(1)*$B$4</f>
         <v>0.1200692</v>
       </c>
       <c r="B12" s="37" t="n">
-        <f aca="false">IF(B$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A12)^DCF!$B$17:$K$17)+DCF!$K$14*(1+B$8)/($A12-B$8)/(1+$A12)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>107.676080894372</v>
+        <f aca="false">IF(B$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A12-B$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>110.685176331286</v>
       </c>
       <c r="C12" s="37" t="n">
-        <f aca="false">IF(C$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A12)^DCF!$B$17:$K$17)+DCF!$K$14*(1+C$8)/($A12-C$8)/(1+$A12)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>112.580324958075</v>
+        <f aca="false">IF(C$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A12-C$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>111.033906635952</v>
       </c>
       <c r="D12" s="37" t="n">
-        <f aca="false">IF(D$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A12)^DCF!$B$17:$K$17)+DCF!$K$14*(1+D$8)/($A12-D$8)/(1+$A12)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>118.097069716641</v>
+        <f aca="false">IF(D$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A12-D$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>111.382191856473</v>
       </c>
       <c r="E12" s="37" t="n">
-        <f aca="false">IF(E$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A12)^DCF!$B$17:$K$17)+DCF!$K$14*(1+E$8)/($A12-E$8)/(1+$A12)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>124.348702386435</v>
+        <f aca="false">IF(E$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A12-E$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>111.729943058076</v>
       </c>
       <c r="F12" s="37" t="n">
-        <f aca="false">IF(F$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A12)^DCF!$B$17:$K$17)+DCF!$K$14*(1+F$8)/($A12-F$8)/(1+$A12)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>131.492543425927</v>
+        <f aca="false">IF(F$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A12-F$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>112.077045921151</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="66" t="n">
-        <f aca="false">DCF!$B$22+(2)*$B$4</f>
+        <f aca="false">DCF!$B$27+(2)*$B$4</f>
         <v>0.1250692</v>
       </c>
       <c r="B13" s="37" t="n">
-        <f aca="false">IF(B$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A13)^DCF!$B$17:$K$17)+DCF!$K$14*(1+B$8)/($A13-B$8)/(1+$A13)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>99.2183472517214</v>
+        <f aca="false">IF(B$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A13-B$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>102.627071137506</v>
       </c>
       <c r="C13" s="37" t="n">
-        <f aca="false">IF(C$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A13)^DCF!$B$17:$K$17)+DCF!$K$14*(1+C$8)/($A13-C$8)/(1+$A13)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>103.443693953947</v>
+        <f aca="false">IF(C$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A13-C$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>102.739973238036</v>
       </c>
       <c r="D13" s="37" t="n">
-        <f aca="false">IF(D$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A13)^DCF!$B$17:$K$17)+DCF!$K$14*(1+D$8)/($A13-D$8)/(1+$A13)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>108.165735899836</v>
+        <f aca="false">IF(D$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A13-D$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>102.826406058116</v>
       </c>
       <c r="E13" s="37" t="n">
-        <f aca="false">IF(E$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A13)^DCF!$B$17:$K$17)+DCF!$K$14*(1+E$8)/($A13-E$8)/(1+$A13)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>113.477522959438</v>
+        <f aca="false">IF(E$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A13-E$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>102.881410896938</v>
       </c>
       <c r="F13" s="37" t="n">
-        <f aca="false">IF(F$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A13)^DCF!$B$17:$K$17)+DCF!$K$14*(1+F$8)/($A13-F$8)/(1+$A13)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32)</f>
-        <v>119.496895428183</v>
+        <f aca="false">IF(F$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A13-F$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
+        <v>102.898707952413</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="B16" s="77" t="n">
-        <f aca="false">DCF!$B$40+(-2)*$B$5</f>
+        <v>307</v>
+      </c>
+      <c r="B16" s="78" t="n">
+        <f aca="false">DCF!$B$50+(-2)*$B$5</f>
         <v>6</v>
       </c>
-      <c r="C16" s="77" t="n">
-        <f aca="false">DCF!$B$40+(-1)*$B$5</f>
+      <c r="C16" s="78" t="n">
+        <f aca="false">DCF!$B$50+(-1)*$B$5</f>
         <v>8</v>
       </c>
-      <c r="D16" s="77" t="n">
-        <f aca="false">DCF!$B$40+(0)*$B$5</f>
+      <c r="D16" s="78" t="n">
+        <f aca="false">DCF!$B$50+(0)*$B$5</f>
         <v>10</v>
       </c>
-      <c r="E16" s="77" t="n">
-        <f aca="false">DCF!$B$40+(1)*$B$5</f>
+      <c r="E16" s="78" t="n">
+        <f aca="false">DCF!$B$50+(1)*$B$5</f>
         <v>12</v>
       </c>
-      <c r="F16" s="77" t="n">
-        <f aca="false">DCF!$B$40+(2)*$B$5</f>
+      <c r="F16" s="78" t="n">
+        <f aca="false">DCF!$B$50+(2)*$B$5</f>
         <v>14</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="66" t="n">
-        <f aca="false">DCF!$B$22+(-2)*$B$4</f>
+        <f aca="false">DCF!$B$27+(-2)*$B$4</f>
         <v>0.1050692</v>
       </c>
       <c r="B17" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A17)^DCF!$B$17:$K$17)+B$16*DCF!$B$38/(1+$A17)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>124.832514997476</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>137.244689743407</v>
       </c>
       <c r="C17" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A17)^DCF!$B$17:$K$17)+C$16*DCF!$B$38/(1+$A17)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>154.605072053205</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>168.68702493657</v>
       </c>
       <c r="D17" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A17)^DCF!$B$17:$K$17)+D$16*DCF!$B$38/(1+$A17)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>184.377629108933</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>200.129360129733</v>
       </c>
       <c r="E17" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A17)^DCF!$B$17:$K$17)+E$16*DCF!$B$38/(1+$A17)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>214.150186164662</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>231.571695322896</v>
       </c>
       <c r="F17" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A17)^DCF!$B$17:$K$17)+F$16*DCF!$B$38/(1+$A17)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>243.92274322039</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>263.014030516059</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="66" t="n">
-        <f aca="false">DCF!$B$22+(-1)*$B$4</f>
+        <f aca="false">DCF!$B$27+(-1)*$B$4</f>
         <v>0.1100692</v>
       </c>
       <c r="B18" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A18)^DCF!$B$17:$K$17)+B$16*DCF!$B$38/(1+$A18)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>119.501189687698</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>131.745326438666</v>
       </c>
       <c r="C18" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A18)^DCF!$B$17:$K$17)+C$16*DCF!$B$38/(1+$A18)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>148.023890255743</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>161.901699605484</v>
       </c>
       <c r="D18" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A18)^DCF!$B$17:$K$17)+D$16*DCF!$B$38/(1+$A18)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>176.546590823789</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>192.058072772303</v>
       </c>
       <c r="E18" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A18)^DCF!$B$17:$K$17)+E$16*DCF!$B$38/(1+$A18)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>205.069291391834</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>222.214445939122</v>
       </c>
       <c r="F18" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A18)^DCF!$B$17:$K$17)+F$16*DCF!$B$38/(1+$A18)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>233.591991959879</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>252.370819105941</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="66" t="n">
-        <f aca="false">DCF!$B$22+(0)*$B$4</f>
+        <f aca="false">DCF!$B$27+(0)*$B$4</f>
         <v>0.1150692</v>
       </c>
       <c r="B19" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A19)^DCF!$B$17:$K$17)+B$16*DCF!$B$38/(1+$A19)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>114.402648883104</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>126.479207898256</v>
       </c>
       <c r="C19" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A19)^DCF!$B$17:$K$17)+C$16*DCF!$B$38/(1+$A19)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>141.73322927017</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>155.407642159904</v>
       </c>
       <c r="D19" s="38" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A19)^DCF!$B$17:$K$17)+D$16*DCF!$B$38/(1+$A19)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>169.063809657237</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>184.336076421551</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A19)^DCF!$B$17:$K$17)+E$16*DCF!$B$38/(1+$A19)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>196.394390044304</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>213.264510683199</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A19)^DCF!$B$17:$K$17)+F$16*DCF!$B$38/(1+$A19)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>223.724970431371</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>242.192944944847</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="66" t="n">
-        <f aca="false">DCF!$B$22+(1)*$B$4</f>
+        <f aca="false">DCF!$B$27+(1)*$B$4</f>
         <v>0.1200692</v>
       </c>
       <c r="B20" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A20)^DCF!$B$17:$K$17)+B$16*DCF!$B$38/(1+$A20)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>109.525664565478</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>121.435330806186</v>
       </c>
       <c r="C20" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A20)^DCF!$B$17:$K$17)+C$16*DCF!$B$38/(1+$A20)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>135.718952812982</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>149.190988475413</v>
       </c>
       <c r="D20" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A20)^DCF!$B$17:$K$17)+D$16*DCF!$B$38/(1+$A20)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>161.912241060486</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>176.94664614464</v>
       </c>
       <c r="E20" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A20)^DCF!$B$17:$K$17)+E$16*DCF!$B$38/(1+$A20)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>188.10552930799</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>204.702303813867</v>
       </c>
       <c r="F20" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A20)^DCF!$B$17:$K$17)+F$16*DCF!$B$38/(1+$A20)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>214.298817555494</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>232.457961483094</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="66" t="n">
-        <f aca="false">DCF!$B$22+(2)*$B$4</f>
+        <f aca="false">DCF!$B$27+(2)*$B$4</f>
         <v>0.1250692</v>
       </c>
       <c r="B21" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A21)^DCF!$B$17:$K$17)+B$16*DCF!$B$38/(1+$A21)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>104.859602546607</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>116.603262569662</v>
       </c>
       <c r="C21" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A21)^DCF!$B$17:$K$17)+C$16*DCF!$B$38/(1+$A21)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>129.967676966441</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>143.238598067401</v>
       </c>
       <c r="D21" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A21)^DCF!$B$17:$K$17)+D$16*DCF!$B$38/(1+$A21)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>155.075751386274</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>169.87393356514</v>
       </c>
       <c r="E21" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A21)^DCF!$B$17:$K$17)+E$16*DCF!$B$38/(1+$A21)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>180.183825806107</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>196.509269062879</v>
       </c>
       <c r="F21" s="37" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,1/(1+$A21)^DCF!$B$17:$K$17)+F$16*DCF!$B$38/(1+$A21)^DCF!$K$17-DCF!$B$29+DCF!$B$30)/DCF!$B$32</f>
-        <v>205.291900225941</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
+        <v>223.144604560618</v>
       </c>
     </row>
   </sheetData>
@@ -3524,7 +3685,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3599,7 +3760,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -3624,347 +3785,347 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B6" s="78" t="n">
+        <v>310</v>
+      </c>
+      <c r="B6" s="79" t="n">
         <f aca="false">('Balance Sheet'!B13-'Balance Sheet'!B22)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="78" t="n">
+      <c r="C6" s="79" t="n">
         <f aca="false">('Balance Sheet'!C13-'Balance Sheet'!C22)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="78" t="n">
+      <c r="D6" s="79" t="n">
         <f aca="false">('Balance Sheet'!D13-'Balance Sheet'!D22)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="78" t="n">
+      <c r="E6" s="79" t="n">
         <f aca="false">('Balance Sheet'!E13-'Balance Sheet'!E22)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="78" t="n">
+      <c r="F6" s="79" t="n">
         <f aca="false">('Balance Sheet'!F13-'Balance Sheet'!F22)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="78" t="n">
+      <c r="G6" s="79" t="n">
         <f aca="false">('Balance Sheet'!G13-'Balance Sheet'!G22)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="78" t="n">
+      <c r="H6" s="79" t="n">
         <f aca="false">('Balance Sheet'!H13-'Balance Sheet'!H22)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="78" t="n">
+      <c r="I6" s="79" t="n">
         <f aca="false">('Balance Sheet'!I13-'Balance Sheet'!I22)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="78" t="n">
+      <c r="J6" s="79" t="n">
         <f aca="false">('Balance Sheet'!J13-'Balance Sheet'!J22)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="78" t="n">
+      <c r="K6" s="79" t="n">
         <f aca="false">('Balance Sheet'!K13-'Balance Sheet'!K22)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="78" t="n">
+      <c r="L6" s="79" t="n">
         <f aca="false">('Balance Sheet'!L13-'Balance Sheet'!L22)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="78" t="n">
+      <c r="M6" s="79" t="n">
         <f aca="false">('Balance Sheet'!M13-'Balance Sheet'!M22)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="78" t="n">
+      <c r="N6" s="79" t="n">
         <f aca="false">('Balance Sheet'!N13-'Balance Sheet'!N22)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="78" t="n">
+      <c r="O6" s="79" t="n">
         <f aca="false">('Balance Sheet'!O13-'Balance Sheet'!O22)</f>
         <v>0</v>
       </c>
-      <c r="P6" s="78" t="n">
+      <c r="P6" s="79" t="n">
         <f aca="false">('Balance Sheet'!P13-'Balance Sheet'!P22)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="78" t="n">
+      <c r="Q6" s="79" t="n">
         <f aca="false">('Balance Sheet'!Q13-'Balance Sheet'!Q22)</f>
         <v>0</v>
       </c>
-      <c r="R6" s="78" t="n">
+      <c r="R6" s="79" t="n">
         <f aca="false">('Balance Sheet'!R13-'Balance Sheet'!R22)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="78" t="n">
+      <c r="S6" s="79" t="n">
         <f aca="false">('Balance Sheet'!S13-'Balance Sheet'!S22)</f>
         <v>0</v>
       </c>
-      <c r="T6" s="78" t="n">
+      <c r="T6" s="79" t="n">
         <f aca="false">('Balance Sheet'!T13-'Balance Sheet'!T22)</f>
         <v>0</v>
       </c>
-      <c r="U6" s="78" t="n">
+      <c r="U6" s="79" t="n">
         <f aca="false">('Balance Sheet'!U13-'Balance Sheet'!U22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B7" s="78" t="n">
+        <v>311</v>
+      </c>
+      <c r="B7" s="79" t="n">
         <f aca="false">('Balance Sheet'!B6-'Cash Flow'!B23)</f>
         <v>-1268.7</v>
       </c>
-      <c r="C7" s="78" t="n">
+      <c r="C7" s="79" t="n">
         <f aca="false">('Balance Sheet'!C6-'Cash Flow'!C23)</f>
         <v>491.16</v>
       </c>
-      <c r="D7" s="78" t="n">
+      <c r="D7" s="79" t="n">
         <f aca="false">('Balance Sheet'!D6-'Cash Flow'!D23)</f>
         <v>7.87999999999984</v>
       </c>
-      <c r="E7" s="78" t="n">
+      <c r="E7" s="79" t="n">
         <f aca="false">('Balance Sheet'!E6-'Cash Flow'!E23)</f>
         <v>-529.87</v>
       </c>
-      <c r="F7" s="78" t="n">
+      <c r="F7" s="79" t="n">
         <f aca="false">('Balance Sheet'!F6-'Cash Flow'!F23)</f>
         <v>51.5699999999998</v>
       </c>
-      <c r="G7" s="78" t="n">
+      <c r="G7" s="79" t="n">
         <f aca="false">('Balance Sheet'!G6-'Cash Flow'!G23)</f>
         <v>53</v>
       </c>
-      <c r="H7" s="78" t="n">
+      <c r="H7" s="79" t="n">
         <f aca="false">('Balance Sheet'!H6-'Cash Flow'!H23)</f>
         <v>-17.3399999999992</v>
       </c>
-      <c r="I7" s="78" t="n">
+      <c r="I7" s="79" t="n">
         <f aca="false">('Balance Sheet'!I6-'Cash Flow'!I23)</f>
         <v>2988.66</v>
       </c>
-      <c r="J7" s="78" t="n">
+      <c r="J7" s="79" t="n">
         <f aca="false">('Balance Sheet'!J6-'Cash Flow'!J23)</f>
         <v>333.339999999999</v>
       </c>
-      <c r="K7" s="78" t="n">
+      <c r="K7" s="79" t="n">
         <f aca="false">('Balance Sheet'!K6-'Cash Flow'!K23)</f>
         <v>-155.04</v>
       </c>
-      <c r="L7" s="78" t="n">
+      <c r="L7" s="79" t="n">
         <f aca="false">('Balance Sheet'!L6-'Cash Flow'!L23)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="78" t="n">
+      <c r="M7" s="79" t="n">
         <f aca="false">('Balance Sheet'!M6-'Cash Flow'!M23)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="78" t="n">
+      <c r="N7" s="79" t="n">
         <f aca="false">('Balance Sheet'!N6-'Cash Flow'!N23)</f>
         <v>0</v>
       </c>
-      <c r="O7" s="78" t="n">
+      <c r="O7" s="79" t="n">
         <f aca="false">('Balance Sheet'!O6-'Cash Flow'!O23)</f>
         <v>0</v>
       </c>
-      <c r="P7" s="78" t="n">
+      <c r="P7" s="79" t="n">
         <f aca="false">('Balance Sheet'!P6-'Cash Flow'!P23)</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="78" t="n">
+      <c r="Q7" s="79" t="n">
         <f aca="false">('Balance Sheet'!Q6-'Cash Flow'!Q23)</f>
         <v>0</v>
       </c>
-      <c r="R7" s="78" t="n">
+      <c r="R7" s="79" t="n">
         <f aca="false">('Balance Sheet'!R6-'Cash Flow'!R23)</f>
         <v>0</v>
       </c>
-      <c r="S7" s="78" t="n">
+      <c r="S7" s="79" t="n">
         <f aca="false">('Balance Sheet'!S6-'Cash Flow'!S23)</f>
         <v>0</v>
       </c>
-      <c r="T7" s="78" t="n">
+      <c r="T7" s="79" t="n">
         <f aca="false">('Balance Sheet'!T6-'Cash Flow'!T23)</f>
         <v>0</v>
       </c>
-      <c r="U7" s="78" t="n">
+      <c r="U7" s="79" t="n">
         <f aca="false">('Balance Sheet'!U6-'Cash Flow'!U23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B8" s="78" t="n">
+        <v>312</v>
+      </c>
+      <c r="B8" s="79" t="n">
         <f aca="false">('Balance Sheet'!B16-(((0+'Income Statement'!B18)-Schedules!B22)+Drivers!B27))</f>
         <v>1487.52</v>
       </c>
-      <c r="C8" s="78" t="n">
+      <c r="C8" s="79" t="n">
         <f aca="false">('Balance Sheet'!C16-((('Balance Sheet'!B16+'Income Statement'!C18)-Schedules!C22)+Drivers!C27))</f>
         <v>487.3</v>
       </c>
-      <c r="D8" s="78" t="n">
+      <c r="D8" s="79" t="n">
         <f aca="false">('Balance Sheet'!D16-((('Balance Sheet'!C16+'Income Statement'!D18)-Schedules!D22)+Drivers!D27))</f>
         <v>7.88000000000011</v>
       </c>
-      <c r="E8" s="78" t="n">
+      <c r="E8" s="79" t="n">
         <f aca="false">('Balance Sheet'!E16-((('Balance Sheet'!D16+'Income Statement'!E18)-Schedules!E22)+Drivers!E27))</f>
         <v>-529.62</v>
       </c>
-      <c r="F8" s="78" t="n">
+      <c r="F8" s="79" t="n">
         <f aca="false">('Balance Sheet'!F16-((('Balance Sheet'!E16+'Income Statement'!F18)-Schedules!F22)+Drivers!F27))</f>
         <v>51.5699999999997</v>
       </c>
-      <c r="G8" s="78" t="n">
+      <c r="G8" s="79" t="n">
         <f aca="false">('Balance Sheet'!G16-((('Balance Sheet'!F16+'Income Statement'!G18)-Schedules!G22)+Drivers!G27))</f>
         <v>53.0000000000005</v>
       </c>
-      <c r="H8" s="78" t="n">
+      <c r="H8" s="79" t="n">
         <f aca="false">('Balance Sheet'!H16-((('Balance Sheet'!G16+'Income Statement'!H18)-Schedules!H22)+Drivers!H27))</f>
         <v>-316.98</v>
       </c>
-      <c r="I8" s="78" t="n">
+      <c r="I8" s="79" t="n">
         <f aca="false">('Balance Sheet'!I16-((('Balance Sheet'!H16+'Income Statement'!I18)-Schedules!I22)+Drivers!I27))</f>
         <v>2937.93</v>
       </c>
-      <c r="J8" s="78" t="n">
+      <c r="J8" s="79" t="n">
         <f aca="false">('Balance Sheet'!J16-((('Balance Sheet'!I16+'Income Statement'!J18)-Schedules!J22)+Drivers!J27))</f>
         <v>328.940000000001</v>
       </c>
-      <c r="K8" s="78" t="n">
+      <c r="K8" s="79" t="n">
         <f aca="false">('Balance Sheet'!K16-((('Balance Sheet'!J16+'Income Statement'!K18)-Schedules!K22)+Drivers!K27))</f>
         <v>-157.380000000001</v>
       </c>
-      <c r="L8" s="78" t="n">
+      <c r="L8" s="79" t="n">
         <f aca="false">('Balance Sheet'!L16-((('Balance Sheet'!K16+'Income Statement'!L18)-Schedules!L22)+Drivers!L27))</f>
         <v>0</v>
       </c>
-      <c r="M8" s="78" t="n">
+      <c r="M8" s="79" t="n">
         <f aca="false">('Balance Sheet'!M16-((('Balance Sheet'!L16+'Income Statement'!M18)-Schedules!M22)+Drivers!M27))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="78" t="n">
+      <c r="N8" s="79" t="n">
         <f aca="false">('Balance Sheet'!N16-((('Balance Sheet'!M16+'Income Statement'!N18)-Schedules!N22)+Drivers!N27))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="78" t="n">
+      <c r="O8" s="79" t="n">
         <f aca="false">('Balance Sheet'!O16-((('Balance Sheet'!N16+'Income Statement'!O18)-Schedules!O22)+Drivers!O27))</f>
         <v>0</v>
       </c>
-      <c r="P8" s="78" t="n">
+      <c r="P8" s="79" t="n">
         <f aca="false">('Balance Sheet'!P16-((('Balance Sheet'!O16+'Income Statement'!P18)-Schedules!P22)+Drivers!P27))</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="78" t="n">
+      <c r="Q8" s="79" t="n">
         <f aca="false">('Balance Sheet'!Q16-((('Balance Sheet'!P16+'Income Statement'!Q18)-Schedules!Q22)+Drivers!Q27))</f>
         <v>0</v>
       </c>
-      <c r="R8" s="78" t="n">
+      <c r="R8" s="79" t="n">
         <f aca="false">('Balance Sheet'!R16-((('Balance Sheet'!Q16+'Income Statement'!R18)-Schedules!R22)+Drivers!R27))</f>
         <v>0</v>
       </c>
-      <c r="S8" s="78" t="n">
+      <c r="S8" s="79" t="n">
         <f aca="false">('Balance Sheet'!S16-((('Balance Sheet'!R16+'Income Statement'!S18)-Schedules!S22)+Drivers!S27))</f>
         <v>0</v>
       </c>
-      <c r="T8" s="78" t="n">
+      <c r="T8" s="79" t="n">
         <f aca="false">('Balance Sheet'!T16-((('Balance Sheet'!S16+'Income Statement'!T18)-Schedules!T22)+Drivers!T27))</f>
         <v>0</v>
       </c>
-      <c r="U8" s="78" t="n">
+      <c r="U8" s="79" t="n">
         <f aca="false">('Balance Sheet'!U16-((('Balance Sheet'!T16+'Income Statement'!U18)-Schedules!U22)+Drivers!U27))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9" s="78" t="n">
+        <v>313</v>
+      </c>
+      <c r="B9" s="79" t="n">
         <f aca="false">('Balance Sheet'!B10-Schedules!B9)</f>
         <v>2812.54</v>
       </c>
-      <c r="C9" s="78" t="n">
+      <c r="C9" s="79" t="n">
         <f aca="false">('Balance Sheet'!C10-Schedules!C9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="78" t="n">
+      <c r="D9" s="79" t="n">
         <f aca="false">('Balance Sheet'!D10-Schedules!D9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="78" t="n">
+      <c r="E9" s="79" t="n">
         <f aca="false">('Balance Sheet'!E10-Schedules!E9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="78" t="n">
+      <c r="F9" s="79" t="n">
         <f aca="false">('Balance Sheet'!F10-Schedules!F9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="78" t="n">
+      <c r="G9" s="79" t="n">
         <f aca="false">('Balance Sheet'!G10-Schedules!G9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="78" t="n">
+      <c r="H9" s="79" t="n">
         <f aca="false">('Balance Sheet'!H10-Schedules!H9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="78" t="n">
+      <c r="I9" s="79" t="n">
         <f aca="false">('Balance Sheet'!I10-Schedules!I9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="78" t="n">
+      <c r="J9" s="79" t="n">
         <f aca="false">('Balance Sheet'!J10-Schedules!J9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="78" t="n">
+      <c r="K9" s="79" t="n">
         <f aca="false">('Balance Sheet'!K10-Schedules!K9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="78" t="n">
+      <c r="L9" s="79" t="n">
         <f aca="false">('Balance Sheet'!L10-Schedules!L9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="78" t="n">
+      <c r="M9" s="79" t="n">
         <f aca="false">('Balance Sheet'!M10-Schedules!M9)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="78" t="n">
+      <c r="N9" s="79" t="n">
         <f aca="false">('Balance Sheet'!N10-Schedules!N9)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="78" t="n">
+      <c r="O9" s="79" t="n">
         <f aca="false">('Balance Sheet'!O10-Schedules!O9)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="78" t="n">
+      <c r="P9" s="79" t="n">
         <f aca="false">('Balance Sheet'!P10-Schedules!P9)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="78" t="n">
+      <c r="Q9" s="79" t="n">
         <f aca="false">('Balance Sheet'!Q10-Schedules!Q9)</f>
         <v>0</v>
       </c>
-      <c r="R9" s="78" t="n">
+      <c r="R9" s="79" t="n">
         <f aca="false">('Balance Sheet'!R10-Schedules!R9)</f>
         <v>0</v>
       </c>
-      <c r="S9" s="78" t="n">
+      <c r="S9" s="79" t="n">
         <f aca="false">('Balance Sheet'!S10-Schedules!S9)</f>
         <v>0</v>
       </c>
-      <c r="T9" s="78" t="n">
+      <c r="T9" s="79" t="n">
         <f aca="false">('Balance Sheet'!T10-Schedules!T9)</f>
         <v>0</v>
       </c>
-      <c r="U9" s="78" t="n">
+      <c r="U9" s="79" t="n">
         <f aca="false">('Balance Sheet'!U10-Schedules!U9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -3989,255 +4150,255 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B11" s="78" t="n">
+        <v>315</v>
+      </c>
+      <c r="B11" s="79" t="n">
         <f aca="false">('Balance Sheet'!B6-Drivers!B29)</f>
         <v>44.88</v>
       </c>
-      <c r="C11" s="78" t="n">
+      <c r="C11" s="79" t="n">
         <f aca="false">('Balance Sheet'!C6-Drivers!C29)</f>
         <v>328.45</v>
       </c>
-      <c r="D11" s="78" t="n">
+      <c r="D11" s="79" t="n">
         <f aca="false">('Balance Sheet'!D6-Drivers!D29)</f>
         <v>101.76</v>
       </c>
-      <c r="E11" s="78" t="n">
+      <c r="E11" s="79" t="n">
         <f aca="false">('Balance Sheet'!E6-Drivers!E29)</f>
         <v>162.61</v>
       </c>
-      <c r="F11" s="78" t="n">
+      <c r="F11" s="79" t="n">
         <f aca="false">('Balance Sheet'!F6-Drivers!F29)</f>
         <v>314.48</v>
       </c>
-      <c r="G11" s="78" t="n">
+      <c r="G11" s="79" t="n">
         <f aca="false">('Balance Sheet'!G6-Drivers!G29)</f>
         <v>1038.24</v>
       </c>
-      <c r="H11" s="78" t="n">
+      <c r="H11" s="79" t="n">
         <f aca="false">('Balance Sheet'!H6-Drivers!H29)</f>
         <v>1631.64</v>
       </c>
-      <c r="I11" s="78" t="n">
+      <c r="I11" s="79" t="n">
         <f aca="false">('Balance Sheet'!I6-Drivers!I29)</f>
         <v>4090.22</v>
       </c>
-      <c r="J11" s="78" t="n">
+      <c r="J11" s="79" t="n">
         <f aca="false">('Balance Sheet'!J6-Drivers!J29)</f>
         <v>2482.07</v>
       </c>
-      <c r="K11" s="78" t="n">
+      <c r="K11" s="79" t="n">
         <f aca="false">('Balance Sheet'!K6-Drivers!K29)</f>
         <v>2317.7</v>
       </c>
-      <c r="L11" s="78" t="n">
+      <c r="L11" s="79" t="n">
         <f aca="false">('Balance Sheet'!L6-Drivers!L29)</f>
         <v>3323.80622788275</v>
       </c>
-      <c r="M11" s="78" t="n">
+      <c r="M11" s="79" t="n">
         <f aca="false">('Balance Sheet'!M6-Drivers!M29)</f>
         <v>-8.66885784489568E-007</v>
       </c>
-      <c r="N11" s="78" t="n">
+      <c r="N11" s="79" t="n">
         <f aca="false">('Balance Sheet'!N6-Drivers!N29)</f>
         <v>-4.93056677441928E-006</v>
       </c>
-      <c r="O11" s="78" t="n">
+      <c r="O11" s="79" t="n">
         <f aca="false">('Balance Sheet'!O6-Drivers!O29)</f>
         <v>-2.09666018236021E-005</v>
       </c>
-      <c r="P11" s="78" t="n">
+      <c r="P11" s="79" t="n">
         <f aca="false">('Balance Sheet'!P6-Drivers!P29)</f>
         <v>-6.09262519901677E-005</v>
       </c>
-      <c r="Q11" s="78" t="n">
+      <c r="Q11" s="79" t="n">
         <f aca="false">('Balance Sheet'!Q6-Drivers!Q29)</f>
         <v>2827.89127432764</v>
       </c>
-      <c r="R11" s="78" t="n">
+      <c r="R11" s="79" t="n">
         <f aca="false">('Balance Sheet'!R6-Drivers!R29)</f>
         <v>5924.43110420206</v>
       </c>
-      <c r="S11" s="78" t="n">
+      <c r="S11" s="79" t="n">
         <f aca="false">('Balance Sheet'!S6-Drivers!S29)</f>
         <v>9332.100059432</v>
       </c>
-      <c r="T11" s="78" t="n">
+      <c r="T11" s="79" t="n">
         <f aca="false">('Balance Sheet'!T6-Drivers!T29)</f>
         <v>13072.4148271819</v>
       </c>
-      <c r="U11" s="78" t="n">
+      <c r="U11" s="79" t="n">
         <f aca="false">('Balance Sheet'!U6-Drivers!U29)</f>
         <v>17146.7499330989</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B12" s="78" t="n">
+        <v>316</v>
+      </c>
+      <c r="B12" s="79" t="n">
         <f aca="false">'Balance Sheet'!B18</f>
         <v>0</v>
       </c>
-      <c r="C12" s="78" t="n">
+      <c r="C12" s="79" t="n">
         <f aca="false">'Balance Sheet'!C18</f>
         <v>0</v>
       </c>
-      <c r="D12" s="78" t="n">
+      <c r="D12" s="79" t="n">
         <f aca="false">'Balance Sheet'!D18</f>
         <v>0</v>
       </c>
-      <c r="E12" s="78" t="n">
+      <c r="E12" s="79" t="n">
         <f aca="false">'Balance Sheet'!E18</f>
         <v>0</v>
       </c>
-      <c r="F12" s="78" t="n">
+      <c r="F12" s="79" t="n">
         <f aca="false">'Balance Sheet'!F18</f>
         <v>0</v>
       </c>
-      <c r="G12" s="78" t="n">
+      <c r="G12" s="79" t="n">
         <f aca="false">'Balance Sheet'!G18</f>
         <v>0</v>
       </c>
-      <c r="H12" s="78" t="n">
+      <c r="H12" s="79" t="n">
         <f aca="false">'Balance Sheet'!H18</f>
         <v>0</v>
       </c>
-      <c r="I12" s="78" t="n">
+      <c r="I12" s="79" t="n">
         <f aca="false">'Balance Sheet'!I18</f>
         <v>0</v>
       </c>
-      <c r="J12" s="78" t="n">
+      <c r="J12" s="79" t="n">
         <f aca="false">'Balance Sheet'!J18</f>
         <v>0</v>
       </c>
-      <c r="K12" s="78" t="n">
+      <c r="K12" s="79" t="n">
         <f aca="false">'Balance Sheet'!K18</f>
         <v>0</v>
       </c>
-      <c r="L12" s="78" t="n">
+      <c r="L12" s="79" t="n">
         <f aca="false">'Balance Sheet'!L18</f>
         <v>0</v>
       </c>
-      <c r="M12" s="78" t="n">
+      <c r="M12" s="79" t="n">
         <f aca="false">'Balance Sheet'!M18</f>
         <v>3392.09242260317</v>
       </c>
-      <c r="N12" s="78" t="n">
+      <c r="N12" s="79" t="n">
         <f aca="false">'Balance Sheet'!N18</f>
         <v>4104.81759271949</v>
       </c>
-      <c r="O12" s="78" t="n">
+      <c r="O12" s="79" t="n">
         <f aca="false">'Balance Sheet'!O18</f>
         <v>2535.31698269003</v>
       </c>
-      <c r="P12" s="78" t="n">
+      <c r="P12" s="79" t="n">
         <f aca="false">'Balance Sheet'!P18</f>
         <v>12.1361421654251</v>
       </c>
-      <c r="Q12" s="78" t="n">
+      <c r="Q12" s="79" t="n">
         <f aca="false">'Balance Sheet'!Q18</f>
         <v>0</v>
       </c>
-      <c r="R12" s="78" t="n">
+      <c r="R12" s="79" t="n">
         <f aca="false">'Balance Sheet'!R18</f>
         <v>0</v>
       </c>
-      <c r="S12" s="78" t="n">
+      <c r="S12" s="79" t="n">
         <f aca="false">'Balance Sheet'!S18</f>
         <v>0</v>
       </c>
-      <c r="T12" s="78" t="n">
+      <c r="T12" s="79" t="n">
         <f aca="false">'Balance Sheet'!T18</f>
         <v>0</v>
       </c>
-      <c r="U12" s="78" t="n">
+      <c r="U12" s="79" t="n">
         <f aca="false">'Balance Sheet'!U18</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B13" s="78" t="n">
+        <v>317</v>
+      </c>
+      <c r="B13" s="79" t="n">
         <f aca="false">'Balance Sheet'!B10</f>
         <v>2730.37</v>
       </c>
-      <c r="C13" s="78" t="n">
+      <c r="C13" s="79" t="n">
         <f aca="false">'Balance Sheet'!C10</f>
         <v>3185.89</v>
       </c>
-      <c r="D13" s="78" t="n">
+      <c r="D13" s="79" t="n">
         <f aca="false">'Balance Sheet'!D10</f>
         <v>3256.49</v>
       </c>
-      <c r="E13" s="78" t="n">
+      <c r="E13" s="79" t="n">
         <f aca="false">'Balance Sheet'!E10</f>
         <v>3947.99</v>
       </c>
-      <c r="F13" s="78" t="n">
+      <c r="F13" s="79" t="n">
         <f aca="false">'Balance Sheet'!F10</f>
         <v>4923.98</v>
       </c>
-      <c r="G13" s="78" t="n">
+      <c r="G13" s="79" t="n">
         <f aca="false">'Balance Sheet'!G10</f>
         <v>6133.89</v>
       </c>
-      <c r="H13" s="78" t="n">
+      <c r="H13" s="79" t="n">
         <f aca="false">'Balance Sheet'!H10</f>
         <v>5974.55</v>
       </c>
-      <c r="I13" s="78" t="n">
+      <c r="I13" s="79" t="n">
         <f aca="false">'Balance Sheet'!I10</f>
         <v>7757.46</v>
       </c>
-      <c r="J13" s="78" t="n">
+      <c r="J13" s="79" t="n">
         <f aca="false">'Balance Sheet'!J10</f>
         <v>9522.93</v>
       </c>
-      <c r="K13" s="78" t="n">
+      <c r="K13" s="79" t="n">
         <f aca="false">'Balance Sheet'!K10</f>
         <v>10527.09</v>
       </c>
-      <c r="L13" s="78" t="n">
+      <c r="L13" s="79" t="n">
         <f aca="false">'Balance Sheet'!L10</f>
         <v>17797.87772343</v>
       </c>
-      <c r="M13" s="78" t="n">
+      <c r="M13" s="79" t="n">
         <f aca="false">'Balance Sheet'!M10</f>
         <v>25063.7157652637</v>
       </c>
-      <c r="N13" s="78" t="n">
+      <c r="N13" s="79" t="n">
         <f aca="false">'Balance Sheet'!N10</f>
         <v>26829.0585332768</v>
       </c>
-      <c r="O13" s="78" t="n">
+      <c r="O13" s="79" t="n">
         <f aca="false">'Balance Sheet'!O10</f>
         <v>26970.2814941649</v>
       </c>
-      <c r="P13" s="78" t="n">
+      <c r="P13" s="79" t="n">
         <f aca="false">'Balance Sheet'!P10</f>
         <v>26916.8904837743</v>
       </c>
-      <c r="Q13" s="78" t="n">
+      <c r="Q13" s="79" t="n">
         <f aca="false">'Balance Sheet'!Q10</f>
         <v>27008.5783108577</v>
       </c>
-      <c r="R13" s="78" t="n">
+      <c r="R13" s="79" t="n">
         <f aca="false">'Balance Sheet'!R10</f>
         <v>27271.7298212504</v>
       </c>
-      <c r="S13" s="78" t="n">
+      <c r="S13" s="79" t="n">
         <f aca="false">'Balance Sheet'!S10</f>
         <v>27669.4211544973</v>
       </c>
-      <c r="T13" s="78" t="n">
+      <c r="T13" s="79" t="n">
         <f aca="false">'Balance Sheet'!T10</f>
         <v>28213.4856872016</v>
       </c>
-      <c r="U13" s="78" t="n">
+      <c r="U13" s="79" t="n">
         <f aca="false">'Balance Sheet'!U10</f>
         <v>28886.6293802962</v>
       </c>
@@ -4246,83 +4407,83 @@
       <c r="A14" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B14" s="78" t="n">
+      <c r="B14" s="79" t="n">
         <f aca="false">Schedules!B24</f>
         <v>1854.23</v>
       </c>
-      <c r="C14" s="78" t="n">
+      <c r="C14" s="79" t="n">
         <f aca="false">Schedules!C24</f>
         <v>2613.07</v>
       </c>
-      <c r="D14" s="78" t="n">
+      <c r="D14" s="79" t="n">
         <f aca="false">Schedules!D24</f>
         <v>2887.67</v>
       </c>
-      <c r="E14" s="78" t="n">
+      <c r="E14" s="79" t="n">
         <f aca="false">Schedules!E24</f>
         <v>2548.22</v>
       </c>
-      <c r="F14" s="78" t="n">
+      <c r="F14" s="79" t="n">
         <f aca="false">Schedules!F24</f>
         <v>2891.17</v>
       </c>
-      <c r="G14" s="78" t="n">
+      <c r="G14" s="79" t="n">
         <f aca="false">Schedules!G24</f>
         <v>3272.12</v>
       </c>
-      <c r="H14" s="78" t="n">
+      <c r="H14" s="79" t="n">
         <f aca="false">Schedules!H24</f>
         <v>3994.62</v>
       </c>
-      <c r="I14" s="78" t="n">
+      <c r="I14" s="79" t="n">
         <f aca="false">Schedules!I24</f>
         <v>8026.36</v>
       </c>
-      <c r="J14" s="78" t="n">
+      <c r="J14" s="79" t="n">
         <f aca="false">Schedules!J24</f>
         <v>9696.9</v>
       </c>
-      <c r="K14" s="78" t="n">
+      <c r="K14" s="79" t="n">
         <f aca="false">Schedules!K24</f>
         <v>10877.5</v>
       </c>
-      <c r="L14" s="78" t="n">
+      <c r="L14" s="79" t="n">
         <f aca="false">Schedules!L24</f>
         <v>18775.8139158579</v>
       </c>
-      <c r="M14" s="78" t="n">
+      <c r="M14" s="79" t="n">
         <f aca="false">Schedules!M24</f>
         <v>20841.5636505861</v>
       </c>
-      <c r="N14" s="78" t="n">
+      <c r="N14" s="79" t="n">
         <f aca="false">Schedules!N24</f>
         <v>22981.2544470552</v>
       </c>
-      <c r="O14" s="78" t="n">
+      <c r="O14" s="79" t="n">
         <f aca="false">Schedules!O24</f>
         <v>25583.3586191545</v>
       </c>
-      <c r="P14" s="78" t="n">
+      <c r="P14" s="79" t="n">
         <f aca="false">Schedules!P24</f>
         <v>28604.4102080769</v>
       </c>
-      <c r="Q14" s="78" t="n">
+      <c r="Q14" s="79" t="n">
         <f aca="false">Schedules!Q24</f>
         <v>32076.4813411262</v>
       </c>
-      <c r="R14" s="78" t="n">
+      <c r="R14" s="79" t="n">
         <f aca="false">Schedules!R24</f>
         <v>35985.8605122595</v>
       </c>
-      <c r="S14" s="78" t="n">
+      <c r="S14" s="79" t="n">
         <f aca="false">Schedules!S24</f>
         <v>40352.9630083805</v>
       </c>
-      <c r="T14" s="78" t="n">
+      <c r="T14" s="79" t="n">
         <f aca="false">Schedules!T24</f>
         <v>45199.3889170401</v>
       </c>
-      <c r="U14" s="78" t="n">
+      <c r="U14" s="79" t="n">
         <f aca="false">Schedules!U24</f>
         <v>50538.4554344112</v>
       </c>
@@ -6666,11 +6827,11 @@
         <v>0.5</v>
       </c>
       <c r="C43" s="36" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D43" s="37" t="n">
         <f aca="false">B43*C43</f>
-        <v>64.5</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6682,11 +6843,11 @@
         <v>0.25</v>
       </c>
       <c r="C44" s="36" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="D44" s="37" t="n">
         <f aca="false">B44*C44</f>
-        <v>38.75</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6698,11 +6859,11 @@
         <v>0.25</v>
       </c>
       <c r="C45" s="36" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D45" s="37" t="n">
         <f aca="false">B45*C45</f>
-        <v>15</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6715,7 +6876,7 @@
       </c>
       <c r="D46" s="38" t="n">
         <f aca="false">SUM(D43:D45)</f>
-        <v>118.25</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6723,8 +6884,8 @@
         <v>127</v>
       </c>
       <c r="B48" s="39" t="n">
-        <f aca="false">DCF!B33</f>
-        <v>129.40298338516</v>
+        <f aca="false">DCF!B43</f>
+        <v>121.083756994038</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6733,7 +6894,7 @@
       </c>
       <c r="B49" s="37" t="n">
         <f aca="false">INDEX(C43:C45,Scenarios!$B$4)</f>
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/reports/JSWINFRA/JSW_Infrastructure_Ltd_ERIP_Model.xlsx
+++ b/reports/JSWINFRA/JSW_Infrastructure_Ltd_ERIP_Model.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="360">
   <si>
     <t xml:space="preserve">JSW Infrastructure Ltd - Dashboard</t>
   </si>
@@ -104,12 +104,15 @@
     <t xml:space="preserve">EPS (INR)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Target basis: DCF with an exit EV/EBITDA of</t>
+    <t xml:space="preserve">    Target basis</t>
   </si>
   <si>
     <t xml:space="preserve">EBITDA margin</t>
   </si>
   <si>
+    <t xml:space="preserve">    Target horizon (months)</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Active scenario</t>
   </si>
   <si>
@@ -155,7 +158,7 @@
     <t xml:space="preserve">    Probability-weighted, perpetuity</t>
   </si>
   <si>
-    <t xml:space="preserve">    DCF at the target exit multiple</t>
+    <t xml:space="preserve">    DCF at the cross-check exit multiple</t>
   </si>
   <si>
     <t xml:space="preserve">    DCF at the alternative exit multiple</t>
@@ -362,6 +365,15 @@
     <t xml:space="preserve">- Scenarios 'base/bull/bear' were each built by financial-model and valued by model.py; the Scenarios sheet checks this workbook against those values.</t>
   </si>
   <si>
+    <t xml:space="preserve">Explained check failures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- EXPLAINED  Reserves roll-forward residual (history) (Mar-24, INR 2,938 Cr): IPO in September 2023: shares rose from 186.5 Cr to 210.0 Cr (23.5 Cr fresh shares, about INR 2,800 Cr raised). Screener records no equity issuance, so reserves grow by more than profit less dividends. Moves the valuation: no. Source: data/financials.json (No. of Equity Shares, Equity Share Capital, Reserves); kb/annual_report notes on unutilised IPO proceeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- EXPLAINED  Reconstructed CFO close to reported CFO (Mar-26, INR 1,071 Cr): Reported FY26 CFO of INR 2,021.5 Cr bridges cleanly: operating profit before working capital INR 2,688.5 Cr, working capital INR -320.4 Cr, tax paid INR -346.6 Cr. The model's reconstruction takes working capital from Screener balance-sheet movements, which include capital creditors, deposits and balances consolidated with the Navkar acquisition. The forecast inherits this as a INR 489 Cr working-capital release in FY27 as balances move to the driver levels, worth about INR 1.5 a share. Moves the valuation: yes. Source: kb/annual_report/pages/page_0180.md (Consolidated Statement of Cash Flows, AR p.181)</t>
+  </si>
+  <si>
     <t xml:space="preserve">JSW Infrastructure Ltd - Summary</t>
   </si>
   <si>
@@ -953,6 +965,18 @@
     <t xml:space="preserve">assumptions.json net_debt, as at the balance-sheet date</t>
   </si>
   <si>
+    <t xml:space="preserve">    Lease liabilities (Ind AS 116, debt-like)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assumptions.json lease_liabilities (annual report)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Minority interest (book value)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assumptions.json minority_interest (annual report)</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Non-operating assets</t>
   </si>
   <si>
@@ -983,7 +1007,52 @@
     <t xml:space="preserve">    Upside / (downside)</t>
   </si>
   <si>
-    <t xml:space="preserve">Exit-multiple cross-check and target</t>
+    <t xml:space="preserve">Target price (12-month forward)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Target method  (Perpetuity DCF or Exit multiple)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perpetuity DCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assumptions.json target_policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Horizon (months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Value per share today, on the target method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dividend per share, next 12 months (first forecast year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedules: dividends declared / shares, first forecast year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Forward value  (value x (1 + ke)^(h/12) - DPS x h/12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Rounding step (INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target price (INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    BUY above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House rating policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SELL below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit-multiple cross-check (not the target unless chosen above)</t>
   </si>
   <si>
     <t xml:space="preserve">    Terminal-year EBITDA</t>
@@ -992,10 +1061,7 @@
     <t xml:space="preserve">    Exit EV/EBITDA implied by the perpetuity TV</t>
   </si>
   <si>
-    <t xml:space="preserve">    Exit multiple (house convention)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target anchor: DCF with an exit multiple</t>
+    <t xml:space="preserve">    Exit multiple</t>
   </si>
   <si>
     <t xml:space="preserve">    Terminal value at exit multiple</t>
@@ -1005,24 +1071,6 @@
   </si>
   <si>
     <t xml:space="preserve">Value per share at exit multiple (INR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Rounding step (INR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target price (INR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    BUY above</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House rating policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    SELL below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating</t>
   </si>
   <si>
     <t xml:space="preserve">    Alternative exit multiple</t>
@@ -1100,16 +1148,16 @@
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
     <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\)"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
-    <numFmt numFmtId="171" formatCode="0.0\x"/>
+    <numFmt numFmtId="171" formatCode="0"/>
     <numFmt numFmtId="172" formatCode="0.00%"/>
     <numFmt numFmtId="173" formatCode="0.00\x"/>
-    <numFmt numFmtId="174" formatCode="0"/>
-    <numFmt numFmtId="175" formatCode="0%"/>
-    <numFmt numFmtId="176" formatCode="#,##0.0"/>
-    <numFmt numFmtId="177" formatCode="#,##0.000;\(#,##0.000\)"/>
-    <numFmt numFmtId="178" formatCode="dd\-mmm\-yyyy"/>
-    <numFmt numFmtId="179" formatCode="0.000"/>
-    <numFmt numFmtId="180" formatCode="0.0000"/>
+    <numFmt numFmtId="174" formatCode="0%"/>
+    <numFmt numFmtId="175" formatCode="#,##0.0"/>
+    <numFmt numFmtId="176" formatCode="#,##0.000;\(#,##0.000\)"/>
+    <numFmt numFmtId="177" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="178" formatCode="0.000"/>
+    <numFmt numFmtId="179" formatCode="0.0000"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -1379,7 +1427,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1436,7 +1484,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1444,7 +1492,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1536,7 +1584,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="171" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1552,7 +1600,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="174" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1560,7 +1608,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1584,11 +1632,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="175" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1644,15 +1692,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1692,7 +1740,19 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="177" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="178" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1700,11 +1760,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="168" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="165" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1712,23 +1772,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="180" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="180" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1921,7 +1973,7 @@
                   <c:v>    Probability-weighted, perpetuity</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>    DCF at the target exit multiple</c:v>
+                  <c:v>    DCF at the cross-check exit multiple</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>    DCF at the alternative exit multiple</c:v>
@@ -1939,22 +1991,22 @@
                 <c:formatCode>#,##0;\(#,##0\)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>121</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>129</c:v>
+                  <c:v>123</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>58</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>107.25</c:v>
+                  <c:v>101.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>184.336076421551</c:v>
+                  <c:v>178.553826483578</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>242.192944944847</c:v>
+                  <c:v>236.410695006873</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>357.45</c:v>
@@ -1965,11 +2017,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="58488432"/>
-        <c:axId val="17057060"/>
+        <c:axId val="9162385"/>
+        <c:axId val="75626988"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58488432"/>
+        <c:axId val="9162385"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2002,7 +2054,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17057060"/>
+        <c:crossAx val="75626988"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2010,7 +2062,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17057060"/>
+        <c:axId val="75626988"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2043,7 +2095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58488432"/>
+        <c:crossAx val="9162385"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2549,7 +2601,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="7" t="str">
-        <f aca="false">DCF!B59</f>
+        <f aca="false">DCF!B60</f>
         <v>SELL</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -2573,8 +2625,8 @@
         <v>10</v>
       </c>
       <c r="B6" s="10" t="n">
-        <f aca="false">DCF!B55</f>
-        <v>185</v>
+        <f aca="false">DCF!B56</f>
+        <v>130</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>11</v>
@@ -2597,7 +2649,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="11" t="n">
-        <f aca="false">DCF!B44</f>
+        <f aca="false">DCF!B46</f>
         <v>357.45</v>
       </c>
       <c r="D7" s="8" t="s">
@@ -2609,11 +2661,11 @@
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">'Income Statement'!L18</f>
-        <v>1526.49308622419</v>
+        <v>1526.49308623925</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">'Income Statement'!M18</f>
-        <v>2347.44288049106</v>
+        <v>2347.44288054327</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2621,8 +2673,8 @@
         <v>14</v>
       </c>
       <c r="B8" s="12" t="n">
-        <f aca="false">DCF!B56</f>
-        <v>-0.482445097216394</v>
+        <f aca="false">DCF!B57</f>
+        <v>-0.636312771016925</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>15</v>
@@ -2633,20 +2685,20 @@
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">'Income Statement'!L19</f>
-        <v>6.56980024198059</v>
+        <v>6.56980024204542</v>
       </c>
       <c r="G8" s="13" t="n">
         <f aca="false">'Income Statement'!M19</f>
-        <v>10.1030466128301</v>
+        <v>10.1030466130547</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="14" t="str">
         <f aca="false">DCF!B50</f>
-        <v>10</v>
+        <v>Perpetuity DCF</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>17</v>
@@ -2668,14 +2720,23 @@
       <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="16" t="str">
+      <c r="B10" s="16" t="n">
+        <f aca="false">DCF!B51</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="14" t="str">
         <f aca="false">Scenarios!B5</f>
         <v>Base</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>3</v>
@@ -2683,16 +2744,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="17" t="n">
-        <f aca="false">DCF!B43</f>
-        <v>121.083756994038</v>
+        <f aca="false">DCF!B45</f>
+        <v>115.301507056065</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="18" t="n">
         <f aca="false">DCF!B27</f>
@@ -2701,7 +2762,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">DCF!B28</f>
@@ -2710,7 +2771,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">DCF!B29</f>
@@ -2719,7 +2780,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="19" t="n">
         <f aca="false">DCF!B35</f>
@@ -2728,7 +2789,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">DCF!B34</f>
@@ -2737,87 +2798,87 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="9" t="n">
-        <f aca="false">DCF!B41</f>
-        <v>28133.8109375647</v>
+        <f aca="false">DCF!B43</f>
+        <v>26790.3051644766</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="17" t="n">
         <f aca="false">Scenarios!C43</f>
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="17" t="n">
         <f aca="false">Scenarios!C44</f>
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="17" t="n">
         <f aca="false">Scenarios!C45</f>
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="17" t="n">
         <f aca="false">Scenarios!D46</f>
-        <v>107.25</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="17" t="n">
-        <f aca="false">DCF!B53</f>
-        <v>184.336076421551</v>
+        <f aca="false">DCF!B68</f>
+        <v>178.553826483578</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="17" t="n">
-        <f aca="false">DCF!B62</f>
-        <v>242.192944944847</v>
+        <f aca="false">DCF!B70</f>
+        <v>236.410695006873</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="17" t="n">
-        <f aca="false">DCF!B44</f>
+        <f aca="false">DCF!B46</f>
         <v>357.45</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2848,12 +2909,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2862,50 +2923,50 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="41" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B6" s="42" t="n">
         <v>0.072</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B7" s="42" t="n">
         <v>0.055</v>
       </c>
       <c r="C7" s="72" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B8" s="73" t="n">
         <v>0.9</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B9" s="74" t="n">
         <f aca="false">0.67*B8+0.33</f>
@@ -2914,7 +2975,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B10" s="75" t="n">
         <f aca="false">B6+B9*B7</f>
@@ -2923,34 +2984,34 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="41" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B13" s="42" t="n">
         <v>0.07</v>
       </c>
       <c r="C13" s="72" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B14" s="42" t="n">
         <v>0.22</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B15" s="15" t="n">
         <f aca="false">B13*(1-B14)</f>
@@ -2959,18 +3020,18 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B16" s="42" t="n">
         <v>0.12</v>
       </c>
       <c r="C16" s="72" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B18" s="76" t="n">
         <f aca="false">B10*(1-B16)+B15*B16</f>
@@ -2979,7 +3040,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B19" s="19" t="n">
         <f aca="false">Scenarios!$B$39</f>
@@ -2988,7 +3049,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B20" s="77" t="str">
         <f aca="false">IF(B19&lt;WACC!$B$18,"OK","FAIL")</f>
@@ -3012,7 +3073,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -3021,17 +3082,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>6</v>
@@ -3040,33 +3101,33 @@
         <v>7</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="41" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3161,7 +3222,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Income Statement'!L12</f>
@@ -3206,7 +3267,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">Drivers!L22</f>
@@ -3251,7 +3312,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B10" s="53" t="n">
         <f aca="false">B8*(1-B9)</f>
@@ -3296,7 +3357,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">'Income Statement'!L11</f>
@@ -3341,7 +3402,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">-Schedules!L7</f>
@@ -3386,7 +3447,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">-Schedules!L12</f>
@@ -3431,7 +3492,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B14" s="64" t="n">
         <f aca="false">B10+B11+B12+B13</f>
@@ -3476,23 +3537,23 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="41" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B17" s="78" t="n">
         <v>46203</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B18" s="78" t="n">
         <v>46477</v>
@@ -3500,7 +3561,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B19" s="78" t="n">
         <v>46296</v>
@@ -3508,7 +3569,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B20" s="79" t="n">
         <f aca="false">MIN(1,MAX(0,(B18-B17)/365.25))</f>
@@ -3517,7 +3578,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B21" s="79" t="n">
         <f aca="false">$B$20</f>
@@ -3553,7 +3614,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B22" s="74" t="n">
         <f aca="false">$B$20*0.5</f>
@@ -3598,7 +3659,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B23" s="79" t="n">
         <f aca="false">1/(1+WACC!$B$18)^B22</f>
@@ -3643,7 +3704,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B24" s="53" t="n">
         <f aca="false">B14*B21*B23</f>
@@ -3688,12 +3749,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="41" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B27" s="18" t="n">
         <f aca="false">WACC!$B$18</f>
@@ -3702,7 +3763,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B28" s="19" t="n">
         <f aca="false">Scenarios!$B$39</f>
@@ -3711,18 +3772,18 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B29" s="42" t="n">
         <v>0.12</v>
       </c>
       <c r="C29" s="72" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B30" s="15" t="n">
         <f aca="false">$B$28/$B$29</f>
@@ -3731,7 +3792,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B31" s="53" t="n">
         <f aca="false">SUM(B24:K24)</f>
@@ -3740,7 +3801,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B32" s="53" t="n">
         <f aca="false">K10*(1+$B$28)*(1-$B$28/$B$29)/($B$27-$B$28)</f>
@@ -3749,7 +3810,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B33" s="53" t="n">
         <f aca="false">$B$32/(1+$B$27)^K22</f>
@@ -3758,7 +3819,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B34" s="64" t="n">
         <f aca="false">$B$31+$B$33</f>
@@ -3767,7 +3828,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B35" s="15" t="n">
         <f aca="false">$B$33/$B$34</f>
@@ -3776,236 +3837,309 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B36" s="81" t="n">
         <v>-2769</v>
       </c>
       <c r="C36" s="72" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B37" s="81" t="n">
-        <v>0</v>
+        <v>489.07</v>
       </c>
       <c r="C37" s="72" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="B38" s="53" t="n">
-        <f aca="false">$B$34-$B$36+$B$37</f>
-        <v>27313.0281082674</v>
+        <v>305</v>
+      </c>
+      <c r="B38" s="81" t="n">
+        <v>815.24</v>
+      </c>
+      <c r="C38" s="72" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="B39" s="19" t="n">
+        <v>307</v>
+      </c>
+      <c r="B39" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="72" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B40" s="53" t="n">
+        <f aca="false">$B$34-$B$36-$B$37-$B$38+$B$39</f>
+        <v>26008.7181082674</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B41" s="19" t="n">
         <f aca="false">WACC!$B$10</f>
         <v>0.123315</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="B40" s="82" t="n">
-        <f aca="false">(1+$B$39)^((B19-B17)/365.25)</f>
-        <v>1.03005096417884</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="B41" s="64" t="n">
-        <f aca="false">$B$38*$B$40</f>
-        <v>28133.8109375647</v>
-      </c>
-    </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="B42" s="13" t="n">
+        <v>311</v>
+      </c>
+      <c r="B42" s="82" t="n">
+        <f aca="false">(1+$B$41)^((B19-B17)/365.25)</f>
+        <v>1.03005096417884</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B43" s="64" t="n">
+        <f aca="false">$B$40*$B$42</f>
+        <v>26790.3051644766</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B44" s="13" t="n">
         <f aca="false">Schedules!K23</f>
         <v>232.35</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="B43" s="48" t="n">
-        <f aca="false">$B$41/$B$42</f>
-        <v>121.083756994038</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">$B$43/$B$44</f>
+        <v>115.301507056065</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B44" s="83" t="n">
+      <c r="B46" s="83" t="n">
         <v>357.45</v>
       </c>
-      <c r="C44" s="72" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B45" s="15" t="n">
-        <f aca="false">$B$43/$B$44-1</f>
-        <v>-0.661256799569064</v>
+      <c r="C46" s="72" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="41" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="B48" s="53" t="n">
+      <c r="A47" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B47" s="15" t="n">
+        <f aca="false">$B$45/$B$46-1</f>
+        <v>-0.677433187701596</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="41" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B50" s="84" t="s">
+        <v>319</v>
+      </c>
+      <c r="C50" s="72" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B51" s="39" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B52" s="47" t="n">
+        <f aca="false">IF($B$50="Exit multiple",$B$68,$B$45)</f>
+        <v>115.301507056065</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B53" s="13" t="n">
+        <f aca="false">IFERROR(Schedules!L22/Schedules!L23,0)</f>
+        <v>0.78837602904361</v>
+      </c>
+      <c r="C53" s="72" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B54" s="47" t="n">
+        <f aca="false">$B$52*(1+$B$41)^($B$51/12)-$B$53*$B$51/12</f>
+        <v>128.73153636964</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="B55" s="39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B56" s="48" t="n">
+        <f aca="false">ROUND($B$54/$B$55,0)*$B$55</f>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="15" t="n">
+        <f aca="false">$B$56/$B$46-1</f>
+        <v>-0.636312771016925</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="B58" s="42" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C58" s="72" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B59" s="42" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C59" s="72" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B60" s="40" t="str">
+        <f aca="false">IF($B$57&gt;$B$58,"BUY",IF($B$57&lt;$B$59,"SELL","HOLD"))</f>
+        <v>SELL</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="41" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="B63" s="53" t="n">
         <f aca="false">K7</f>
         <v>8935.70507202225</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="B49" s="84" t="n">
-        <f aca="false">$B$32/$B$48</f>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="B64" s="85" t="n">
+        <f aca="false">$B$32/$B$63</f>
         <v>5.62697940334977</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="B50" s="85" t="n">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="B65" s="86" t="n">
         <v>10</v>
       </c>
-      <c r="C50" s="72" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="B51" s="53" t="n">
-        <f aca="false">$B$50*$B$48</f>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B66" s="53" t="n">
+        <f aca="false">$B$65*$B$63</f>
         <v>89357.0507202225</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="B52" s="53" t="n">
-        <f aca="false">$B$51/(1+$B$27)^K22</f>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B67" s="53" t="n">
+        <f aca="false">$B$66/(1+$B$27)^K22</f>
         <v>32627.1317364001</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="B53" s="48" t="n">
-        <f aca="false">($B$31+$B$52-$B$36+$B$37)*$B$40/$B$42</f>
-        <v>184.336076421551</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="B54" s="39" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B55" s="48" t="n">
-        <f aca="false">ROUND($B$53/$B$54,0)*$B$54</f>
-        <v>185</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B68" s="48" t="n">
+        <f aca="false">($B$31+$B$67-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
+        <v>178.553826483578</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="B69" s="86" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="15" t="n">
-        <f aca="false">$B$55/$B$44-1</f>
-        <v>-0.482445097216394</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="B57" s="42" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C57" s="72" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="B58" s="42" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C58" s="72" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B59" s="40" t="str">
-        <f aca="false">IF($B$56&gt;$B$57,"BUY",IF($B$56&lt;$B$58,"SELL","HOLD"))</f>
-        <v>SELL</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B61" s="85" t="n">
-        <v>14</v>
-      </c>
-      <c r="C61" s="72" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="B62" s="47" t="n">
-        <f aca="false">($B$31+$B$61*$B$48/(1+$B$27)^K22-$B$36+$B$37)*$B$40/$B$42</f>
-        <v>242.192944944847</v>
+      <c r="C69" s="72" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B70" s="47" t="n">
+        <f aca="false">($B$31+$B$69*$B$63/(1+$B$27)^K22-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
+        <v>236.410695006873</v>
       </c>
     </row>
   </sheetData>
@@ -4034,17 +4168,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B4" s="42" t="n">
         <v>0.005</v>
@@ -4052,20 +4186,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="B5" s="85" t="n">
+        <v>345</v>
+      </c>
+      <c r="B5" s="86" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="41" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="B8" s="75" t="n">
         <f aca="false">DCF!$B$28+(-2)*$B$4</f>
@@ -4094,24 +4228,24 @@
         <v>0.1050692</v>
       </c>
       <c r="B9" s="47" t="n">
-        <f aca="false">IF(B$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A9-B$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>141.481278112723</v>
+        <f aca="false">IF(B$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A9-B$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>135.69902817475</v>
       </c>
       <c r="C9" s="47" t="n">
-        <f aca="false">IF(C$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A9-C$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>143.132215753428</v>
+        <f aca="false">IF(C$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A9-C$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>137.349965815455</v>
       </c>
       <c r="D9" s="47" t="n">
-        <f aca="false">IF(D$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A9-D$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>144.97554083931</v>
+        <f aca="false">IF(D$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A9-D$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>139.193290901336</v>
       </c>
       <c r="E9" s="47" t="n">
-        <f aca="false">IF(E$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A9-E$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>147.059294823852</v>
+        <f aca="false">IF(E$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A9-E$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>141.277044885879</v>
       </c>
       <c r="F9" s="47" t="n">
-        <f aca="false">IF(F$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A9-F$8)/(1+$A9)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>149.448966827652</v>
+        <f aca="false">IF(F$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A9-F$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>143.666716889679</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4120,24 +4254,24 @@
         <v>0.1100692</v>
       </c>
       <c r="B10" s="47" t="n">
-        <f aca="false">IF(B$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A10-B$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>129.905471348028</v>
+        <f aca="false">IF(B$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A10-B$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>124.123221410054</v>
       </c>
       <c r="C10" s="47" t="n">
-        <f aca="false">IF(C$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A10-C$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>130.990241483892</v>
+        <f aca="false">IF(C$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A10-C$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>125.207991545919</v>
       </c>
       <c r="D10" s="47" t="n">
-        <f aca="false">IF(D$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A10-D$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>132.175198939132</v>
+        <f aca="false">IF(D$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A10-D$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>126.392949001159</v>
       </c>
       <c r="E10" s="47" t="n">
-        <f aca="false">IF(E$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A10-E$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>133.483439276481</v>
+        <f aca="false">IF(E$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A10-E$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>127.701189338508</v>
       </c>
       <c r="F10" s="47" t="n">
-        <f aca="false">IF(F$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A10-F$8)/(1+$A10)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>134.945747710853</v>
+        <f aca="false">IF(F$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A10-F$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>129.16349777288</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4146,24 +4280,24 @@
         <v>0.1150692</v>
       </c>
       <c r="B11" s="47" t="n">
-        <f aca="false">IF(B$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A11-B$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>119.717140280606</v>
+        <f aca="false">IF(B$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A11-B$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>113.934890342633</v>
       </c>
       <c r="C11" s="47" t="n">
-        <f aca="false">IF(C$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A11-C$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>120.380707675442</v>
+        <f aca="false">IF(C$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A11-C$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>114.598457737469</v>
       </c>
       <c r="D11" s="48" t="n">
-        <f aca="false">IF(D$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A11-D$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>121.083756994038</v>
+        <f aca="false">IF(D$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A11-D$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>115.301507056065</v>
       </c>
       <c r="E11" s="47" t="n">
-        <f aca="false">IF(E$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A11-E$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>121.834740293165</v>
+        <f aca="false">IF(E$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A11-E$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>116.052490355191</v>
       </c>
       <c r="F11" s="47" t="n">
-        <f aca="false">IF(F$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A11-F$8)/(1+$A11)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>122.644707496719</v>
+        <f aca="false">IF(F$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A11-F$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>116.862457558745</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4172,24 +4306,24 @@
         <v>0.1200692</v>
       </c>
       <c r="B12" s="47" t="n">
-        <f aca="false">IF(B$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A12-B$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>110.685176331286</v>
+        <f aca="false">IF(B$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A12-B$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>104.902926393313</v>
       </c>
       <c r="C12" s="47" t="n">
-        <f aca="false">IF(C$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A12-C$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>111.033906635952</v>
+        <f aca="false">IF(C$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A12-C$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>105.251656697979</v>
       </c>
       <c r="D12" s="47" t="n">
-        <f aca="false">IF(D$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A12-D$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>111.382191856473</v>
+        <f aca="false">IF(D$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A12-D$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>105.599941918499</v>
       </c>
       <c r="E12" s="47" t="n">
-        <f aca="false">IF(E$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A12-E$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>111.729943058076</v>
+        <f aca="false">IF(E$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A12-E$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>105.947693120103</v>
       </c>
       <c r="F12" s="47" t="n">
-        <f aca="false">IF(F$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A12-F$8)/(1+$A12)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>112.077045921151</v>
+        <f aca="false">IF(F$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A12-F$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>106.294795983178</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4198,53 +4332,53 @@
         <v>0.1250692</v>
       </c>
       <c r="B13" s="47" t="n">
-        <f aca="false">IF(B$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A13-B$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>102.627071137506</v>
+        <f aca="false">IF(B$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A13-B$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>96.8448211995322</v>
       </c>
       <c r="C13" s="47" t="n">
-        <f aca="false">IF(C$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A13-C$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>102.739973238036</v>
+        <f aca="false">IF(C$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A13-C$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>96.9577233000628</v>
       </c>
       <c r="D13" s="47" t="n">
-        <f aca="false">IF(D$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A13-D$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>102.826406058116</v>
+        <f aca="false">IF(D$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A13-D$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>97.044156120143</v>
       </c>
       <c r="E13" s="47" t="n">
-        <f aca="false">IF(E$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A13-E$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>102.881410896938</v>
+        <f aca="false">IF(E$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A13-E$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>97.0991609589645</v>
       </c>
       <c r="F13" s="47" t="n">
-        <f aca="false">IF(F$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A13-F$8)/(1+$A13)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42)</f>
-        <v>102.898707952413</v>
+        <f aca="false">IF(F$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A13-F$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
+        <v>97.1164580144396</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="41" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="B16" s="86" t="n">
-        <f aca="false">DCF!$B$50+(-2)*$B$5</f>
+        <v>349</v>
+      </c>
+      <c r="B16" s="87" t="n">
+        <f aca="false">DCF!$B$65+(-2)*$B$5</f>
         <v>6</v>
       </c>
-      <c r="C16" s="86" t="n">
-        <f aca="false">DCF!$B$50+(-1)*$B$5</f>
+      <c r="C16" s="87" t="n">
+        <f aca="false">DCF!$B$65+(-1)*$B$5</f>
         <v>8</v>
       </c>
-      <c r="D16" s="86" t="n">
-        <f aca="false">DCF!$B$50+(0)*$B$5</f>
+      <c r="D16" s="87" t="n">
+        <f aca="false">DCF!$B$65+(0)*$B$5</f>
         <v>10</v>
       </c>
-      <c r="E16" s="86" t="n">
-        <f aca="false">DCF!$B$50+(1)*$B$5</f>
+      <c r="E16" s="87" t="n">
+        <f aca="false">DCF!$B$65+(1)*$B$5</f>
         <v>12</v>
       </c>
-      <c r="F16" s="86" t="n">
-        <f aca="false">DCF!$B$50+(2)*$B$5</f>
+      <c r="F16" s="87" t="n">
+        <f aca="false">DCF!$B$65+(2)*$B$5</f>
         <v>14</v>
       </c>
     </row>
@@ -4254,24 +4388,24 @@
         <v>0.1050692</v>
       </c>
       <c r="B17" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>137.244689743407</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>131.462439805433</v>
       </c>
       <c r="C17" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>168.68702493657</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>162.904774998597</v>
       </c>
       <c r="D17" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>200.129360129733</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>194.34711019176</v>
       </c>
       <c r="E17" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>231.571695322896</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>225.789445384923</v>
       </c>
       <c r="F17" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A17)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>263.014030516059</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>257.231780578086</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4280,24 +4414,24 @@
         <v>0.1100692</v>
       </c>
       <c r="B18" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>131.745326438666</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>125.963076500692</v>
       </c>
       <c r="C18" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>161.901699605484</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>156.119449667511</v>
       </c>
       <c r="D18" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>192.058072772303</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>186.27582283433</v>
       </c>
       <c r="E18" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>222.214445939122</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>216.432196001149</v>
       </c>
       <c r="F18" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A18)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>252.370819105941</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>246.588569167967</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4306,24 +4440,24 @@
         <v>0.1150692</v>
       </c>
       <c r="B19" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>126.479207898256</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>120.696957960283</v>
       </c>
       <c r="C19" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>155.407642159904</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>149.62539222193</v>
       </c>
       <c r="D19" s="48" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>184.336076421551</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>178.553826483578</v>
       </c>
       <c r="E19" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>213.264510683199</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>207.482260745226</v>
       </c>
       <c r="F19" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A19)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>242.192944944847</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>236.410695006873</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4332,24 +4466,24 @@
         <v>0.1200692</v>
       </c>
       <c r="B20" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>121.435330806186</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>115.653080868212</v>
       </c>
       <c r="C20" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>149.190988475413</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>143.40873853744</v>
       </c>
       <c r="D20" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>176.94664614464</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>171.164396206667</v>
       </c>
       <c r="E20" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>204.702303813867</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>198.920053875894</v>
       </c>
       <c r="F20" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A20)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>232.457961483094</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>226.675711545121</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4358,24 +4492,24 @@
         <v>0.1250692</v>
       </c>
       <c r="B21" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+B$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>116.603262569662</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>110.821012631689</v>
       </c>
       <c r="C21" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+C$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>143.238598067401</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>137.456348129428</v>
       </c>
       <c r="D21" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+D$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>169.87393356514</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>164.091683627167</v>
       </c>
       <c r="E21" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+E$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>196.509269062879</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>190.727019124905</v>
       </c>
       <c r="F21" s="47" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+F$16*DCF!$B$48/(1+$A21)^DCF!$K$22-DCF!$B$36+DCF!$B$37)*DCF!$B$40/DCF!$B$42</f>
-        <v>223.144604560618</v>
+        <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
+        <v>217.362354622644</v>
       </c>
     </row>
   </sheetData>
@@ -4404,44 +4538,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>5</v>
@@ -4453,33 +4587,33 @@
         <v>7</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="T4" s="27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="U4" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
@@ -4504,347 +4638,347 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="B6" s="87" t="n">
+        <v>352</v>
+      </c>
+      <c r="B6" s="88" t="n">
         <f aca="false">('Balance Sheet'!B13-'Balance Sheet'!B22)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="87" t="n">
+      <c r="C6" s="88" t="n">
         <f aca="false">('Balance Sheet'!C13-'Balance Sheet'!C22)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="87" t="n">
+      <c r="D6" s="88" t="n">
         <f aca="false">('Balance Sheet'!D13-'Balance Sheet'!D22)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="87" t="n">
+      <c r="E6" s="88" t="n">
         <f aca="false">('Balance Sheet'!E13-'Balance Sheet'!E22)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="87" t="n">
+      <c r="F6" s="88" t="n">
         <f aca="false">('Balance Sheet'!F13-'Balance Sheet'!F22)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="87" t="n">
+      <c r="G6" s="88" t="n">
         <f aca="false">('Balance Sheet'!G13-'Balance Sheet'!G22)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="87" t="n">
+      <c r="H6" s="88" t="n">
         <f aca="false">('Balance Sheet'!H13-'Balance Sheet'!H22)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="87" t="n">
+      <c r="I6" s="88" t="n">
         <f aca="false">('Balance Sheet'!I13-'Balance Sheet'!I22)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="87" t="n">
+      <c r="J6" s="88" t="n">
         <f aca="false">('Balance Sheet'!J13-'Balance Sheet'!J22)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="87" t="n">
+      <c r="K6" s="88" t="n">
         <f aca="false">('Balance Sheet'!K13-'Balance Sheet'!K22)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="87" t="n">
+      <c r="L6" s="88" t="n">
         <f aca="false">('Balance Sheet'!L13-'Balance Sheet'!L22)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="87" t="n">
+        <v>5.32287231180817E-007</v>
+      </c>
+      <c r="M6" s="88" t="n">
         <f aca="false">('Balance Sheet'!M13-'Balance Sheet'!M22)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="87" t="n">
+        <v>5.32279955223203E-007</v>
+      </c>
+      <c r="N6" s="88" t="n">
         <f aca="false">('Balance Sheet'!N13-'Balance Sheet'!N22)</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="87" t="n">
+        <v>5.32294507138431E-007</v>
+      </c>
+      <c r="O6" s="88" t="n">
         <f aca="false">('Balance Sheet'!O13-'Balance Sheet'!O22)</f>
-        <v>0</v>
-      </c>
-      <c r="P6" s="87" t="n">
+        <v>5.32294507138431E-007</v>
+      </c>
+      <c r="P6" s="88" t="n">
         <f aca="false">('Balance Sheet'!P13-'Balance Sheet'!P22)</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="87" t="n">
+        <v>5.32294507138431E-007</v>
+      </c>
+      <c r="Q6" s="88" t="n">
         <f aca="false">('Balance Sheet'!Q13-'Balance Sheet'!Q22)</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="87" t="n">
+        <v>5.32294507138431E-007</v>
+      </c>
+      <c r="R6" s="88" t="n">
         <f aca="false">('Balance Sheet'!R13-'Balance Sheet'!R22)</f>
-        <v>0</v>
-      </c>
-      <c r="S6" s="87" t="n">
+        <v>5.32287231180817E-007</v>
+      </c>
+      <c r="S6" s="88" t="n">
         <f aca="false">('Balance Sheet'!S13-'Balance Sheet'!S22)</f>
-        <v>0</v>
-      </c>
-      <c r="T6" s="87" t="n">
+        <v>5.32294507138431E-007</v>
+      </c>
+      <c r="T6" s="88" t="n">
         <f aca="false">('Balance Sheet'!T13-'Balance Sheet'!T22)</f>
-        <v>0</v>
-      </c>
-      <c r="U6" s="87" t="n">
+        <v>5.32287231180817E-007</v>
+      </c>
+      <c r="U6" s="88" t="n">
         <f aca="false">('Balance Sheet'!U13-'Balance Sheet'!U22)</f>
-        <v>0</v>
+        <v>5.32279955223203E-007</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B7" s="87" t="n">
+        <v>353</v>
+      </c>
+      <c r="B7" s="88" t="n">
         <f aca="false">('Balance Sheet'!B6-'Cash Flow'!B23)</f>
         <v>-1268.7</v>
       </c>
-      <c r="C7" s="87" t="n">
+      <c r="C7" s="88" t="n">
         <f aca="false">('Balance Sheet'!C6-'Cash Flow'!C23)</f>
         <v>491.16</v>
       </c>
-      <c r="D7" s="87" t="n">
+      <c r="D7" s="88" t="n">
         <f aca="false">('Balance Sheet'!D6-'Cash Flow'!D23)</f>
         <v>7.87999999999984</v>
       </c>
-      <c r="E7" s="87" t="n">
+      <c r="E7" s="88" t="n">
         <f aca="false">('Balance Sheet'!E6-'Cash Flow'!E23)</f>
         <v>-529.87</v>
       </c>
-      <c r="F7" s="87" t="n">
+      <c r="F7" s="88" t="n">
         <f aca="false">('Balance Sheet'!F6-'Cash Flow'!F23)</f>
         <v>51.5699999999998</v>
       </c>
-      <c r="G7" s="87" t="n">
+      <c r="G7" s="88" t="n">
         <f aca="false">('Balance Sheet'!G6-'Cash Flow'!G23)</f>
         <v>53</v>
       </c>
-      <c r="H7" s="87" t="n">
+      <c r="H7" s="88" t="n">
         <f aca="false">('Balance Sheet'!H6-'Cash Flow'!H23)</f>
         <v>-17.3399999999992</v>
       </c>
-      <c r="I7" s="87" t="n">
+      <c r="I7" s="88" t="n">
         <f aca="false">('Balance Sheet'!I6-'Cash Flow'!I23)</f>
         <v>2988.66</v>
       </c>
-      <c r="J7" s="87" t="n">
+      <c r="J7" s="88" t="n">
         <f aca="false">('Balance Sheet'!J6-'Cash Flow'!J23)</f>
         <v>333.339999999999</v>
       </c>
-      <c r="K7" s="87" t="n">
+      <c r="K7" s="88" t="n">
         <f aca="false">('Balance Sheet'!K6-'Cash Flow'!K23)</f>
         <v>-155.04</v>
       </c>
-      <c r="L7" s="87" t="n">
+      <c r="L7" s="88" t="n">
         <f aca="false">('Balance Sheet'!L6-'Cash Flow'!L23)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="87" t="n">
+      <c r="M7" s="88" t="n">
         <f aca="false">('Balance Sheet'!M6-'Cash Flow'!M23)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="87" t="n">
+      <c r="N7" s="88" t="n">
         <f aca="false">('Balance Sheet'!N6-'Cash Flow'!N23)</f>
         <v>0</v>
       </c>
-      <c r="O7" s="87" t="n">
+      <c r="O7" s="88" t="n">
         <f aca="false">('Balance Sheet'!O6-'Cash Flow'!O23)</f>
         <v>0</v>
       </c>
-      <c r="P7" s="87" t="n">
+      <c r="P7" s="88" t="n">
         <f aca="false">('Balance Sheet'!P6-'Cash Flow'!P23)</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="87" t="n">
+      <c r="Q7" s="88" t="n">
         <f aca="false">('Balance Sheet'!Q6-'Cash Flow'!Q23)</f>
         <v>0</v>
       </c>
-      <c r="R7" s="87" t="n">
+      <c r="R7" s="88" t="n">
         <f aca="false">('Balance Sheet'!R6-'Cash Flow'!R23)</f>
         <v>0</v>
       </c>
-      <c r="S7" s="87" t="n">
+      <c r="S7" s="88" t="n">
         <f aca="false">('Balance Sheet'!S6-'Cash Flow'!S23)</f>
         <v>0</v>
       </c>
-      <c r="T7" s="87" t="n">
+      <c r="T7" s="88" t="n">
         <f aca="false">('Balance Sheet'!T6-'Cash Flow'!T23)</f>
         <v>0</v>
       </c>
-      <c r="U7" s="87" t="n">
+      <c r="U7" s="88" t="n">
         <f aca="false">('Balance Sheet'!U6-'Cash Flow'!U23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="B8" s="87" t="n">
+        <v>354</v>
+      </c>
+      <c r="B8" s="88" t="n">
         <f aca="false">('Balance Sheet'!B16-(((0+'Income Statement'!B18)-Schedules!B22)+Drivers!B27))</f>
         <v>1487.52</v>
       </c>
-      <c r="C8" s="87" t="n">
+      <c r="C8" s="88" t="n">
         <f aca="false">('Balance Sheet'!C16-((('Balance Sheet'!B16+'Income Statement'!C18)-Schedules!C22)+Drivers!C27))</f>
         <v>487.3</v>
       </c>
-      <c r="D8" s="87" t="n">
+      <c r="D8" s="88" t="n">
         <f aca="false">('Balance Sheet'!D16-((('Balance Sheet'!C16+'Income Statement'!D18)-Schedules!D22)+Drivers!D27))</f>
         <v>7.88000000000011</v>
       </c>
-      <c r="E8" s="87" t="n">
+      <c r="E8" s="88" t="n">
         <f aca="false">('Balance Sheet'!E16-((('Balance Sheet'!D16+'Income Statement'!E18)-Schedules!E22)+Drivers!E27))</f>
         <v>-529.62</v>
       </c>
-      <c r="F8" s="87" t="n">
+      <c r="F8" s="88" t="n">
         <f aca="false">('Balance Sheet'!F16-((('Balance Sheet'!E16+'Income Statement'!F18)-Schedules!F22)+Drivers!F27))</f>
         <v>51.5699999999997</v>
       </c>
-      <c r="G8" s="87" t="n">
+      <c r="G8" s="88" t="n">
         <f aca="false">('Balance Sheet'!G16-((('Balance Sheet'!F16+'Income Statement'!G18)-Schedules!G22)+Drivers!G27))</f>
         <v>53.0000000000005</v>
       </c>
-      <c r="H8" s="87" t="n">
+      <c r="H8" s="88" t="n">
         <f aca="false">('Balance Sheet'!H16-((('Balance Sheet'!G16+'Income Statement'!H18)-Schedules!H22)+Drivers!H27))</f>
         <v>-316.98</v>
       </c>
-      <c r="I8" s="87" t="n">
+      <c r="I8" s="88" t="n">
         <f aca="false">('Balance Sheet'!I16-((('Balance Sheet'!H16+'Income Statement'!I18)-Schedules!I22)+Drivers!I27))</f>
         <v>2937.93</v>
       </c>
-      <c r="J8" s="87" t="n">
+      <c r="J8" s="88" t="n">
         <f aca="false">('Balance Sheet'!J16-((('Balance Sheet'!I16+'Income Statement'!J18)-Schedules!J22)+Drivers!J27))</f>
         <v>328.940000000001</v>
       </c>
-      <c r="K8" s="87" t="n">
+      <c r="K8" s="88" t="n">
         <f aca="false">('Balance Sheet'!K16-((('Balance Sheet'!J16+'Income Statement'!K18)-Schedules!K22)+Drivers!K27))</f>
         <v>-157.380000000001</v>
       </c>
-      <c r="L8" s="87" t="n">
+      <c r="L8" s="88" t="n">
         <f aca="false">('Balance Sheet'!L16-((('Balance Sheet'!K16+'Income Statement'!L18)-Schedules!L22)+Drivers!L27))</f>
         <v>0</v>
       </c>
-      <c r="M8" s="87" t="n">
+      <c r="M8" s="88" t="n">
         <f aca="false">('Balance Sheet'!M16-((('Balance Sheet'!L16+'Income Statement'!M18)-Schedules!M22)+Drivers!M27))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="87" t="n">
+      <c r="N8" s="88" t="n">
         <f aca="false">('Balance Sheet'!N16-((('Balance Sheet'!M16+'Income Statement'!N18)-Schedules!N22)+Drivers!N27))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="87" t="n">
+      <c r="O8" s="88" t="n">
         <f aca="false">('Balance Sheet'!O16-((('Balance Sheet'!N16+'Income Statement'!O18)-Schedules!O22)+Drivers!O27))</f>
         <v>0</v>
       </c>
-      <c r="P8" s="87" t="n">
+      <c r="P8" s="88" t="n">
         <f aca="false">('Balance Sheet'!P16-((('Balance Sheet'!O16+'Income Statement'!P18)-Schedules!P22)+Drivers!P27))</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="87" t="n">
+      <c r="Q8" s="88" t="n">
         <f aca="false">('Balance Sheet'!Q16-((('Balance Sheet'!P16+'Income Statement'!Q18)-Schedules!Q22)+Drivers!Q27))</f>
         <v>0</v>
       </c>
-      <c r="R8" s="87" t="n">
+      <c r="R8" s="88" t="n">
         <f aca="false">('Balance Sheet'!R16-((('Balance Sheet'!Q16+'Income Statement'!R18)-Schedules!R22)+Drivers!R27))</f>
         <v>0</v>
       </c>
-      <c r="S8" s="87" t="n">
+      <c r="S8" s="88" t="n">
         <f aca="false">('Balance Sheet'!S16-((('Balance Sheet'!R16+'Income Statement'!S18)-Schedules!S22)+Drivers!S27))</f>
         <v>0</v>
       </c>
-      <c r="T8" s="87" t="n">
+      <c r="T8" s="88" t="n">
         <f aca="false">('Balance Sheet'!T16-((('Balance Sheet'!S16+'Income Statement'!T18)-Schedules!T22)+Drivers!T27))</f>
         <v>0</v>
       </c>
-      <c r="U8" s="87" t="n">
+      <c r="U8" s="88" t="n">
         <f aca="false">('Balance Sheet'!U16-((('Balance Sheet'!T16+'Income Statement'!U18)-Schedules!U22)+Drivers!U27))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="B9" s="87" t="n">
+        <v>355</v>
+      </c>
+      <c r="B9" s="88" t="n">
         <f aca="false">('Balance Sheet'!B10-Schedules!B9)</f>
         <v>2812.54</v>
       </c>
-      <c r="C9" s="87" t="n">
+      <c r="C9" s="88" t="n">
         <f aca="false">('Balance Sheet'!C10-Schedules!C9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="87" t="n">
+      <c r="D9" s="88" t="n">
         <f aca="false">('Balance Sheet'!D10-Schedules!D9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="87" t="n">
+      <c r="E9" s="88" t="n">
         <f aca="false">('Balance Sheet'!E10-Schedules!E9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="87" t="n">
+      <c r="F9" s="88" t="n">
         <f aca="false">('Balance Sheet'!F10-Schedules!F9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="87" t="n">
+      <c r="G9" s="88" t="n">
         <f aca="false">('Balance Sheet'!G10-Schedules!G9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="87" t="n">
+      <c r="H9" s="88" t="n">
         <f aca="false">('Balance Sheet'!H10-Schedules!H9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="87" t="n">
+      <c r="I9" s="88" t="n">
         <f aca="false">('Balance Sheet'!I10-Schedules!I9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="87" t="n">
+      <c r="J9" s="88" t="n">
         <f aca="false">('Balance Sheet'!J10-Schedules!J9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="87" t="n">
+      <c r="K9" s="88" t="n">
         <f aca="false">('Balance Sheet'!K10-Schedules!K9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="87" t="n">
+      <c r="L9" s="88" t="n">
         <f aca="false">('Balance Sheet'!L10-Schedules!L9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="87" t="n">
+      <c r="M9" s="88" t="n">
         <f aca="false">('Balance Sheet'!M10-Schedules!M9)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="87" t="n">
+      <c r="N9" s="88" t="n">
         <f aca="false">('Balance Sheet'!N10-Schedules!N9)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="87" t="n">
+      <c r="O9" s="88" t="n">
         <f aca="false">('Balance Sheet'!O10-Schedules!O9)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="87" t="n">
+      <c r="P9" s="88" t="n">
         <f aca="false">('Balance Sheet'!P10-Schedules!P9)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="87" t="n">
+      <c r="Q9" s="88" t="n">
         <f aca="false">('Balance Sheet'!Q10-Schedules!Q9)</f>
         <v>0</v>
       </c>
-      <c r="R9" s="87" t="n">
+      <c r="R9" s="88" t="n">
         <f aca="false">('Balance Sheet'!R10-Schedules!R9)</f>
         <v>0</v>
       </c>
-      <c r="S9" s="87" t="n">
+      <c r="S9" s="88" t="n">
         <f aca="false">('Balance Sheet'!S10-Schedules!S9)</f>
         <v>0</v>
       </c>
-      <c r="T9" s="87" t="n">
+      <c r="T9" s="88" t="n">
         <f aca="false">('Balance Sheet'!T10-Schedules!T9)</f>
         <v>0</v>
       </c>
-      <c r="U9" s="87" t="n">
+      <c r="U9" s="88" t="n">
         <f aca="false">('Balance Sheet'!U10-Schedules!U9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="29"/>
@@ -4869,342 +5003,342 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" s="87" t="n">
+        <v>357</v>
+      </c>
+      <c r="B11" s="88" t="n">
         <f aca="false">('Balance Sheet'!B6-Drivers!B29)</f>
         <v>44.88</v>
       </c>
-      <c r="C11" s="87" t="n">
+      <c r="C11" s="88" t="n">
         <f aca="false">('Balance Sheet'!C6-Drivers!C29)</f>
         <v>328.45</v>
       </c>
-      <c r="D11" s="87" t="n">
+      <c r="D11" s="88" t="n">
         <f aca="false">('Balance Sheet'!D6-Drivers!D29)</f>
         <v>101.76</v>
       </c>
-      <c r="E11" s="87" t="n">
+      <c r="E11" s="88" t="n">
         <f aca="false">('Balance Sheet'!E6-Drivers!E29)</f>
         <v>162.61</v>
       </c>
-      <c r="F11" s="87" t="n">
+      <c r="F11" s="88" t="n">
         <f aca="false">('Balance Sheet'!F6-Drivers!F29)</f>
         <v>314.48</v>
       </c>
-      <c r="G11" s="87" t="n">
+      <c r="G11" s="88" t="n">
         <f aca="false">('Balance Sheet'!G6-Drivers!G29)</f>
         <v>1038.24</v>
       </c>
-      <c r="H11" s="87" t="n">
+      <c r="H11" s="88" t="n">
         <f aca="false">('Balance Sheet'!H6-Drivers!H29)</f>
         <v>1631.64</v>
       </c>
-      <c r="I11" s="87" t="n">
+      <c r="I11" s="88" t="n">
         <f aca="false">('Balance Sheet'!I6-Drivers!I29)</f>
         <v>4090.22</v>
       </c>
-      <c r="J11" s="87" t="n">
+      <c r="J11" s="88" t="n">
         <f aca="false">('Balance Sheet'!J6-Drivers!J29)</f>
         <v>2482.07</v>
       </c>
-      <c r="K11" s="87" t="n">
+      <c r="K11" s="88" t="n">
         <f aca="false">('Balance Sheet'!K6-Drivers!K29)</f>
         <v>2317.7</v>
       </c>
-      <c r="L11" s="87" t="n">
+      <c r="L11" s="88" t="n">
         <f aca="false">('Balance Sheet'!L6-Drivers!L29)</f>
-        <v>3323.8062278758</v>
-      </c>
-      <c r="M11" s="87" t="n">
+        <v>3323.80622844811</v>
+      </c>
+      <c r="M11" s="88" t="n">
         <f aca="false">('Balance Sheet'!M6-Drivers!M29)</f>
-        <v>-5.4688825912308E-007</v>
-      </c>
-      <c r="N11" s="87" t="n">
+        <v>1.55976022142568E-005</v>
+      </c>
+      <c r="N11" s="88" t="n">
         <f aca="false">('Balance Sheet'!N6-Drivers!N29)</f>
-        <v>5.87546423957974E-007</v>
-      </c>
-      <c r="O11" s="87" t="n">
+        <v>4.67905548475756E-005</v>
+      </c>
+      <c r="O11" s="88" t="n">
         <f aca="false">('Balance Sheet'!O6-Drivers!O29)</f>
-        <v>1.15894764576296E-005</v>
-      </c>
-      <c r="P11" s="87" t="n">
+        <v>0.00012698123566679</v>
+      </c>
+      <c r="P11" s="88" t="n">
         <f aca="false">('Balance Sheet'!P6-Drivers!P29)</f>
-        <v>5.70540061062275E-005</v>
-      </c>
-      <c r="Q11" s="87" t="n">
+        <v>0.000294910974957929</v>
+      </c>
+      <c r="Q11" s="88" t="n">
         <f aca="false">('Balance Sheet'!Q6-Drivers!Q29)</f>
-        <v>2827.89134226905</v>
-      </c>
-      <c r="R11" s="87" t="n">
+        <v>2827.89145521328</v>
+      </c>
+      <c r="R11" s="88" t="n">
         <f aca="false">('Balance Sheet'!R6-Drivers!R29)</f>
-        <v>5924.43127893236</v>
-      </c>
-      <c r="S11" s="87" t="n">
+        <v>5924.43149620052</v>
+      </c>
+      <c r="S11" s="88" t="n">
         <f aca="false">('Balance Sheet'!S6-Drivers!S29)</f>
-        <v>9332.1004120394</v>
-      </c>
-      <c r="T11" s="87" t="n">
+        <v>9332.10078483102</v>
+      </c>
+      <c r="T11" s="88" t="n">
         <f aca="false">('Balance Sheet'!T6-Drivers!T29)</f>
-        <v>13072.4154439604</v>
-      </c>
-      <c r="U11" s="87" t="n">
+        <v>13072.4160370738</v>
+      </c>
+      <c r="U11" s="88" t="n">
         <f aca="false">('Balance Sheet'!U6-Drivers!U29)</f>
-        <v>17146.7509122089</v>
+        <v>17146.7518060995</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="B12" s="87" t="n">
+        <v>358</v>
+      </c>
+      <c r="B12" s="88" t="n">
         <f aca="false">'Balance Sheet'!B18</f>
         <v>0</v>
       </c>
-      <c r="C12" s="87" t="n">
+      <c r="C12" s="88" t="n">
         <f aca="false">'Balance Sheet'!C18</f>
         <v>0</v>
       </c>
-      <c r="D12" s="87" t="n">
+      <c r="D12" s="88" t="n">
         <f aca="false">'Balance Sheet'!D18</f>
         <v>0</v>
       </c>
-      <c r="E12" s="87" t="n">
+      <c r="E12" s="88" t="n">
         <f aca="false">'Balance Sheet'!E18</f>
         <v>0</v>
       </c>
-      <c r="F12" s="87" t="n">
+      <c r="F12" s="88" t="n">
         <f aca="false">'Balance Sheet'!F18</f>
         <v>0</v>
       </c>
-      <c r="G12" s="87" t="n">
+      <c r="G12" s="88" t="n">
         <f aca="false">'Balance Sheet'!G18</f>
         <v>0</v>
       </c>
-      <c r="H12" s="87" t="n">
+      <c r="H12" s="88" t="n">
         <f aca="false">'Balance Sheet'!H18</f>
         <v>0</v>
       </c>
-      <c r="I12" s="87" t="n">
+      <c r="I12" s="88" t="n">
         <f aca="false">'Balance Sheet'!I18</f>
         <v>0</v>
       </c>
-      <c r="J12" s="87" t="n">
+      <c r="J12" s="88" t="n">
         <f aca="false">'Balance Sheet'!J18</f>
         <v>0</v>
       </c>
-      <c r="K12" s="87" t="n">
+      <c r="K12" s="88" t="n">
         <f aca="false">'Balance Sheet'!K18</f>
         <v>0</v>
       </c>
-      <c r="L12" s="87" t="n">
+      <c r="L12" s="88" t="n">
         <f aca="false">'Balance Sheet'!L18</f>
         <v>0</v>
       </c>
-      <c r="M12" s="87" t="n">
+      <c r="M12" s="88" t="n">
         <f aca="false">'Balance Sheet'!M18</f>
-        <v>3392.09242289184</v>
-      </c>
-      <c r="N12" s="87" t="n">
+        <v>3392.09243648074</v>
+      </c>
+      <c r="N12" s="88" t="n">
         <f aca="false">'Balance Sheet'!N18</f>
-        <v>4104.81759753617</v>
-      </c>
-      <c r="O12" s="87" t="n">
+        <v>4104.8176354869</v>
+      </c>
+      <c r="O12" s="88" t="n">
         <f aca="false">'Balance Sheet'!O18</f>
-        <v>2535.31701057285</v>
-      </c>
-      <c r="P12" s="87" t="n">
+        <v>2535.31710340578</v>
+      </c>
+      <c r="P12" s="88" t="n">
         <f aca="false">'Balance Sheet'!P18</f>
-        <v>12.1362410026081</v>
-      </c>
-      <c r="Q12" s="87" t="n">
+        <v>12.1364265639545</v>
+      </c>
+      <c r="Q12" s="88" t="n">
         <f aca="false">'Balance Sheet'!Q18</f>
         <v>0</v>
       </c>
-      <c r="R12" s="87" t="n">
+      <c r="R12" s="88" t="n">
         <f aca="false">'Balance Sheet'!R18</f>
         <v>0</v>
       </c>
-      <c r="S12" s="87" t="n">
+      <c r="S12" s="88" t="n">
         <f aca="false">'Balance Sheet'!S18</f>
         <v>0</v>
       </c>
-      <c r="T12" s="87" t="n">
+      <c r="T12" s="88" t="n">
         <f aca="false">'Balance Sheet'!T18</f>
         <v>0</v>
       </c>
-      <c r="U12" s="87" t="n">
+      <c r="U12" s="88" t="n">
         <f aca="false">'Balance Sheet'!U18</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="B13" s="87" t="n">
+        <v>359</v>
+      </c>
+      <c r="B13" s="88" t="n">
         <f aca="false">'Balance Sheet'!B10</f>
         <v>2730.37</v>
       </c>
-      <c r="C13" s="87" t="n">
+      <c r="C13" s="88" t="n">
         <f aca="false">'Balance Sheet'!C10</f>
         <v>3185.89</v>
       </c>
-      <c r="D13" s="87" t="n">
+      <c r="D13" s="88" t="n">
         <f aca="false">'Balance Sheet'!D10</f>
         <v>3256.49</v>
       </c>
-      <c r="E13" s="87" t="n">
+      <c r="E13" s="88" t="n">
         <f aca="false">'Balance Sheet'!E10</f>
         <v>3947.99</v>
       </c>
-      <c r="F13" s="87" t="n">
+      <c r="F13" s="88" t="n">
         <f aca="false">'Balance Sheet'!F10</f>
         <v>4923.98</v>
       </c>
-      <c r="G13" s="87" t="n">
+      <c r="G13" s="88" t="n">
         <f aca="false">'Balance Sheet'!G10</f>
         <v>6133.89</v>
       </c>
-      <c r="H13" s="87" t="n">
+      <c r="H13" s="88" t="n">
         <f aca="false">'Balance Sheet'!H10</f>
         <v>5974.55</v>
       </c>
-      <c r="I13" s="87" t="n">
+      <c r="I13" s="88" t="n">
         <f aca="false">'Balance Sheet'!I10</f>
         <v>7757.46</v>
       </c>
-      <c r="J13" s="87" t="n">
+      <c r="J13" s="88" t="n">
         <f aca="false">'Balance Sheet'!J10</f>
         <v>9522.93</v>
       </c>
-      <c r="K13" s="87" t="n">
+      <c r="K13" s="88" t="n">
         <f aca="false">'Balance Sheet'!K10</f>
         <v>10527.09</v>
       </c>
-      <c r="L13" s="87" t="n">
+      <c r="L13" s="88" t="n">
         <f aca="false">'Balance Sheet'!L10</f>
         <v>17797.87772343</v>
       </c>
-      <c r="M13" s="87" t="n">
+      <c r="M13" s="88" t="n">
         <f aca="false">'Balance Sheet'!M10</f>
         <v>25063.7157652637</v>
       </c>
-      <c r="N13" s="87" t="n">
+      <c r="N13" s="88" t="n">
         <f aca="false">'Balance Sheet'!N10</f>
         <v>26829.0585332768</v>
       </c>
-      <c r="O13" s="87" t="n">
+      <c r="O13" s="88" t="n">
         <f aca="false">'Balance Sheet'!O10</f>
         <v>26970.2814941649</v>
       </c>
-      <c r="P13" s="87" t="n">
+      <c r="P13" s="88" t="n">
         <f aca="false">'Balance Sheet'!P10</f>
         <v>26916.8904837743</v>
       </c>
-      <c r="Q13" s="87" t="n">
+      <c r="Q13" s="88" t="n">
         <f aca="false">'Balance Sheet'!Q10</f>
         <v>27008.5783108577</v>
       </c>
-      <c r="R13" s="87" t="n">
+      <c r="R13" s="88" t="n">
         <f aca="false">'Balance Sheet'!R10</f>
         <v>27271.7298212504</v>
       </c>
-      <c r="S13" s="87" t="n">
+      <c r="S13" s="88" t="n">
         <f aca="false">'Balance Sheet'!S10</f>
         <v>27669.4211544973</v>
       </c>
-      <c r="T13" s="87" t="n">
+      <c r="T13" s="88" t="n">
         <f aca="false">'Balance Sheet'!T10</f>
         <v>28213.4856872016</v>
       </c>
-      <c r="U13" s="87" t="n">
+      <c r="U13" s="88" t="n">
         <f aca="false">'Balance Sheet'!U10</f>
         <v>28886.6293802962</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B14" s="87" t="n">
+        <v>256</v>
+      </c>
+      <c r="B14" s="88" t="n">
         <f aca="false">Schedules!B24</f>
         <v>1854.23</v>
       </c>
-      <c r="C14" s="87" t="n">
+      <c r="C14" s="88" t="n">
         <f aca="false">Schedules!C24</f>
         <v>2613.07</v>
       </c>
-      <c r="D14" s="87" t="n">
+      <c r="D14" s="88" t="n">
         <f aca="false">Schedules!D24</f>
         <v>2887.67</v>
       </c>
-      <c r="E14" s="87" t="n">
+      <c r="E14" s="88" t="n">
         <f aca="false">Schedules!E24</f>
         <v>2548.22</v>
       </c>
-      <c r="F14" s="87" t="n">
+      <c r="F14" s="88" t="n">
         <f aca="false">Schedules!F24</f>
         <v>2891.17</v>
       </c>
-      <c r="G14" s="87" t="n">
+      <c r="G14" s="88" t="n">
         <f aca="false">Schedules!G24</f>
         <v>3272.12</v>
       </c>
-      <c r="H14" s="87" t="n">
+      <c r="H14" s="88" t="n">
         <f aca="false">Schedules!H24</f>
         <v>3994.62</v>
       </c>
-      <c r="I14" s="87" t="n">
+      <c r="I14" s="88" t="n">
         <f aca="false">Schedules!I24</f>
         <v>8026.36</v>
       </c>
-      <c r="J14" s="87" t="n">
+      <c r="J14" s="88" t="n">
         <f aca="false">Schedules!J24</f>
         <v>9696.9</v>
       </c>
-      <c r="K14" s="87" t="n">
+      <c r="K14" s="88" t="n">
         <f aca="false">Schedules!K24</f>
         <v>10877.5</v>
       </c>
-      <c r="L14" s="87" t="n">
+      <c r="L14" s="88" t="n">
         <f aca="false">Schedules!L24</f>
-        <v>18775.8139158509</v>
-      </c>
-      <c r="M14" s="87" t="n">
+        <v>18775.813915891</v>
+      </c>
+      <c r="M14" s="88" t="n">
         <f aca="false">Schedules!M24</f>
-        <v>20841.5636506175</v>
-      </c>
-      <c r="N14" s="87" t="n">
+        <v>20841.5636526408</v>
+      </c>
+      <c r="N14" s="88" t="n">
         <f aca="false">Schedules!N24</f>
-        <v>22981.2544477567</v>
-      </c>
-      <c r="O14" s="87" t="n">
+        <v>22981.2544554766</v>
+      </c>
+      <c r="O14" s="88" t="n">
         <f aca="false">Schedules!O24</f>
-        <v>25583.3586238277</v>
-      </c>
-      <c r="P14" s="87" t="n">
+        <v>25583.3586458543</v>
+      </c>
+      <c r="P14" s="88" t="n">
         <f aca="false">Schedules!P24</f>
-        <v>28604.4102272199</v>
-      </c>
-      <c r="Q14" s="87" t="n">
+        <v>28604.4102789833</v>
+      </c>
+      <c r="Q14" s="88" t="n">
         <f aca="false">Schedules!Q24</f>
-        <v>32076.4814090676</v>
-      </c>
-      <c r="R14" s="87" t="n">
+        <v>32076.4815214796</v>
+      </c>
+      <c r="R14" s="88" t="n">
         <f aca="false">Schedules!R24</f>
-        <v>35985.8606869898</v>
-      </c>
-      <c r="S14" s="87" t="n">
+        <v>35985.8609037257</v>
+      </c>
+      <c r="S14" s="88" t="n">
         <f aca="false">Schedules!S24</f>
-        <v>40352.9633609879</v>
-      </c>
-      <c r="T14" s="87" t="n">
+        <v>40352.9637332472</v>
+      </c>
+      <c r="T14" s="88" t="n">
         <f aca="false">Schedules!T24</f>
-        <v>45199.3895338186</v>
-      </c>
-      <c r="U14" s="87" t="n">
+        <v>45199.3901263997</v>
+      </c>
+      <c r="U14" s="88" t="n">
         <f aca="false">Schedules!U24</f>
-        <v>50538.4564135213</v>
+        <v>50538.4573068796</v>
       </c>
     </row>
   </sheetData>
@@ -5230,7 +5364,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
@@ -5239,146 +5373,146 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="0" t="s">
         <v>56</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="0" t="n">
         <v>2937.93</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="0" t="n">
         <v>0</v>
@@ -5389,10 +5523,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>1070.87</v>
@@ -5403,10 +5537,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>0</v>
@@ -5417,24 +5551,24 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>17797.8747</v>
@@ -5445,10 +5579,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>18775.812</v>
@@ -5459,99 +5593,99 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="0" t="s">
         <v>72</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>5</v>
@@ -5568,103 +5702,118 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -5693,44 +5842,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>5</v>
@@ -5742,33 +5891,33 @@
         <v>7</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="T4" s="27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="U4" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
@@ -5878,7 +6027,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">(IFERROR(('Income Statement'!B6)/(0),0)-1)</f>
@@ -6048,7 +6197,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B10)/('Income Statement'!B6),0)</f>
@@ -6133,7 +6282,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">'Income Statement'!B12</f>
@@ -6262,48 +6411,48 @@
       </c>
       <c r="L11" s="34" t="n">
         <f aca="false">'Income Statement'!L18</f>
-        <v>1526.49308622419</v>
+        <v>1526.49308623925</v>
       </c>
       <c r="M11" s="34" t="n">
         <f aca="false">'Income Statement'!M18</f>
-        <v>2347.44288049106</v>
+        <v>2347.44288054327</v>
       </c>
       <c r="N11" s="34" t="n">
         <f aca="false">'Income Statement'!N18</f>
-        <v>2431.46681485079</v>
+        <v>2431.46681502389</v>
       </c>
       <c r="O11" s="34" t="n">
         <f aca="false">'Income Statement'!O18</f>
-        <v>2956.93656213672</v>
+        <v>2956.93656265893</v>
       </c>
       <c r="P11" s="34" t="n">
         <f aca="false">'Income Statement'!P18</f>
-        <v>3433.01317789291</v>
+        <v>3433.01317924968</v>
       </c>
       <c r="Q11" s="34" t="n">
         <f aca="false">'Income Statement'!Q18</f>
-        <v>3945.53539697909</v>
+        <v>3945.5354008047</v>
       </c>
       <c r="R11" s="34" t="n">
         <f aca="false">'Income Statement'!R18</f>
-        <v>4442.47635107271</v>
+        <v>4442.47635944327</v>
       </c>
       <c r="S11" s="34" t="n">
         <f aca="false">'Income Statement'!S18</f>
-        <v>4962.61647082813</v>
+        <v>4962.61648578567</v>
       </c>
       <c r="T11" s="34" t="n">
         <f aca="false">'Income Statement'!T18</f>
-        <v>5507.30210845641</v>
+        <v>5507.30213294144</v>
       </c>
       <c r="U11" s="34" t="n">
         <f aca="false">'Income Statement'!U18</f>
-        <v>6067.12086876619</v>
+        <v>6067.12090646413</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B12" s="35" t="n">
         <f aca="false">'Income Statement'!B19</f>
@@ -6347,48 +6496,48 @@
       </c>
       <c r="L12" s="36" t="n">
         <f aca="false">'Income Statement'!L19</f>
-        <v>6.56980024198059</v>
+        <v>6.56980024204542</v>
       </c>
       <c r="M12" s="36" t="n">
         <f aca="false">'Income Statement'!M19</f>
-        <v>10.1030466128301</v>
+        <v>10.1030466130547</v>
       </c>
       <c r="N12" s="36" t="n">
         <f aca="false">'Income Statement'!N19</f>
-        <v>10.4646731863602</v>
+        <v>10.4646731871052</v>
       </c>
       <c r="O12" s="36" t="n">
         <f aca="false">'Income Statement'!O19</f>
-        <v>12.7262171815654</v>
+        <v>12.7262171838129</v>
       </c>
       <c r="P12" s="36" t="n">
         <f aca="false">'Income Statement'!P19</f>
-        <v>14.7751804514436</v>
+        <v>14.7751804572829</v>
       </c>
       <c r="Q12" s="36" t="n">
         <f aca="false">'Income Statement'!Q19</f>
-        <v>16.981000202191</v>
+        <v>16.9810002186559</v>
       </c>
       <c r="R12" s="36" t="n">
         <f aca="false">'Income Statement'!R19</f>
-        <v>19.1197604952559</v>
+        <v>19.1197605312816</v>
       </c>
       <c r="S12" s="36" t="n">
         <f aca="false">'Income Statement'!S19</f>
-        <v>21.3583665626345</v>
+        <v>21.3583666270096</v>
       </c>
       <c r="T12" s="36" t="n">
         <f aca="false">'Income Statement'!T19</f>
-        <v>23.7026129049125</v>
+        <v>23.7026130102924</v>
       </c>
       <c r="U12" s="36" t="n">
         <f aca="false">'Income Statement'!U19</f>
-        <v>26.1119899667148</v>
+        <v>26.1119901289612</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
@@ -6413,7 +6562,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">(((('Income Statement'!B12*(1-Drivers!B22))+'Income Statement'!B11)-Schedules!B7)-Schedules!B12)</f>
@@ -6498,7 +6647,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">(((('Income Statement'!B18+'Income Statement'!B11)-Schedules!B7)-Schedules!B12)+('Balance Sheet'!B19-0))</f>
@@ -6542,48 +6691,48 @@
       </c>
       <c r="L15" s="34" t="n">
         <f aca="false">(((('Income Statement'!L18+'Income Statement'!L11)-Schedules!L7)-Schedules!L12)+('Balance Sheet'!L19-'Balance Sheet'!K19))</f>
-        <v>-5254.92116315095</v>
+        <v>-5254.92116313589</v>
       </c>
       <c r="M15" s="34" t="n">
         <f aca="false">(((('Income Statement'!M18+'Income Statement'!M11)-Schedules!M7)-Schedules!M12)+('Balance Sheet'!M19-'Balance Sheet'!L19))</f>
-        <v>-2033.43937318432</v>
+        <v>-2033.43935954321</v>
       </c>
       <c r="N15" s="34" t="n">
         <f aca="false">(((('Income Statement'!N18+'Income Statement'!N11)-Schedules!N7)-Schedules!N12)+('Balance Sheet'!N19-'Balance Sheet'!M19))</f>
-        <v>1030.10089430503</v>
+        <v>1030.10091883996</v>
       </c>
       <c r="O15" s="34" t="n">
         <f aca="false">(((('Income Statement'!O18+'Income Statement'!O11)-Schedules!O7)-Schedules!O12)+('Balance Sheet'!O19-'Balance Sheet'!N19))</f>
-        <v>961.767200603523</v>
+        <v>961.767256007925</v>
       </c>
       <c r="P15" s="34" t="n">
         <f aca="false">(((('Income Statement'!P18+'Income Statement'!P11)-Schedules!P7)-Schedules!P12)+('Balance Sheet'!P19-'Balance Sheet'!O19))</f>
-        <v>794.451933153538</v>
+        <v>794.452027238724</v>
       </c>
       <c r="Q15" s="34" t="n">
         <f aca="false">(((('Income Statement'!Q18+'Income Statement'!Q11)-Schedules!Q7)-Schedules!Q12)+('Balance Sheet'!Q19-'Balance Sheet'!P19))</f>
-        <v>3651.83723731112</v>
+        <v>3651.83705557539</v>
       </c>
       <c r="R15" s="34" t="n">
         <f aca="false">(((('Income Statement'!R18+'Income Statement'!R11)-Schedules!R7)-Schedules!R12)+('Balance Sheet'!R19-'Balance Sheet'!Q19))</f>
-        <v>3987.27663126403</v>
+        <v>3987.27663963459</v>
       </c>
       <c r="S15" s="34" t="n">
         <f aca="false">(((('Income Statement'!S18+'Income Statement'!S11)-Schedules!S7)-Schedules!S12)+('Balance Sheet'!S19-'Balance Sheet'!R19))</f>
-        <v>4368.48724245516</v>
+        <v>4368.4872574127</v>
       </c>
       <c r="T15" s="34" t="n">
         <f aca="false">(((('Income Statement'!T18+'Income Statement'!T11)-Schedules!T7)-Schedules!T12)+('Balance Sheet'!T19-'Balance Sheet'!S19))</f>
-        <v>4769.56866106387</v>
+        <v>4769.5686855489</v>
       </c>
       <c r="U15" s="34" t="n">
         <f aca="false">(((('Income Statement'!U18+'Income Statement'!U11)-Schedules!U7)-Schedules!U12)+('Balance Sheet'!U19-'Balance Sheet'!T19))</f>
-        <v>5191.0370875969</v>
+        <v>5191.03712529483</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">IFERROR((B14)/('Income Statement'!B10),0)</f>
@@ -6668,7 +6817,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B17" s="29"/>
       <c r="C17" s="29"/>
@@ -6693,7 +6842,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">(('Balance Sheet'!B19-'Balance Sheet'!B6)-'Balance Sheet'!B12)</f>
@@ -6737,48 +6886,48 @@
       </c>
       <c r="L18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!L19-'Balance Sheet'!L6)-'Balance Sheet'!L12)</f>
-        <v>2549.7537721242</v>
+        <v>2549.75377155189</v>
       </c>
       <c r="M18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!M19-'Balance Sheet'!M6)-'Balance Sheet'!M12)</f>
-        <v>9265.65242343873</v>
+        <v>9265.65242088314</v>
       </c>
       <c r="N18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!N19-'Balance Sheet'!N6)-'Balance Sheet'!N12)</f>
-        <v>9978.37759694863</v>
+        <v>9978.37758869635</v>
       </c>
       <c r="O18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!O19-'Balance Sheet'!O6)-'Balance Sheet'!O12)</f>
-        <v>8398.87699898338</v>
+        <v>8398.87697642454</v>
       </c>
       <c r="P18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!P19-'Balance Sheet'!P6)-'Balance Sheet'!P12)</f>
-        <v>5860.6961839486</v>
+        <v>5860.69613165298</v>
       </c>
       <c r="Q18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!Q19-'Balance Sheet'!Q6)-'Balance Sheet'!Q12)</f>
-        <v>3005.66865773095</v>
+        <v>3005.66854478672</v>
       </c>
       <c r="R18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!R19-'Balance Sheet'!R6)-'Balance Sheet'!R12)</f>
-        <v>-105.871278932358</v>
+        <v>-105.871496200515</v>
       </c>
       <c r="S18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!S19-'Balance Sheet'!S6)-'Balance Sheet'!S12)</f>
-        <v>-3528.5404120394</v>
+        <v>-3528.54078483102</v>
       </c>
       <c r="T18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!T19-'Balance Sheet'!T6)-'Balance Sheet'!T12)</f>
-        <v>-7278.8554439604</v>
+        <v>-7278.8560370738</v>
       </c>
       <c r="U18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!U19-'Balance Sheet'!U6)-'Balance Sheet'!U12)</f>
-        <v>-11363.1909122089</v>
+        <v>-11363.1918060995</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B19" s="37" t="n">
         <f aca="false">IFERROR((B18)/('Income Statement'!B10),0)</f>
@@ -6822,48 +6971,48 @@
       </c>
       <c r="L19" s="38" t="n">
         <f aca="false">IFERROR((L18)/('Income Statement'!L10),0)</f>
-        <v>0.886121531715689</v>
+        <v>0.886121531516793</v>
       </c>
       <c r="M19" s="38" t="n">
         <f aca="false">IFERROR((M18)/('Income Statement'!M10),0)</f>
-        <v>2.03105161794384</v>
+        <v>2.03105161738365</v>
       </c>
       <c r="N19" s="38" t="n">
         <f aca="false">IFERROR((N18)/('Income Statement'!N10),0)</f>
-        <v>1.84764584772792</v>
+        <v>1.84764584619988</v>
       </c>
       <c r="O19" s="38" t="n">
         <f aca="false">IFERROR((O18)/('Income Statement'!O10),0)</f>
-        <v>1.36653355587151</v>
+        <v>1.36653355220109</v>
       </c>
       <c r="P19" s="38" t="n">
         <f aca="false">IFERROR((P18)/('Income Statement'!P10),0)</f>
-        <v>0.88672013470673</v>
+        <v>0.886720126794431</v>
       </c>
       <c r="Q19" s="38" t="n">
         <f aca="false">IFERROR((Q18)/('Income Statement'!Q10),0)</f>
-        <v>0.425164573535171</v>
+        <v>0.425164557558731</v>
       </c>
       <c r="R19" s="38" t="n">
         <f aca="false">IFERROR((R18)/('Income Statement'!R10),0)</f>
-        <v>-0.0141030882699507</v>
+        <v>-0.014103117212191</v>
       </c>
       <c r="S19" s="38" t="n">
         <f aca="false">IFERROR((S18)/('Income Statement'!S10),0)</f>
-        <v>-0.442869611259771</v>
+        <v>-0.442869658049112</v>
       </c>
       <c r="T19" s="38" t="n">
         <f aca="false">IFERROR((T18)/('Income Statement'!T10),0)</f>
-        <v>-0.861618704565247</v>
+        <v>-0.861618774773757</v>
       </c>
       <c r="U19" s="38" t="n">
         <f aca="false">IFERROR((U18)/('Income Statement'!U10),0)</f>
-        <v>-1.2716613653451</v>
+        <v>-1.27166146538092</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B20" s="37" t="n">
         <f aca="false">IFERROR(('Income Statement'!B12)/('Income Statement'!B14),0)</f>
@@ -6911,23 +7060,23 @@
       </c>
       <c r="M20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!M12)/('Income Statement'!M14),0)</f>
-        <v>5.53150558757212</v>
+        <v>5.53150558319938</v>
       </c>
       <c r="N20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!N12)/('Income Statement'!N14),0)</f>
-        <v>4.91448742950511</v>
+        <v>4.91448741761059</v>
       </c>
       <c r="O20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!O12)/('Income Statement'!O14),0)</f>
-        <v>5.99455171898007</v>
+        <v>5.99455168060185</v>
       </c>
       <c r="P20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!P12)/('Income Statement'!P14),0)</f>
-        <v>8.30234461451502</v>
+        <v>8.30234447280542</v>
       </c>
       <c r="Q20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!Q12)/('Income Statement'!Q14),0)</f>
-        <v>10.8157860366612</v>
+        <v>10.8157858906448</v>
       </c>
       <c r="R20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!R12)/('Income Statement'!R14),0)</f>
@@ -6948,7 +7097,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">((('Balance Sheet'!B15+'Balance Sheet'!B16)+'Balance Sheet'!B19)-'Balance Sheet'!B6)</f>
@@ -6992,48 +7141,48 @@
       </c>
       <c r="L21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!L15+'Balance Sheet'!L16)+'Balance Sheet'!L19)-'Balance Sheet'!L6)</f>
-        <v>21350.9276879751</v>
+        <v>21350.9276874429</v>
       </c>
       <c r="M21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!M15+'Balance Sheet'!M16)+'Balance Sheet'!M19)-'Balance Sheet'!M6)</f>
-        <v>30132.5760740562</v>
+        <v>30132.5760735239</v>
       </c>
       <c r="N21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!N15+'Balance Sheet'!N16)+'Balance Sheet'!N19)-'Balance Sheet'!N6)</f>
-        <v>32984.9920447053</v>
+        <v>32984.992044173</v>
       </c>
       <c r="O21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!O15+'Balance Sheet'!O16)+'Balance Sheet'!O19)-'Balance Sheet'!O6)</f>
-        <v>34007.5956228111</v>
+        <v>34007.5956222788</v>
       </c>
       <c r="P21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!P15+'Balance Sheet'!P16)+'Balance Sheet'!P19)-'Balance Sheet'!P6)</f>
-        <v>34490.4664111685</v>
+        <v>34490.4664106363</v>
       </c>
       <c r="Q21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!Q15+'Balance Sheet'!Q16)+'Balance Sheet'!Q19)-'Balance Sheet'!Q6)</f>
-        <v>35107.5100667986</v>
+        <v>35107.5100662663</v>
       </c>
       <c r="R21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!R15+'Balance Sheet'!R16)+'Balance Sheet'!R19)-'Balance Sheet'!R6)</f>
-        <v>35905.3494080574</v>
+        <v>35905.3494075252</v>
       </c>
       <c r="S21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!S15+'Balance Sheet'!S16)+'Balance Sheet'!S19)-'Balance Sheet'!S6)</f>
-        <v>36849.7829489485</v>
+        <v>36849.7829484162</v>
       </c>
       <c r="T21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!T15+'Balance Sheet'!T16)+'Balance Sheet'!T19)-'Balance Sheet'!T6)</f>
-        <v>37945.8940898582</v>
+        <v>37945.8940893259</v>
       </c>
       <c r="U21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!U15+'Balance Sheet'!U16)+'Balance Sheet'!U19)-'Balance Sheet'!U6)</f>
-        <v>39200.6255013123</v>
+        <v>39200.62550078</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">IFERROR((('Income Statement'!B12*(1-Drivers!B22)))/(AVERAGE(0,B21)),0)</f>
@@ -7077,48 +7226,48 @@
       </c>
       <c r="L22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!L12*(1-Drivers!L22)))/(AVERAGE(K21,L21)),0)</f>
-        <v>0.0910138606188624</v>
+        <v>0.0910138606201785</v>
       </c>
       <c r="M22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!M12*(1-Drivers!M22)))/(AVERAGE(L21,M21)),0)</f>
-        <v>0.100842144305001</v>
+        <v>0.100842144307087</v>
       </c>
       <c r="N22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!N12*(1-Drivers!N22)))/(AVERAGE(M21,N21)),0)</f>
-        <v>0.0905301333485183</v>
+        <v>0.0905301333500452</v>
       </c>
       <c r="O22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!O12*(1-Drivers!O22)))/(AVERAGE(N21,O21)),0)</f>
-        <v>0.0998039914458886</v>
+        <v>0.0998039914474745</v>
       </c>
       <c r="P22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!P12*(1-Drivers!P22)))/(AVERAGE(O21,P21)),0)</f>
-        <v>0.107938625618455</v>
+        <v>0.107938625620133</v>
       </c>
       <c r="Q22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!Q12*(1-Drivers!Q22)))/(AVERAGE(P21,Q21)),0)</f>
-        <v>0.116626733096488</v>
+        <v>0.116626733098272</v>
       </c>
       <c r="R22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!R12*(1-Drivers!R22)))/(AVERAGE(Q21,R21)),0)</f>
-        <v>0.123775037224323</v>
+        <v>0.123775037226179</v>
       </c>
       <c r="S22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!S12*(1-Drivers!S22)))/(AVERAGE(R21,S21)),0)</f>
-        <v>0.130293517446166</v>
+        <v>0.130293517448073</v>
       </c>
       <c r="T22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!T12*(1-Drivers!T22)))/(AVERAGE(S21,T21)),0)</f>
-        <v>0.136184205844232</v>
+        <v>0.13618420584617</v>
       </c>
       <c r="U22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!U12*(1-Drivers!U22)))/(AVERAGE(T21,U21)),0)</f>
-        <v>0.141135906443221</v>
+        <v>0.141135906445169</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B23" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B18)/(AVERAGE(0,Schedules!B24)),0)</f>
@@ -7162,43 +7311,43 @@
       </c>
       <c r="L23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!L18)/(AVERAGE(Schedules!K24,Schedules!L24)),0)</f>
-        <v>0.10295598600251</v>
+        <v>0.102955986003387</v>
       </c>
       <c r="M23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!M18)/(AVERAGE(Schedules!L24,Schedules!M24)),0)</f>
-        <v>0.118505717676675</v>
+        <v>0.118505717673138</v>
       </c>
       <c r="N23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!N18)/(AVERAGE(Schedules!M24,Schedules!N24)),0)</f>
-        <v>0.110968071902295</v>
+        <v>0.110968071885523</v>
       </c>
       <c r="O23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!O18)/(AVERAGE(Schedules!N24,Schedules!O24)),0)</f>
-        <v>0.121773298503509</v>
+        <v>0.121773298450426</v>
       </c>
       <c r="P23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!P18)/(AVERAGE(Schedules!O24,Schedules!P24)),0)</f>
-        <v>0.126708046877872</v>
+        <v>0.126708046755404</v>
       </c>
       <c r="Q23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!Q18)/(AVERAGE(Schedules!P24,Schedules!Q24)),0)</f>
-        <v>0.130042103554709</v>
+        <v>0.130042103328963</v>
       </c>
       <c r="R23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!R18)/(AVERAGE(Schedules!Q24,Schedules!R24)),0)</f>
-        <v>0.130541389386894</v>
+        <v>0.130541389001566</v>
       </c>
       <c r="S23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!S18)/(AVERAGE(Schedules!R24,Schedules!S24)),0)</f>
-        <v>0.130015533582472</v>
+        <v>0.130015532971204</v>
       </c>
       <c r="T23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!T18)/(AVERAGE(Schedules!S24,Schedules!T24)),0)</f>
-        <v>0.12874694668487</v>
+        <v>0.128746945805289</v>
       </c>
       <c r="U23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!U18)/(AVERAGE(Schedules!T24,Schedules!U24)),0)</f>
-        <v>0.126744461581126</v>
+        <v>0.12674446040146</v>
       </c>
     </row>
   </sheetData>
@@ -7227,17 +7376,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B4" s="39" t="n">
         <v>1</v>
@@ -7245,7 +7394,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B5" s="40" t="str">
         <f aca="false">CHOOSE($B$4,"Base","Bull","Bear")</f>
@@ -7254,7 +7403,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>6</v>
@@ -7263,38 +7412,38 @@
         <v>7</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="41" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B9" s="42" t="n">
         <v>0.19</v>
@@ -7329,7 +7478,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B10" s="42" t="n">
         <v>0.451</v>
@@ -7364,7 +7513,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B11" s="42" t="n">
         <v>0.451</v>
@@ -7399,7 +7548,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B12" s="42" t="n">
         <v>1.254</v>
@@ -7434,7 +7583,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="42" t="n">
         <v>0.04</v>
@@ -7442,7 +7591,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B14" s="43" t="n">
         <v>0.5</v>
@@ -7450,12 +7599,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="41" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B17" s="42" t="n">
         <v>0.278</v>
@@ -7490,7 +7639,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B18" s="42" t="n">
         <v>0.451</v>
@@ -7525,7 +7674,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B19" s="42" t="n">
         <v>0.451</v>
@@ -7560,7 +7709,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B20" s="42" t="n">
         <v>1.168</v>
@@ -7595,7 +7744,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" s="42" t="n">
         <v>0.045</v>
@@ -7603,7 +7752,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B22" s="43" t="n">
         <v>0.25</v>
@@ -7611,17 +7760,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="44" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="41" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B26" s="42" t="n">
         <v>0.15</v>
@@ -7656,7 +7805,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B27" s="42" t="n">
         <v>0.44</v>
@@ -7691,7 +7840,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B28" s="42" t="n">
         <v>0.44</v>
@@ -7726,7 +7875,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B29" s="42" t="n">
         <v>1.254</v>
@@ -7761,7 +7910,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30" s="42" t="n">
         <v>0.03</v>
@@ -7769,7 +7918,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B31" s="43" t="n">
         <v>0.25</v>
@@ -7777,17 +7926,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="44" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="41" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B35" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B9,B17,B26)</f>
@@ -7832,7 +7981,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B36" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B10,B18,B27)</f>
@@ -7877,7 +8026,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B37" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B11,B19,B28)</f>
@@ -7922,7 +8071,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B38" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B12,B20,B29)</f>
@@ -7967,7 +8116,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" s="15" t="n">
         <f aca="false">CHOOSE(Scenarios!$B$4,B13,B21,B30)</f>
@@ -7976,74 +8125,74 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="41" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B43" s="45" t="n">
         <f aca="false">B14</f>
         <v>0.5</v>
       </c>
       <c r="C43" s="46" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D43" s="47" t="n">
         <f aca="false">B43*C43</f>
-        <v>60.5</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B44" s="45" t="n">
         <f aca="false">B22</f>
         <v>0.25</v>
       </c>
       <c r="C44" s="46" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D44" s="47" t="n">
         <f aca="false">B44*C44</f>
-        <v>32.25</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B45" s="45" t="n">
         <f aca="false">B31</f>
         <v>0.25</v>
       </c>
       <c r="C45" s="46" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D45" s="47" t="n">
         <f aca="false">B45*C45</f>
-        <v>14.5</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B46" s="45" t="n">
         <f aca="false">SUM(B43:B45)</f>
@@ -8051,30 +8200,30 @@
       </c>
       <c r="D46" s="48" t="n">
         <f aca="false">SUM(D43:D45)</f>
-        <v>107.25</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B48" s="49" t="n">
-        <f aca="false">DCF!B43</f>
-        <v>121.083756994038</v>
+        <f aca="false">DCF!B45</f>
+        <v>115.301507056065</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B49" s="47" t="n">
         <f aca="false">INDEX(C43:C45,Scenarios!$B$4)</f>
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B50" s="48" t="n">
         <f aca="false">ROUND(B48,0)-B49</f>
@@ -8113,44 +8262,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>5</v>
@@ -8162,33 +8311,33 @@
         <v>7</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="T4" s="27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="U4" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
@@ -8213,7 +8362,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B6" s="19" t="n">
         <f aca="false">(IFERROR(('Income Statement'!B6)/(0),0)-1)</f>
@@ -8298,7 +8447,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B7" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B8)/('Income Statement'!B6),0)</f>
@@ -8383,7 +8532,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B10)/('Income Statement'!B6),0)</f>
@@ -8468,7 +8617,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B13)/('Income Statement'!B6),0)</f>
@@ -8543,7 +8692,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="29"/>
@@ -8568,7 +8717,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">IFERROR((Schedules!B7)/('Income Statement'!B6),0)</f>
@@ -8653,7 +8802,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B12" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B11)/(0),0)</f>
@@ -8728,7 +8877,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B13" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B11)/('Income Statement'!B6),0)</f>
@@ -8803,7 +8952,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!B11)/('Income Statement'!B6),0)</f>
@@ -8878,7 +9027,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B15" s="29"/>
       <c r="C15" s="29"/>
@@ -8903,7 +9052,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B16" s="51" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B7)/('Income Statement'!B6),0)*365)</f>
@@ -8978,7 +9127,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B17" s="51" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B8)/('Income Statement'!B7),0)*365)</f>
@@ -9053,7 +9202,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B18" s="51" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B20)/('Income Statement'!B7),0)*365)</f>
@@ -9128,7 +9277,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B19" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!B9)/('Income Statement'!B6),0)</f>
@@ -9203,7 +9352,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B20" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!B21)/('Income Statement'!B6),0)</f>
@@ -9278,7 +9427,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -9303,7 +9452,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B17)/('Income Statement'!B16),0)</f>
@@ -9378,7 +9527,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B23" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!B14)/(AVERAGE(0,'Balance Sheet'!B19)),0)</f>
@@ -9453,7 +9602,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="32" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B24" s="15" t="n">
         <f aca="false">0</f>
@@ -9528,7 +9677,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B25" s="19" t="n">
         <f aca="false">(IFERROR(('Balance Sheet'!B17)/(0),0)-1)</f>
@@ -9603,7 +9752,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B26" s="53" t="n">
         <f aca="false">0</f>
@@ -9678,7 +9827,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B27" s="53" t="n">
         <f aca="false">0</f>
@@ -9753,7 +9902,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B28" s="19" t="n">
         <f aca="false">IFERROR((Schedules!B22)/('Income Statement'!B18),0)</f>
@@ -9828,7 +9977,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="32" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B29" s="53" t="n">
         <f aca="false">0</f>
@@ -9927,44 +10076,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>5</v>
@@ -9976,33 +10125,33 @@
         <v>7</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="T4" s="27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="U4" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
@@ -10102,7 +10251,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B7" s="56" t="n">
         <v>139</v>
@@ -10177,7 +10326,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B8" s="57" t="n">
         <f aca="false">(B6-B7)</f>
@@ -10262,7 +10411,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B9" s="53" t="n">
         <f aca="false">(B8-B10)</f>
@@ -10422,7 +10571,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B11" s="56" t="n">
         <v>82.17</v>
@@ -10497,7 +10646,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B12" s="62" t="n">
         <f aca="false">(B10-B11)</f>
@@ -10582,7 +10731,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B13" s="56" t="n">
         <v>57.01</v>
@@ -10616,48 +10765,48 @@
       </c>
       <c r="L13" s="34" t="n">
         <f aca="false">((L6*Drivers!L9)+(Drivers!L24*AVERAGE('Balance Sheet'!K6,'Balance Sheet'!L6)))</f>
-        <v>292.41031560614</v>
+        <v>292.410315624448</v>
       </c>
       <c r="M13" s="34" t="n">
         <f aca="false">((M6*Drivers!M9)+(Drivers!M24*AVERAGE('Balance Sheet'!L6,'Balance Sheet'!M6)))</f>
-        <v>283.172535624469</v>
+        <v>283.172536167008</v>
       </c>
       <c r="N13" s="34" t="n">
         <f aca="false">((N6*Drivers!N9)+(Drivers!N24*AVERAGE('Balance Sheet'!M6,'Balance Sheet'!N6)))</f>
-        <v>199.734052814929</v>
+        <v>199.734054840742</v>
       </c>
       <c r="O13" s="34" t="n">
         <f aca="false">((O6*Drivers!O9)+(Drivers!O24*AVERAGE('Balance Sheet'!N6,'Balance Sheet'!O6)))</f>
-        <v>219.944161131642</v>
+        <v>219.944166383775</v>
       </c>
       <c r="P13" s="34" t="n">
         <f aca="false">((P6*Drivers!P9)+(Drivers!P24*AVERAGE('Balance Sheet'!O6,'Balance Sheet'!P6)))</f>
-        <v>232.680572978458</v>
+        <v>232.680584460008</v>
       </c>
       <c r="Q13" s="34" t="n">
         <f aca="false">((Q6*Drivers!Q9)+(Drivers!Q24*AVERAGE('Balance Sheet'!P6,'Balance Sheet'!Q6)))</f>
-        <v>336.257608950636</v>
+        <v>336.257620351468</v>
       </c>
       <c r="R13" s="34" t="n">
         <f aca="false">((R6*Drivers!R9)+(Drivers!R24*AVERAGE('Balance Sheet'!Q6,'Balance Sheet'!R6)))</f>
-        <v>540.710539256074</v>
+        <v>540.71054998756</v>
       </c>
       <c r="S13" s="34" t="n">
         <f aca="false">((S6*Drivers!S9)+(Drivers!S24*AVERAGE('Balance Sheet'!R6,'Balance Sheet'!S6)))</f>
-        <v>764.261473461908</v>
+        <v>764.261492638239</v>
       </c>
       <c r="T13" s="34" t="n">
         <f aca="false">((T6*Drivers!T9)+(Drivers!T24*AVERAGE('Balance Sheet'!S6,'Balance Sheet'!T6)))</f>
-        <v>1008.83743769315</v>
+        <v>1008.8374690842</v>
       </c>
       <c r="U13" s="34" t="n">
         <f aca="false">((U6*Drivers!U9)+(Drivers!U24*AVERAGE('Balance Sheet'!T6,'Balance Sheet'!U6)))</f>
-        <v>1275.75501929028</v>
+        <v>1275.75506762001</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B14" s="56" t="n">
         <v>90.21</v>
@@ -10695,23 +10844,23 @@
       </c>
       <c r="M14" s="34" t="n">
         <f aca="false">(Drivers!M23*AVERAGE('Balance Sheet'!L19,'Balance Sheet'!M19))</f>
-        <v>601.647634801215</v>
+        <v>601.647635276826</v>
       </c>
       <c r="N14" s="34" t="n">
         <f aca="false">(Drivers!N23*AVERAGE('Balance Sheet'!M19,'Balance Sheet'!N19))</f>
-        <v>745.316250714981</v>
+        <v>745.316252518868</v>
       </c>
       <c r="O14" s="34" t="n">
         <f aca="false">(Drivers!O23*AVERAGE('Balance Sheet'!N19,'Balance Sheet'!O19))</f>
-        <v>714.979111283816</v>
+        <v>714.979115861244</v>
       </c>
       <c r="P14" s="34" t="n">
         <f aca="false">(Drivers!P23*AVERAGE('Balance Sheet'!O19,'Balance Sheet'!P19))</f>
-        <v>570.860263805141</v>
+        <v>570.860273548941</v>
       </c>
       <c r="Q14" s="34" t="n">
         <f aca="false">(Drivers!Q23*AVERAGE('Balance Sheet'!P19,'Balance Sheet'!Q19))</f>
-        <v>481.074168435091</v>
+        <v>481.074174929739</v>
       </c>
       <c r="R14" s="34" t="n">
         <f aca="false">(Drivers!R23*AVERAGE('Balance Sheet'!Q19,'Balance Sheet'!R19))</f>
@@ -10732,7 +10881,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B15" s="56" t="n">
         <v>0</v>
@@ -10807,7 +10956,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B16" s="60" t="n">
         <v>395.56</v>
@@ -10841,48 +10990,48 @@
       </c>
       <c r="L16" s="63" t="n">
         <f aca="false">(((L12+L13)-L14)+L15)</f>
-        <v>1957.04241823614</v>
+        <v>1957.04241825445</v>
       </c>
       <c r="M16" s="63" t="n">
         <f aca="false">(((M12+M13)-M14)+M15)</f>
-        <v>3009.54215447572</v>
+        <v>3009.54215454265</v>
       </c>
       <c r="N16" s="63" t="n">
         <f aca="false">(((N12+N13)-N14)+N15)</f>
-        <v>3117.2651472446</v>
+        <v>3117.26514746653</v>
       </c>
       <c r="O16" s="63" t="n">
         <f aca="false">(((O12+O13)-O14)+O15)</f>
-        <v>3790.94431042907</v>
+        <v>3790.94431110378</v>
       </c>
       <c r="P16" s="63" t="n">
         <f aca="false">(((P12+P13)-P14)+P15)</f>
-        <v>4401.29894601655</v>
+        <v>4401.2989477543</v>
       </c>
       <c r="Q16" s="63" t="n">
         <f aca="false">(((Q12+Q13)-Q14)+Q15)</f>
-        <v>5058.37871407419</v>
+        <v>5058.37871898038</v>
       </c>
       <c r="R16" s="63" t="n">
         <f aca="false">(((R12+R13)-R14)+R15)</f>
-        <v>5695.48250137527</v>
+        <v>5695.48251210676</v>
       </c>
       <c r="S16" s="63" t="n">
         <f aca="false">(((S12+S13)-S14)+S15)</f>
-        <v>6362.32880875402</v>
+        <v>6362.32882793035</v>
       </c>
       <c r="T16" s="63" t="n">
         <f aca="false">(((T12+T13)-T14)+T15)</f>
-        <v>7060.64372879027</v>
+        <v>7060.64376018133</v>
       </c>
       <c r="U16" s="63" t="n">
         <f aca="false">(((U12+U13)-U14)+U15)</f>
-        <v>7778.36008816178</v>
+        <v>7778.36013649152</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B17" s="56" t="n">
         <v>85.17</v>
@@ -10916,43 +11065,43 @@
       </c>
       <c r="L17" s="34" t="n">
         <f aca="false">(L16*Drivers!L22)</f>
-        <v>430.549332011951</v>
+        <v>430.549332015194</v>
       </c>
       <c r="M17" s="34" t="n">
         <f aca="false">(M16*Drivers!M22)</f>
-        <v>662.099273984659</v>
+        <v>662.099273999383</v>
       </c>
       <c r="N17" s="34" t="n">
         <f aca="false">(N16*Drivers!N22)</f>
-        <v>685.798332393813</v>
+        <v>685.798332442636</v>
       </c>
       <c r="O17" s="34" t="n">
         <f aca="false">(O16*Drivers!O22)</f>
-        <v>834.007748292348</v>
+        <v>834.007748442262</v>
       </c>
       <c r="P17" s="34" t="n">
         <f aca="false">(P16*Drivers!P22)</f>
-        <v>968.285768123642</v>
+        <v>968.285768504626</v>
       </c>
       <c r="Q17" s="34" t="n">
         <f aca="false">(Q16*Drivers!Q22)</f>
-        <v>1112.84331709511</v>
+        <v>1112.84331817568</v>
       </c>
       <c r="R17" s="34" t="n">
         <f aca="false">(R16*Drivers!R22)</f>
-        <v>1253.00615030256</v>
+        <v>1253.00615266349</v>
       </c>
       <c r="S17" s="34" t="n">
         <f aca="false">(S16*Drivers!S22)</f>
-        <v>1399.71233792588</v>
+        <v>1399.71234214468</v>
       </c>
       <c r="T17" s="34" t="n">
         <f aca="false">(T16*Drivers!T22)</f>
-        <v>1553.34162033386</v>
+        <v>1553.34162723989</v>
       </c>
       <c r="U17" s="34" t="n">
         <f aca="false">(U16*Drivers!U22)</f>
-        <v>1711.23921939559</v>
+        <v>1711.23923002739</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10991,48 +11140,48 @@
       </c>
       <c r="L18" s="63" t="n">
         <f aca="false">(L16-L17)</f>
-        <v>1526.49308622419</v>
+        <v>1526.49308623925</v>
       </c>
       <c r="M18" s="63" t="n">
         <f aca="false">(M16-M17)</f>
-        <v>2347.44288049106</v>
+        <v>2347.44288054327</v>
       </c>
       <c r="N18" s="63" t="n">
         <f aca="false">(N16-N17)</f>
-        <v>2431.46681485079</v>
+        <v>2431.46681502389</v>
       </c>
       <c r="O18" s="63" t="n">
         <f aca="false">(O16-O17)</f>
-        <v>2956.93656213672</v>
+        <v>2956.93656265893</v>
       </c>
       <c r="P18" s="63" t="n">
         <f aca="false">(P16-P17)</f>
-        <v>3433.01317789291</v>
+        <v>3433.01317924968</v>
       </c>
       <c r="Q18" s="63" t="n">
         <f aca="false">(Q16-Q17)</f>
-        <v>3945.53539697909</v>
+        <v>3945.5354008047</v>
       </c>
       <c r="R18" s="63" t="n">
         <f aca="false">(R16-R17)</f>
-        <v>4442.47635107271</v>
+        <v>4442.47635944327</v>
       </c>
       <c r="S18" s="63" t="n">
         <f aca="false">(S16-S17)</f>
-        <v>4962.61647082813</v>
+        <v>4962.61648578567</v>
       </c>
       <c r="T18" s="63" t="n">
         <f aca="false">(T16-T17)</f>
-        <v>5507.30210845641</v>
+        <v>5507.30213294144</v>
       </c>
       <c r="U18" s="63" t="n">
         <f aca="false">(U16-U17)</f>
-        <v>6067.12086876619</v>
+        <v>6067.12090646413</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="35" t="n">
         <f aca="false">IFERROR((B18)/(Schedules!B23),0)</f>
@@ -11076,43 +11225,43 @@
       </c>
       <c r="L19" s="36" t="n">
         <f aca="false">IFERROR((L18)/(Schedules!L23),0)</f>
-        <v>6.56980024198059</v>
+        <v>6.56980024204542</v>
       </c>
       <c r="M19" s="36" t="n">
         <f aca="false">IFERROR((M18)/(Schedules!M23),0)</f>
-        <v>10.1030466128301</v>
+        <v>10.1030466130547</v>
       </c>
       <c r="N19" s="36" t="n">
         <f aca="false">IFERROR((N18)/(Schedules!N23),0)</f>
-        <v>10.4646731863602</v>
+        <v>10.4646731871052</v>
       </c>
       <c r="O19" s="36" t="n">
         <f aca="false">IFERROR((O18)/(Schedules!O23),0)</f>
-        <v>12.7262171815654</v>
+        <v>12.7262171838129</v>
       </c>
       <c r="P19" s="36" t="n">
         <f aca="false">IFERROR((P18)/(Schedules!P23),0)</f>
-        <v>14.7751804514436</v>
+        <v>14.7751804572829</v>
       </c>
       <c r="Q19" s="36" t="n">
         <f aca="false">IFERROR((Q18)/(Schedules!Q23),0)</f>
-        <v>16.981000202191</v>
+        <v>16.9810002186559</v>
       </c>
       <c r="R19" s="36" t="n">
         <f aca="false">IFERROR((R18)/(Schedules!R23),0)</f>
-        <v>19.1197604952559</v>
+        <v>19.1197605312816</v>
       </c>
       <c r="S19" s="36" t="n">
         <f aca="false">IFERROR((S18)/(Schedules!S23),0)</f>
-        <v>21.3583665626345</v>
+        <v>21.3583666270096</v>
       </c>
       <c r="T19" s="36" t="n">
         <f aca="false">IFERROR((T18)/(Schedules!T23),0)</f>
-        <v>23.7026129049125</v>
+        <v>23.7026130102924</v>
       </c>
       <c r="U19" s="36" t="n">
         <f aca="false">IFERROR((U18)/(Schedules!U23),0)</f>
-        <v>26.1119899667148</v>
+        <v>26.1119901289612</v>
       </c>
     </row>
   </sheetData>
@@ -11141,44 +11290,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>5</v>
@@ -11190,33 +11339,33 @@
         <v>7</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="T4" s="27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="U4" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
@@ -11241,7 +11390,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B6" s="56" t="n">
         <v>44.88</v>
@@ -11275,48 +11424,48 @@
       </c>
       <c r="L6" s="34" t="n">
         <f aca="false">(K6+'Cash Flow'!L21)</f>
-        <v>4323.8062278758</v>
+        <v>4323.80622844811</v>
       </c>
       <c r="M6" s="34" t="n">
         <f aca="false">(L6+'Cash Flow'!M21)</f>
-        <v>999.999999453112</v>
+        <v>1000.0000155976</v>
       </c>
       <c r="N6" s="34" t="n">
         <f aca="false">(M6+'Cash Flow'!N21)</f>
-        <v>1000.00000058755</v>
+        <v>1000.00004679055</v>
       </c>
       <c r="O6" s="34" t="n">
         <f aca="false">(N6+'Cash Flow'!O21)</f>
-        <v>1000.00001158948</v>
+        <v>1000.00012698124</v>
       </c>
       <c r="P6" s="34" t="n">
         <f aca="false">(O6+'Cash Flow'!P21)</f>
-        <v>1000.00005705401</v>
+        <v>1000.00029491098</v>
       </c>
       <c r="Q6" s="34" t="n">
         <f aca="false">(P6+'Cash Flow'!Q21)</f>
-        <v>3827.89134226905</v>
+        <v>3827.89145521328</v>
       </c>
       <c r="R6" s="34" t="n">
         <f aca="false">(Q6+'Cash Flow'!R21)</f>
-        <v>6924.43127893236</v>
+        <v>6924.43149620052</v>
       </c>
       <c r="S6" s="34" t="n">
         <f aca="false">(R6+'Cash Flow'!S21)</f>
-        <v>10332.1004120394</v>
+        <v>10332.100784831</v>
       </c>
       <c r="T6" s="34" t="n">
         <f aca="false">(S6+'Cash Flow'!T21)</f>
-        <v>14072.4154439604</v>
+        <v>14072.4160370738</v>
       </c>
       <c r="U6" s="34" t="n">
         <f aca="false">(T6+'Cash Flow'!U21)</f>
-        <v>18146.7509122089</v>
+        <v>18146.7518060995</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B7" s="56" t="n">
         <v>198.5</v>
@@ -11391,7 +11540,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B8" s="56" t="n">
         <v>34.33</v>
@@ -11466,7 +11615,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B9" s="56" t="n">
         <v>598.95</v>
@@ -11541,7 +11690,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B10" s="56" t="n">
         <v>2730.37</v>
@@ -11616,7 +11765,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B11" s="56" t="n">
         <v>380.01</v>
@@ -11691,7 +11840,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B12" s="56" t="n">
         <v>94.64</v>
@@ -11766,7 +11915,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B13" s="62" t="n">
         <f aca="false">((((((B6+B7)+B8)+B9)+B10)+B11)+B12)</f>
@@ -11810,48 +11959,48 @@
       </c>
       <c r="L13" s="63" t="n">
         <f aca="false">((((((L6+L7)+L8)+L9)+L10)+L11)+L12)</f>
-        <v>28073.2218203392</v>
+        <v>28073.2218209115</v>
       </c>
       <c r="M13" s="63" t="n">
         <f aca="false">((((((M6+M7)+M8)+M9)+M10)+M11)+M12)</f>
-        <v>34553.2034517079</v>
+        <v>34553.2034678524</v>
       </c>
       <c r="N13" s="63" t="n">
         <f aca="false">((((((N6+N7)+N8)+N9)+N10)+N11)+N12)</f>
-        <v>38181.9001132028</v>
+        <v>38181.9001594058</v>
       </c>
       <c r="O13" s="63" t="n">
         <f aca="false">((((((O6+O7)+O8)+O9)+O10)+O11)+O12)</f>
-        <v>39838.6387117883</v>
+        <v>39838.63882718</v>
       </c>
       <c r="P13" s="63" t="n">
         <f aca="false">((((((P6+P7)+P8)+P9)+P10)+P11)+P12)</f>
-        <v>40721.6073789273</v>
+        <v>40721.6076167843</v>
       </c>
       <c r="Q13" s="63" t="n">
         <f aca="false">((((((Q6+Q7)+Q8)+Q9)+Q10)+Q11)+Q12)</f>
-        <v>44530.6297271574</v>
+        <v>44530.6298401017</v>
       </c>
       <c r="R13" s="63" t="n">
         <f aca="false">((((((R6+R7)+R8)+R9)+R10)+R11)+R12)</f>
-        <v>48798.8028327093</v>
+        <v>48798.8030499775</v>
       </c>
       <c r="S13" s="63" t="n">
         <f aca="false">((((((S6+S7)+S8)+S9)+S10)+S11)+S12)</f>
-        <v>53531.7428560499</v>
+        <v>53531.7432288415</v>
       </c>
       <c r="T13" s="63" t="n">
         <f aca="false">((((((T6+T7)+T8)+T9)+T10)+T11)+T12)</f>
-        <v>58751.0655564328</v>
+        <v>58751.0661495462</v>
       </c>
       <c r="U13" s="63" t="n">
         <f aca="false">((((((U6+U7)+U8)+U9)+U10)+U11)+U12)</f>
-        <v>64485.4549744171</v>
+        <v>64485.4558683077</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -11876,7 +12025,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B15" s="56" t="n">
         <v>56.32</v>
@@ -11951,7 +12100,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B16" s="56" t="n">
         <v>1797.91</v>
@@ -11985,48 +12134,48 @@
       </c>
       <c r="L16" s="34" t="n">
         <f aca="false">(((K16+'Income Statement'!L18)-Schedules!L22)+Drivers!L27)</f>
-        <v>18358.7739158509</v>
+        <v>18358.773915891</v>
       </c>
       <c r="M16" s="34" t="n">
         <f aca="false">(((L16+'Income Statement'!M18)-Schedules!M22)+Drivers!M27)</f>
-        <v>20424.5236506175</v>
+        <v>20424.5236526408</v>
       </c>
       <c r="N16" s="34" t="n">
         <f aca="false">(((M16+'Income Statement'!N18)-Schedules!N22)+Drivers!N27)</f>
-        <v>22564.2144477567</v>
+        <v>22564.2144554766</v>
       </c>
       <c r="O16" s="34" t="n">
         <f aca="false">(((N16+'Income Statement'!O18)-Schedules!O22)+Drivers!O27)</f>
-        <v>25166.3186238277</v>
+        <v>25166.3186458543</v>
       </c>
       <c r="P16" s="34" t="n">
         <f aca="false">(((O16+'Income Statement'!P18)-Schedules!P22)+Drivers!P27)</f>
-        <v>28187.3702272199</v>
+        <v>28187.3702789833</v>
       </c>
       <c r="Q16" s="34" t="n">
         <f aca="false">(((P16+'Income Statement'!Q18)-Schedules!Q22)+Drivers!Q27)</f>
-        <v>31659.4414090676</v>
+        <v>31659.4415214796</v>
       </c>
       <c r="R16" s="34" t="n">
         <f aca="false">(((Q16+'Income Statement'!R18)-Schedules!R22)+Drivers!R27)</f>
-        <v>35568.8206869898</v>
+        <v>35568.8209037257</v>
       </c>
       <c r="S16" s="34" t="n">
         <f aca="false">(((R16+'Income Statement'!S18)-Schedules!S22)+Drivers!S27)</f>
-        <v>39935.9233609879</v>
+        <v>39935.9237332472</v>
       </c>
       <c r="T16" s="34" t="n">
         <f aca="false">(((S16+'Income Statement'!T18)-Schedules!T22)+Drivers!T27)</f>
-        <v>44782.3495338186</v>
+        <v>44782.3501263997</v>
       </c>
       <c r="U16" s="34" t="n">
         <f aca="false">(((T16+'Income Statement'!U18)-Schedules!U22)+Drivers!U27)</f>
-        <v>50121.4164135213</v>
+        <v>50121.4173068796</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B17" s="56" t="n">
         <v>1599.11</v>
@@ -12101,7 +12250,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B18" s="56" t="n">
         <v>0</v>
@@ -12139,19 +12288,19 @@
       </c>
       <c r="M18" s="34" t="n">
         <f aca="false">((L18+Schedules!M18)-Schedules!M19)</f>
-        <v>3392.09242289184</v>
+        <v>3392.09243648074</v>
       </c>
       <c r="N18" s="34" t="n">
         <f aca="false">((M18+Schedules!N18)-Schedules!N19)</f>
-        <v>4104.81759753617</v>
+        <v>4104.8176354869</v>
       </c>
       <c r="O18" s="34" t="n">
         <f aca="false">((N18+Schedules!O18)-Schedules!O19)</f>
-        <v>2535.31701057285</v>
+        <v>2535.31710340578</v>
       </c>
       <c r="P18" s="34" t="n">
         <f aca="false">((O18+Schedules!P18)-Schedules!P19)</f>
-        <v>12.1362410026081</v>
+        <v>12.1364265639545</v>
       </c>
       <c r="Q18" s="34" t="n">
         <f aca="false">((P18+Schedules!Q18)-Schedules!Q19)</f>
@@ -12176,7 +12325,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B19" s="53" t="n">
         <f aca="false">(B17+B18)</f>
@@ -12224,19 +12373,19 @@
       </c>
       <c r="M19" s="59" t="n">
         <f aca="false">(M17+M18)</f>
-        <v>10291.0124228918</v>
+        <v>10291.0124364807</v>
       </c>
       <c r="N19" s="59" t="n">
         <f aca="false">(N17+N18)</f>
-        <v>11003.7375975362</v>
+        <v>11003.7376354869</v>
       </c>
       <c r="O19" s="59" t="n">
         <f aca="false">(O17+O18)</f>
-        <v>9424.23701057285</v>
+        <v>9424.23710340578</v>
       </c>
       <c r="P19" s="59" t="n">
         <f aca="false">(P17+P18)</f>
-        <v>6886.05624100261</v>
+        <v>6886.05642656396</v>
       </c>
       <c r="Q19" s="59" t="n">
         <f aca="false">(Q17+Q18)</f>
@@ -12261,7 +12410,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B20" s="56" t="n">
         <v>0</v>
@@ -12336,7 +12485,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B21" s="56" t="n">
         <v>628.34</v>
@@ -12411,7 +12560,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B22" s="62" t="n">
         <f aca="false">((((B15+B16)+B19)+B20)+B21)</f>
@@ -12455,43 +12604,43 @@
       </c>
       <c r="L22" s="63" t="n">
         <f aca="false">((((L15+L16)+L19)+L20)+L21)</f>
-        <v>28073.2218203392</v>
+        <v>28073.2218203792</v>
       </c>
       <c r="M22" s="63" t="n">
         <f aca="false">((((M15+M16)+M19)+M20)+M21)</f>
-        <v>34553.2034517079</v>
+        <v>34553.2034673201</v>
       </c>
       <c r="N22" s="63" t="n">
         <f aca="false">((((N15+N16)+N19)+N20)+N21)</f>
-        <v>38181.9001132028</v>
+        <v>38181.9001588735</v>
       </c>
       <c r="O22" s="63" t="n">
         <f aca="false">((((O15+O16)+O19)+O20)+O21)</f>
-        <v>39838.6387117882</v>
+        <v>39838.6388266477</v>
       </c>
       <c r="P22" s="63" t="n">
         <f aca="false">((((P15+P16)+P19)+P20)+P21)</f>
-        <v>40721.6073789273</v>
+        <v>40721.607616252</v>
       </c>
       <c r="Q22" s="63" t="n">
         <f aca="false">((((Q15+Q16)+Q19)+Q20)+Q21)</f>
-        <v>44530.6297271574</v>
+        <v>44530.6298395694</v>
       </c>
       <c r="R22" s="63" t="n">
         <f aca="false">((((R15+R16)+R19)+R20)+R21)</f>
-        <v>48798.8028327093</v>
+        <v>48798.8030494452</v>
       </c>
       <c r="S22" s="63" t="n">
         <f aca="false">((((S15+S16)+S19)+S20)+S21)</f>
-        <v>53531.7428560499</v>
+        <v>53531.7432283092</v>
       </c>
       <c r="T22" s="63" t="n">
         <f aca="false">((((T15+T16)+T19)+T20)+T21)</f>
-        <v>58751.0655564328</v>
+        <v>58751.0661490139</v>
       </c>
       <c r="U22" s="63" t="n">
         <f aca="false">((((U15+U16)+U19)+U20)+U21)</f>
-        <v>64485.4549744171</v>
+        <v>64485.4558677754</v>
       </c>
     </row>
   </sheetData>
@@ -12520,44 +12669,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>5</v>
@@ -12569,33 +12718,33 @@
         <v>7</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="T4" s="27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="U4" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
@@ -12620,7 +12769,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">'Income Statement'!B18</f>
@@ -12664,48 +12813,48 @@
       </c>
       <c r="L6" s="34" t="n">
         <f aca="false">'Income Statement'!L18</f>
-        <v>1526.49308622419</v>
+        <v>1526.49308623925</v>
       </c>
       <c r="M6" s="34" t="n">
         <f aca="false">'Income Statement'!M18</f>
-        <v>2347.44288049106</v>
+        <v>2347.44288054327</v>
       </c>
       <c r="N6" s="34" t="n">
         <f aca="false">'Income Statement'!N18</f>
-        <v>2431.46681485079</v>
+        <v>2431.46681502389</v>
       </c>
       <c r="O6" s="34" t="n">
         <f aca="false">'Income Statement'!O18</f>
-        <v>2956.93656213672</v>
+        <v>2956.93656265893</v>
       </c>
       <c r="P6" s="34" t="n">
         <f aca="false">'Income Statement'!P18</f>
-        <v>3433.01317789291</v>
+        <v>3433.01317924968</v>
       </c>
       <c r="Q6" s="34" t="n">
         <f aca="false">'Income Statement'!Q18</f>
-        <v>3945.53539697909</v>
+        <v>3945.5354008047</v>
       </c>
       <c r="R6" s="34" t="n">
         <f aca="false">'Income Statement'!R18</f>
-        <v>4442.47635107271</v>
+        <v>4442.47635944327</v>
       </c>
       <c r="S6" s="34" t="n">
         <f aca="false">'Income Statement'!S18</f>
-        <v>4962.61647082813</v>
+        <v>4962.61648578567</v>
       </c>
       <c r="T6" s="34" t="n">
         <f aca="false">'Income Statement'!T18</f>
-        <v>5507.30210845641</v>
+        <v>5507.30213294144</v>
       </c>
       <c r="U6" s="34" t="n">
         <f aca="false">'Income Statement'!U18</f>
-        <v>6067.12086876619</v>
+        <v>6067.12090646413</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">'Income Statement'!B11</f>
@@ -12790,7 +12939,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">-(Schedules!B12)</f>
@@ -12875,7 +13024,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B9" s="62" t="n">
         <f aca="false">((B6+B7)+B8)</f>
@@ -12919,48 +13068,48 @@
       </c>
       <c r="L9" s="63" t="n">
         <f aca="false">((L6+L7)+L8)</f>
-        <v>2745.74129124905</v>
+        <v>2745.74129126411</v>
       </c>
       <c r="M9" s="63" t="n">
         <f aca="false">((M6+M7)+M8)</f>
-        <v>3074.28650195616</v>
+        <v>3074.28650200836</v>
       </c>
       <c r="N9" s="63" t="n">
         <f aca="false">((N6+N7)+N8)</f>
-        <v>3820.46109282677</v>
+        <v>3820.46109299987</v>
       </c>
       <c r="O9" s="63" t="n">
         <f aca="false">((O6+O7)+O8)</f>
-        <v>4542.62986374265</v>
+        <v>4542.62986426485</v>
       </c>
       <c r="P9" s="63" t="n">
         <f aca="false">((P6+P7)+P8)</f>
-        <v>5149.1722191681</v>
+        <v>5149.17222052487</v>
       </c>
       <c r="Q9" s="63" t="n">
         <f aca="false">((Q6+Q7)+Q8)</f>
-        <v>5636.89007330864</v>
+        <v>5636.89007713425</v>
       </c>
       <c r="R9" s="63" t="n">
         <f aca="false">((R6+R7)+R8)</f>
-        <v>6138.01390168346</v>
+        <v>6138.01391005402</v>
       </c>
       <c r="S9" s="63" t="n">
         <f aca="false">((S6+S7)+S8)</f>
-        <v>6672.00941939877</v>
+        <v>6672.00943435631</v>
       </c>
       <c r="T9" s="63" t="n">
         <f aca="false">((T6+T7)+T8)</f>
-        <v>7242.03717067293</v>
+        <v>7242.03719515796</v>
       </c>
       <c r="U9" s="63" t="n">
         <f aca="false">((U6+U7)+U8)</f>
-        <v>7830.30638384225</v>
+        <v>7830.30642154019</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="29"/>
@@ -12985,7 +13134,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">(-(Schedules!B7)-('Balance Sheet'!B11-0))</f>
@@ -13070,7 +13219,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">-(('Balance Sheet'!B12-0))</f>
@@ -13155,7 +13304,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B13" s="62" t="n">
         <f aca="false">(B11+B12)</f>
@@ -13240,7 +13389,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -13265,7 +13414,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">('Balance Sheet'!B17-0)</f>
@@ -13350,7 +13499,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">('Balance Sheet'!B18-0)</f>
@@ -13398,23 +13547,23 @@
       </c>
       <c r="M16" s="34" t="n">
         <f aca="false">('Balance Sheet'!M18-'Balance Sheet'!L18)</f>
-        <v>3392.09242289184</v>
+        <v>3392.09243648074</v>
       </c>
       <c r="N16" s="34" t="n">
         <f aca="false">('Balance Sheet'!N18-'Balance Sheet'!M18)</f>
-        <v>712.725174644329</v>
+        <v>712.725199006156</v>
       </c>
       <c r="O16" s="34" t="n">
         <f aca="false">('Balance Sheet'!O18-'Balance Sheet'!N18)</f>
-        <v>-1569.50058696332</v>
+        <v>-1569.50053208112</v>
       </c>
       <c r="P16" s="34" t="n">
         <f aca="false">('Balance Sheet'!P18-'Balance Sheet'!O18)</f>
-        <v>-2523.18076957025</v>
+        <v>-2523.18067684183</v>
       </c>
       <c r="Q16" s="34" t="n">
         <f aca="false">('Balance Sheet'!Q18-'Balance Sheet'!P18)</f>
-        <v>-12.1362410026081</v>
+        <v>-12.1364265639545</v>
       </c>
       <c r="R16" s="34" t="n">
         <f aca="false">('Balance Sheet'!R18-'Balance Sheet'!Q18)</f>
@@ -13435,7 +13584,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">-(Schedules!B22)</f>
@@ -13479,48 +13628,48 @@
       </c>
       <c r="L17" s="34" t="n">
         <f aca="false">-(Schedules!L22)</f>
-        <v>-183.179170373246</v>
+        <v>-183.179169816</v>
       </c>
       <c r="M17" s="34" t="n">
         <f aca="false">-(Schedules!M22)</f>
-        <v>-281.693145724554</v>
+        <v>-281.69314379348</v>
       </c>
       <c r="N17" s="34" t="n">
         <f aca="false">-(Schedules!N22)</f>
-        <v>-291.776017711589</v>
+        <v>-291.776012188</v>
       </c>
       <c r="O17" s="34" t="n">
         <f aca="false">-(Schedules!O22)</f>
-        <v>-354.83238606567</v>
+        <v>-354.832372281323</v>
       </c>
       <c r="P17" s="34" t="n">
         <f aca="false">-(Schedules!P22)</f>
-        <v>-411.961574500669</v>
+        <v>-411.961546120644</v>
       </c>
       <c r="Q17" s="34" t="n">
         <f aca="false">-(Schedules!Q22)</f>
-        <v>-473.464215131402</v>
+        <v>-473.46415830841</v>
       </c>
       <c r="R17" s="34" t="n">
         <f aca="false">-(Schedules!R22)</f>
-        <v>-533.097073150546</v>
+        <v>-533.096977197171</v>
       </c>
       <c r="S17" s="34" t="n">
         <f aca="false">-(Schedules!S22)</f>
-        <v>-595.513796830043</v>
+        <v>-595.513656264118</v>
       </c>
       <c r="T17" s="34" t="n">
         <f aca="false">-(Schedules!T22)</f>
-        <v>-660.875935625699</v>
+        <v>-660.875739788952</v>
       </c>
       <c r="U17" s="34" t="n">
         <f aca="false">-(Schedules!U22)</f>
-        <v>-728.05398906355</v>
+        <v>-728.053725984277</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">Drivers!B27</f>
@@ -13605,7 +13754,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B19" s="62" t="n">
         <f aca="false">(((B15+B16)+B17)+B18)</f>
@@ -13649,48 +13798,48 @@
       </c>
       <c r="L19" s="63" t="n">
         <f aca="false">(((L15+L16)+L17)+L18)</f>
-        <v>6371.82082962675</v>
+        <v>6371.820830184</v>
       </c>
       <c r="M19" s="63" t="n">
         <f aca="false">(((M15+M16)+M17)+M18)</f>
-        <v>3110.39927716729</v>
+        <v>3110.39929268727</v>
       </c>
       <c r="N19" s="63" t="n">
         <f aca="false">(((N15+N16)+N17)+N18)</f>
-        <v>420.94915693274</v>
+        <v>420.949186818156</v>
       </c>
       <c r="O19" s="63" t="n">
         <f aca="false">(((O15+O16)+O17)+O18)</f>
-        <v>-1934.33297302899</v>
+        <v>-1934.33290436244</v>
       </c>
       <c r="P19" s="63" t="n">
         <f aca="false">(((P15+P16)+P17)+P18)</f>
-        <v>-2950.14234407091</v>
+        <v>-2950.14222296247</v>
       </c>
       <c r="Q19" s="63" t="n">
         <f aca="false">(((Q15+Q16)+Q17)+Q18)</f>
-        <v>-500.60045613401</v>
+        <v>-500.600584872365</v>
       </c>
       <c r="R19" s="63" t="n">
         <f aca="false">(((R15+R16)+R17)+R18)</f>
-        <v>-548.097073150546</v>
+        <v>-548.096977197171</v>
       </c>
       <c r="S19" s="63" t="n">
         <f aca="false">(((S15+S16)+S17)+S18)</f>
-        <v>-610.513796830043</v>
+        <v>-610.513656264118</v>
       </c>
       <c r="T19" s="63" t="n">
         <f aca="false">(((T15+T16)+T17)+T18)</f>
-        <v>-670.875935625699</v>
+        <v>-670.875739788952</v>
       </c>
       <c r="U19" s="63" t="n">
         <f aca="false">(((U15+U16)+U17)+U18)</f>
-        <v>-738.05398906355</v>
+        <v>-738.053725984277</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -13715,7 +13864,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B21" s="64" t="n">
         <f aca="false">((B9+B13)+B19)</f>
@@ -13759,48 +13908,48 @@
       </c>
       <c r="L21" s="65" t="n">
         <f aca="false">((L9+L13)+L19)</f>
-        <v>2006.1062278758</v>
+        <v>2006.10622844811</v>
       </c>
       <c r="M21" s="65" t="n">
         <f aca="false">((M9+M13)+M19)</f>
-        <v>-3323.80622842269</v>
+        <v>-3323.80621285051</v>
       </c>
       <c r="N21" s="65" t="n">
         <f aca="false">((N9+N13)+N19)</f>
-        <v>1.13443468308105E-006</v>
+        <v>3.11929526333188E-005</v>
       </c>
       <c r="O21" s="65" t="n">
         <f aca="false">((O9+O13)+O19)</f>
-        <v>1.10019300336717E-005</v>
+        <v>8.01906808192143E-005</v>
       </c>
       <c r="P21" s="65" t="n">
         <f aca="false">((P9+P13)+P19)</f>
-        <v>4.54645296485978E-005</v>
+        <v>0.000167929739291139</v>
       </c>
       <c r="Q21" s="65" t="n">
         <f aca="false">((Q9+Q13)+Q19)</f>
-        <v>2827.89128521505</v>
+        <v>2827.8911603023</v>
       </c>
       <c r="R21" s="65" t="n">
         <f aca="false">((R9+R13)+R19)</f>
-        <v>3096.53993666331</v>
+        <v>3096.54004098724</v>
       </c>
       <c r="S21" s="65" t="n">
         <f aca="false">((S9+S13)+S19)</f>
-        <v>3407.66913310704</v>
+        <v>3407.6692886305</v>
       </c>
       <c r="T21" s="65" t="n">
         <f aca="false">((T9+T13)+T19)</f>
-        <v>3740.315031921</v>
+        <v>3740.31525224278</v>
       </c>
       <c r="U21" s="65" t="n">
         <f aca="false">((U9+U13)+U19)</f>
-        <v>4074.33546824851</v>
+        <v>4074.33576902572</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B22" s="53" t="n">
         <f aca="false">0</f>
@@ -13848,44 +13997,44 @@
       </c>
       <c r="M22" s="34" t="n">
         <f aca="false">'Balance Sheet'!L6</f>
-        <v>4323.8062278758</v>
+        <v>4323.80622844811</v>
       </c>
       <c r="N22" s="34" t="n">
         <f aca="false">'Balance Sheet'!M6</f>
-        <v>999.999999453112</v>
+        <v>1000.0000155976</v>
       </c>
       <c r="O22" s="34" t="n">
         <f aca="false">'Balance Sheet'!N6</f>
-        <v>1000.00000058755</v>
+        <v>1000.00004679055</v>
       </c>
       <c r="P22" s="34" t="n">
         <f aca="false">'Balance Sheet'!O6</f>
-        <v>1000.00001158948</v>
+        <v>1000.00012698124</v>
       </c>
       <c r="Q22" s="34" t="n">
         <f aca="false">'Balance Sheet'!P6</f>
-        <v>1000.00005705401</v>
+        <v>1000.00029491098</v>
       </c>
       <c r="R22" s="34" t="n">
         <f aca="false">'Balance Sheet'!Q6</f>
-        <v>3827.89134226905</v>
+        <v>3827.89145521328</v>
       </c>
       <c r="S22" s="34" t="n">
         <f aca="false">'Balance Sheet'!R6</f>
-        <v>6924.43127893236</v>
+        <v>6924.43149620052</v>
       </c>
       <c r="T22" s="34" t="n">
         <f aca="false">'Balance Sheet'!S6</f>
-        <v>10332.1004120394</v>
+        <v>10332.100784831</v>
       </c>
       <c r="U22" s="34" t="n">
         <f aca="false">'Balance Sheet'!T6</f>
-        <v>14072.4154439604</v>
+        <v>14072.4160370738</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B23" s="62" t="n">
         <f aca="false">(B22+B21)</f>
@@ -13929,48 +14078,48 @@
       </c>
       <c r="L23" s="63" t="n">
         <f aca="false">(L22+L21)</f>
-        <v>4323.8062278758</v>
+        <v>4323.80622844811</v>
       </c>
       <c r="M23" s="63" t="n">
         <f aca="false">(M22+M21)</f>
-        <v>999.999999453112</v>
+        <v>1000.0000155976</v>
       </c>
       <c r="N23" s="63" t="n">
         <f aca="false">(N22+N21)</f>
-        <v>1000.00000058755</v>
+        <v>1000.00004679055</v>
       </c>
       <c r="O23" s="63" t="n">
         <f aca="false">(O22+O21)</f>
-        <v>1000.00001158948</v>
+        <v>1000.00012698124</v>
       </c>
       <c r="P23" s="63" t="n">
         <f aca="false">(P22+P21)</f>
-        <v>1000.00005705401</v>
+        <v>1000.00029491098</v>
       </c>
       <c r="Q23" s="63" t="n">
         <f aca="false">(Q22+Q21)</f>
-        <v>3827.89134226905</v>
+        <v>3827.89145521328</v>
       </c>
       <c r="R23" s="63" t="n">
         <f aca="false">(R22+R21)</f>
-        <v>6924.43127893236</v>
+        <v>6924.43149620052</v>
       </c>
       <c r="S23" s="63" t="n">
         <f aca="false">(S22+S21)</f>
-        <v>10332.1004120394</v>
+        <v>10332.100784831</v>
       </c>
       <c r="T23" s="63" t="n">
         <f aca="false">(T22+T21)</f>
-        <v>14072.4154439604</v>
+        <v>14072.4160370738</v>
       </c>
       <c r="U23" s="63" t="n">
         <f aca="false">(U22+U21)</f>
-        <v>18146.7509122089</v>
+        <v>18146.7518060995</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B24" s="29"/>
       <c r="C24" s="29"/>
@@ -13995,7 +14144,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B25" s="56" t="n">
         <v>615.85</v>
@@ -14070,7 +14219,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B26" s="56" t="n">
         <v>-1051.79</v>
@@ -14145,7 +14294,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B27" s="56" t="n">
         <v>387.15</v>
@@ -14220,7 +14369,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B28" s="66" t="n">
         <f aca="false">(B9-B25)</f>
@@ -14264,43 +14413,43 @@
       </c>
       <c r="L28" s="67" t="n">
         <f aca="false">(L9-L25)</f>
-        <v>2745.74129124905</v>
+        <v>2745.74129126411</v>
       </c>
       <c r="M28" s="67" t="n">
         <f aca="false">(M9-M25)</f>
-        <v>3074.28650195616</v>
+        <v>3074.28650200836</v>
       </c>
       <c r="N28" s="67" t="n">
         <f aca="false">(N9-N25)</f>
-        <v>3820.46109282677</v>
+        <v>3820.46109299987</v>
       </c>
       <c r="O28" s="67" t="n">
         <f aca="false">(O9-O25)</f>
-        <v>4542.62986374265</v>
+        <v>4542.62986426485</v>
       </c>
       <c r="P28" s="67" t="n">
         <f aca="false">(P9-P25)</f>
-        <v>5149.1722191681</v>
+        <v>5149.17222052487</v>
       </c>
       <c r="Q28" s="67" t="n">
         <f aca="false">(Q9-Q25)</f>
-        <v>5636.89007330864</v>
+        <v>5636.89007713425</v>
       </c>
       <c r="R28" s="67" t="n">
         <f aca="false">(R9-R25)</f>
-        <v>6138.01390168346</v>
+        <v>6138.01391005402</v>
       </c>
       <c r="S28" s="67" t="n">
         <f aca="false">(S9-S25)</f>
-        <v>6672.00941939877</v>
+        <v>6672.00943435631</v>
       </c>
       <c r="T28" s="67" t="n">
         <f aca="false">(T9-T25)</f>
-        <v>7242.03717067293</v>
+        <v>7242.03719515796</v>
       </c>
       <c r="U28" s="67" t="n">
         <f aca="false">(U9-U25)</f>
-        <v>7830.30638384225</v>
+        <v>7830.30642154019</v>
       </c>
     </row>
   </sheetData>
@@ -14329,44 +14478,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>5</v>
@@ -14378,33 +14527,33 @@
         <v>7</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="T4" s="27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="U4" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
@@ -14429,7 +14578,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B6" s="53" t="n">
         <f aca="false">0</f>
@@ -14514,7 +14663,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B7" s="56" t="n">
         <v>0</v>
@@ -14589,7 +14738,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Income Statement'!B11</f>
@@ -14674,7 +14823,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B9" s="62" t="n">
         <f aca="false">((B6+B7)-B8)</f>
@@ -14759,7 +14908,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="29"/>
@@ -14784,7 +14933,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B11" s="30" t="n">
         <f aca="false">(((('Balance Sheet'!B7+'Balance Sheet'!B8)+'Balance Sheet'!B9)-'Balance Sheet'!B20)-'Balance Sheet'!B21)</f>
@@ -14869,7 +15018,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B12" s="53" t="n">
         <f aca="false">(B11-0)</f>
@@ -14954,7 +15103,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B13" s="51" t="n">
         <f aca="false">(IFERROR((B11)/('Income Statement'!B6),0)*365)</f>
@@ -15039,7 +15188,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -15064,7 +15213,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B15" s="53" t="n">
         <f aca="false">0</f>
@@ -15149,7 +15298,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">(('Cash Flow'!B15+'Cash Flow'!B17)+'Cash Flow'!B18)</f>
@@ -15193,48 +15342,48 @@
       </c>
       <c r="L16" s="34" t="n">
         <f aca="false">(('Cash Flow'!L15+'Cash Flow'!L17)+'Cash Flow'!L18)</f>
-        <v>6371.82082962675</v>
+        <v>6371.820830184</v>
       </c>
       <c r="M16" s="34" t="n">
         <f aca="false">(('Cash Flow'!M15+'Cash Flow'!M17)+'Cash Flow'!M18)</f>
-        <v>-281.693145724554</v>
+        <v>-281.69314379348</v>
       </c>
       <c r="N16" s="34" t="n">
         <f aca="false">(('Cash Flow'!N15+'Cash Flow'!N17)+'Cash Flow'!N18)</f>
-        <v>-291.776017711589</v>
+        <v>-291.776012188</v>
       </c>
       <c r="O16" s="34" t="n">
         <f aca="false">(('Cash Flow'!O15+'Cash Flow'!O17)+'Cash Flow'!O18)</f>
-        <v>-364.83238606567</v>
+        <v>-364.832372281323</v>
       </c>
       <c r="P16" s="34" t="n">
         <f aca="false">(('Cash Flow'!P15+'Cash Flow'!P17)+'Cash Flow'!P18)</f>
-        <v>-426.961574500669</v>
+        <v>-426.961546120644</v>
       </c>
       <c r="Q16" s="34" t="n">
         <f aca="false">(('Cash Flow'!Q15+'Cash Flow'!Q17)+'Cash Flow'!Q18)</f>
-        <v>-488.464215131402</v>
+        <v>-488.46415830841</v>
       </c>
       <c r="R16" s="34" t="n">
         <f aca="false">(('Cash Flow'!R15+'Cash Flow'!R17)+'Cash Flow'!R18)</f>
-        <v>-548.097073150546</v>
+        <v>-548.096977197171</v>
       </c>
       <c r="S16" s="34" t="n">
         <f aca="false">(('Cash Flow'!S15+'Cash Flow'!S17)+'Cash Flow'!S18)</f>
-        <v>-610.513796830043</v>
+        <v>-610.513656264118</v>
       </c>
       <c r="T16" s="34" t="n">
         <f aca="false">(('Cash Flow'!T15+'Cash Flow'!T17)+'Cash Flow'!T18)</f>
-        <v>-670.875935625699</v>
+        <v>-670.875739788952</v>
       </c>
       <c r="U16" s="34" t="n">
         <f aca="false">(('Cash Flow'!U15+'Cash Flow'!U17)+'Cash Flow'!U18)</f>
-        <v>-738.05398906355</v>
+        <v>-738.053725984277</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">(((0+'Cash Flow'!B9)+'Cash Flow'!B13)+B16)</f>
@@ -15278,48 +15427,48 @@
       </c>
       <c r="L17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!K6+'Cash Flow'!L9)+'Cash Flow'!L13)+L16)</f>
-        <v>4323.80622809533</v>
+        <v>4323.80622400886</v>
       </c>
       <c r="M17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!L6+'Cash Flow'!M9)+'Cash Flow'!M13)+M16)</f>
-        <v>-2392.09242289184</v>
+        <v>-2392.09243648074</v>
       </c>
       <c r="N17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!M6+'Cash Flow'!N9)+'Cash Flow'!N13)+N16)</f>
-        <v>287.274825355671</v>
+        <v>287.274800993844</v>
       </c>
       <c r="O17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!N6+'Cash Flow'!O9)+'Cash Flow'!O13)+O16)</f>
-        <v>2569.50058696332</v>
+        <v>2569.50053208112</v>
       </c>
       <c r="P17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!O6+'Cash Flow'!P9)+'Cash Flow'!P13)+P16)</f>
-        <v>3523.18076957025</v>
+        <v>3523.18067684183</v>
       </c>
       <c r="Q17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!P6+'Cash Flow'!Q9)+'Cash Flow'!Q13)+Q16)</f>
-        <v>3840.02731238759</v>
+        <v>3840.02713354262</v>
       </c>
       <c r="R17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!Q6+'Cash Flow'!R9)+'Cash Flow'!R13)+R16)</f>
-        <v>6924.43053744753</v>
+        <v>6924.42994673367</v>
       </c>
       <c r="S17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!R6+'Cash Flow'!S9)+'Cash Flow'!S13)+S16)</f>
-        <v>10332.098914795</v>
+        <v>10332.0981012463</v>
       </c>
       <c r="T17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!S6+'Cash Flow'!T9)+'Cash Flow'!T13)+T16)</f>
-        <v>14072.4127990515</v>
+        <v>14072.411735707</v>
       </c>
       <c r="U17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!T6+'Cash Flow'!U9)+'Cash Flow'!U13)+U16)</f>
-        <v>18146.7466189723</v>
+        <v>18146.7452828377</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">MAX((Drivers!B29-B17),0)</f>
@@ -15367,11 +15516,11 @@
       </c>
       <c r="M18" s="34" t="n">
         <f aca="false">MAX((Drivers!M29-M17),0)</f>
-        <v>3392.09242289184</v>
+        <v>3392.09243648074</v>
       </c>
       <c r="N18" s="34" t="n">
         <f aca="false">MAX((Drivers!N29-N17),0)</f>
-        <v>712.725174644329</v>
+        <v>712.725199006156</v>
       </c>
       <c r="O18" s="34" t="n">
         <f aca="false">MAX((Drivers!O29-O17),0)</f>
@@ -15404,7 +15553,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">MIN(0,MAX((B17-Drivers!B29),0))</f>
@@ -15460,15 +15609,15 @@
       </c>
       <c r="O19" s="34" t="n">
         <f aca="false">MIN('Balance Sheet'!N18,MAX((O17-Drivers!O29),0))</f>
-        <v>1569.50058696332</v>
+        <v>1569.50053208112</v>
       </c>
       <c r="P19" s="34" t="n">
         <f aca="false">MIN('Balance Sheet'!O18,MAX((P17-Drivers!P29),0))</f>
-        <v>2523.18076957025</v>
+        <v>2523.18067684183</v>
       </c>
       <c r="Q19" s="34" t="n">
         <f aca="false">MIN('Balance Sheet'!P18,MAX((Q17-Drivers!Q29),0))</f>
-        <v>12.1362410026081</v>
+        <v>12.1364265639545</v>
       </c>
       <c r="R19" s="34" t="n">
         <f aca="false">MIN('Balance Sheet'!Q18,MAX((R17-Drivers!R29),0))</f>
@@ -15489,7 +15638,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">AVERAGE(0,'Balance Sheet'!B19)</f>
@@ -15537,23 +15686,23 @@
       </c>
       <c r="M20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!L19,'Balance Sheet'!M19)</f>
-        <v>8594.96621144592</v>
+        <v>8594.96621824037</v>
       </c>
       <c r="N20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!M19,'Balance Sheet'!N19)</f>
-        <v>10647.375010214</v>
+        <v>10647.3750359838</v>
       </c>
       <c r="O20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!N19,'Balance Sheet'!O19)</f>
-        <v>10213.9873040545</v>
+        <v>10213.9873694463</v>
       </c>
       <c r="P20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!O19,'Balance Sheet'!P19)</f>
-        <v>8155.14662578773</v>
+        <v>8155.14676498487</v>
       </c>
       <c r="Q20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!P19,'Balance Sheet'!Q19)</f>
-        <v>6872.4881205013</v>
+        <v>6872.48821328198</v>
       </c>
       <c r="R20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!Q19,'Balance Sheet'!R19)</f>
@@ -15574,7 +15723,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -15599,7 +15748,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B22" s="56" t="n">
         <v>0</v>
@@ -15633,48 +15782,48 @@
       </c>
       <c r="L22" s="34" t="n">
         <f aca="false">('Income Statement'!L18*Drivers!L28)</f>
-        <v>183.179170373246</v>
+        <v>183.179170348283</v>
       </c>
       <c r="M22" s="34" t="n">
         <f aca="false">('Income Statement'!M18*Drivers!M28)</f>
-        <v>281.693145724554</v>
+        <v>281.69314379348</v>
       </c>
       <c r="N22" s="34" t="n">
         <f aca="false">('Income Statement'!N18*Drivers!N28)</f>
-        <v>291.776017711589</v>
+        <v>291.776012188</v>
       </c>
       <c r="O22" s="34" t="n">
         <f aca="false">('Income Statement'!O18*Drivers!O28)</f>
-        <v>354.83238606567</v>
+        <v>354.832372281323</v>
       </c>
       <c r="P22" s="34" t="n">
         <f aca="false">('Income Statement'!P18*Drivers!P28)</f>
-        <v>411.961574500669</v>
+        <v>411.961546120644</v>
       </c>
       <c r="Q22" s="34" t="n">
         <f aca="false">('Income Statement'!Q18*Drivers!Q28)</f>
-        <v>473.464215131402</v>
+        <v>473.46415830841</v>
       </c>
       <c r="R22" s="34" t="n">
         <f aca="false">('Income Statement'!R18*Drivers!R28)</f>
-        <v>533.097073150546</v>
+        <v>533.096977197171</v>
       </c>
       <c r="S22" s="34" t="n">
         <f aca="false">('Income Statement'!S18*Drivers!S28)</f>
-        <v>595.513796830043</v>
+        <v>595.513656264118</v>
       </c>
       <c r="T22" s="34" t="n">
         <f aca="false">('Income Statement'!T18*Drivers!T28)</f>
-        <v>660.875935625699</v>
+        <v>660.875739788952</v>
       </c>
       <c r="U22" s="34" t="n">
         <f aca="false">('Income Statement'!U18*Drivers!U28)</f>
-        <v>728.05398906355</v>
+        <v>728.053725984277</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B23" s="69" t="n">
         <v>56847632</v>
@@ -15749,7 +15898,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B24" s="30" t="n">
         <f aca="false">('Balance Sheet'!B15+'Balance Sheet'!B16)</f>
@@ -15793,48 +15942,48 @@
       </c>
       <c r="L24" s="31" t="n">
         <f aca="false">('Balance Sheet'!L15+'Balance Sheet'!L16)</f>
-        <v>18775.8139158509</v>
+        <v>18775.813915891</v>
       </c>
       <c r="M24" s="31" t="n">
         <f aca="false">('Balance Sheet'!M15+'Balance Sheet'!M16)</f>
-        <v>20841.5636506175</v>
+        <v>20841.5636526408</v>
       </c>
       <c r="N24" s="31" t="n">
         <f aca="false">('Balance Sheet'!N15+'Balance Sheet'!N16)</f>
-        <v>22981.2544477567</v>
+        <v>22981.2544554766</v>
       </c>
       <c r="O24" s="31" t="n">
         <f aca="false">('Balance Sheet'!O15+'Balance Sheet'!O16)</f>
-        <v>25583.3586238277</v>
+        <v>25583.3586458543</v>
       </c>
       <c r="P24" s="31" t="n">
         <f aca="false">('Balance Sheet'!P15+'Balance Sheet'!P16)</f>
-        <v>28604.4102272199</v>
+        <v>28604.4102789833</v>
       </c>
       <c r="Q24" s="31" t="n">
         <f aca="false">('Balance Sheet'!Q15+'Balance Sheet'!Q16)</f>
-        <v>32076.4814090676</v>
+        <v>32076.4815214796</v>
       </c>
       <c r="R24" s="31" t="n">
         <f aca="false">('Balance Sheet'!R15+'Balance Sheet'!R16)</f>
-        <v>35985.8606869898</v>
+        <v>35985.8609037257</v>
       </c>
       <c r="S24" s="31" t="n">
         <f aca="false">('Balance Sheet'!S15+'Balance Sheet'!S16)</f>
-        <v>40352.9633609879</v>
+        <v>40352.9637332472</v>
       </c>
       <c r="T24" s="31" t="n">
         <f aca="false">('Balance Sheet'!T15+'Balance Sheet'!T16)</f>
-        <v>45199.3895338186</v>
+        <v>45199.3901263997</v>
       </c>
       <c r="U24" s="31" t="n">
         <f aca="false">('Balance Sheet'!U15+'Balance Sheet'!U16)</f>
-        <v>50538.4564135213</v>
+        <v>50538.4573068796</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="32" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B25" s="71" t="n">
         <f aca="false">IFERROR((B24)/(B23),0)</f>
@@ -15878,43 +16027,43 @@
       </c>
       <c r="L25" s="70" t="n">
         <f aca="false">IFERROR((L24)/(L23),0)</f>
-        <v>80.8083232875014</v>
+        <v>80.8083232876736</v>
       </c>
       <c r="M25" s="70" t="n">
         <f aca="false">IFERROR((M24)/(M23),0)</f>
-        <v>89.6990043065094</v>
+        <v>89.6990043152174</v>
       </c>
       <c r="N25" s="70" t="n">
         <f aca="false">IFERROR((N24)/(N23),0)</f>
-        <v>98.9079167108098</v>
+        <v>98.9079167440355</v>
       </c>
       <c r="O25" s="70" t="n">
         <f aca="false">IFERROR((O24)/(O23),0)</f>
-        <v>110.106987836573</v>
+        <v>110.106987931372</v>
       </c>
       <c r="P25" s="70" t="n">
         <f aca="false">IFERROR((P24)/(P23),0)</f>
-        <v>123.109146663309</v>
+        <v>123.109146886091</v>
       </c>
       <c r="Q25" s="70" t="n">
         <f aca="false">IFERROR((Q24)/(Q23),0)</f>
-        <v>138.052426981139</v>
+        <v>138.052427464943</v>
       </c>
       <c r="R25" s="70" t="n">
         <f aca="false">IFERROR((R24)/(R23),0)</f>
-        <v>154.877816599913</v>
+        <v>154.877817532712</v>
       </c>
       <c r="S25" s="70" t="n">
         <f aca="false">IFERROR((S24)/(S23),0)</f>
-        <v>173.673179948302</v>
+        <v>173.673181550451</v>
       </c>
       <c r="T25" s="70" t="n">
         <f aca="false">IFERROR((T24)/(T23),0)</f>
-        <v>194.53148067062</v>
+        <v>194.531483221002</v>
       </c>
       <c r="U25" s="70" t="n">
         <f aca="false">IFERROR((U24)/(U23),0)</f>
-        <v>217.510034058624</v>
+        <v>217.510037903506</v>
       </c>
     </row>
   </sheetData>

--- a/reports/JSWINFRA/JSW_Infrastructure_Ltd_ERIP_Model.xlsx
+++ b/reports/JSWINFRA/JSW_Infrastructure_Ltd_ERIP_Model.xlsx
@@ -2017,11 +2017,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="9162385"/>
-        <c:axId val="75626988"/>
+        <c:axId val="30115816"/>
+        <c:axId val="24229435"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9162385"/>
+        <c:axId val="30115816"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2054,7 +2054,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75626988"/>
+        <c:crossAx val="24229435"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2062,7 +2062,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75626988"/>
+        <c:axId val="24229435"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2095,7 +2095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9162385"/>
+        <c:crossAx val="30115816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/reports/JSWINFRA/JSW_Infrastructure_Ltd_ERIP_Model.xlsx
+++ b/reports/JSWINFRA/JSW_Infrastructure_Ltd_ERIP_Model.xlsx
@@ -2095,10 +2095,10 @@
                   <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>178.553826483578</c:v>
+                  <c:v>178.553877967152</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>236.410695006873</c:v>
+                  <c:v>236.410746490447</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>357.45</c:v>
@@ -2109,11 +2109,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="13018175"/>
-        <c:axId val="13045619"/>
+        <c:axId val="88051463"/>
+        <c:axId val="27967283"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="13018175"/>
+        <c:axId val="88051463"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2146,7 +2146,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13045619"/>
+        <c:crossAx val="27967283"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2154,7 +2154,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13045619"/>
+        <c:axId val="27967283"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2187,7 +2187,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13018175"/>
+        <c:crossAx val="88051463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2753,11 +2753,11 @@
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">'Income Statement'!L18</f>
-        <v>1526.49308623925</v>
+        <v>1526.49086481146</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">'Income Statement'!M18</f>
-        <v>2347.44288054327</v>
+        <v>2347.43945614069</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2777,11 +2777,11 @@
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">'Income Statement'!L19</f>
-        <v>6.56980024204542</v>
+        <v>6.56979068134909</v>
       </c>
       <c r="G8" s="13" t="n">
         <f aca="false">'Income Statement'!M19</f>
-        <v>10.1030466130547</v>
+        <v>10.103031874933</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">DCF!B45</f>
-        <v>115.301507056065</v>
+        <v>115.301503264642</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B17" s="19" t="n">
         <f aca="false">DCF!B35</f>
-        <v>0.748011685210146</v>
+        <v>0.748011203270923</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">DCF!B34</f>
-        <v>24544.0281082674</v>
+        <v>24544.027253031</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">DCF!B43</f>
-        <v>26790.3051644766</v>
+        <v>26790.3042835395</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B25" s="17" t="n">
         <f aca="false">DCF!B68</f>
-        <v>178.553826483578</v>
+        <v>178.553877967152</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B26" s="17" t="n">
         <f aca="false">DCF!B70</f>
-        <v>236.410695006873</v>
+        <v>236.410746490447</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3309,43 +3309,43 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">'Income Statement'!L12</f>
-        <v>2147.55650263</v>
+        <v>2147.55346393399</v>
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">'Income Statement'!M12</f>
-        <v>3328.01725365247</v>
+        <v>3328.01232689081</v>
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false">'Income Statement'!N12</f>
-        <v>3662.84734514465</v>
+        <v>3662.8406626519</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">'Income Statement'!O12</f>
-        <v>4285.97926058124</v>
+        <v>4285.97253183287</v>
       </c>
       <c r="F8" s="9" t="n">
         <f aca="false">'Income Statement'!P12</f>
-        <v>4739.47863684324</v>
+        <v>4739.47233385641</v>
       </c>
       <c r="G8" s="9" t="n">
         <f aca="false">'Income Statement'!Q12</f>
-        <v>5203.19527355865</v>
+        <v>5203.18942299021</v>
       </c>
       <c r="H8" s="9" t="n">
         <f aca="false">'Income Statement'!R12</f>
-        <v>5634.3713621192</v>
+        <v>5634.36589072376</v>
       </c>
       <c r="I8" s="9" t="n">
         <f aca="false">'Income Statement'!S12</f>
-        <v>6076.61673529211</v>
+        <v>6076.61156728654</v>
       </c>
       <c r="J8" s="9" t="n">
         <f aca="false">'Income Statement'!T12</f>
-        <v>6529.48069109713</v>
+        <v>6529.47576661084</v>
       </c>
       <c r="K8" s="9" t="n">
         <f aca="false">'Income Statement'!U12</f>
-        <v>6979.57946887151</v>
+        <v>6979.57472876916</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3399,43 +3399,43 @@
       </c>
       <c r="B10" s="51" t="n">
         <f aca="false">B8*(1-B9)</f>
-        <v>1675.0940720514</v>
+        <v>1675.09170186851</v>
       </c>
       <c r="C10" s="51" t="n">
         <f aca="false">C8*(1-C9)</f>
-        <v>2595.85345784892</v>
+        <v>2595.84961497483</v>
       </c>
       <c r="D10" s="51" t="n">
         <f aca="false">D8*(1-D9)</f>
-        <v>2857.02092921283</v>
+        <v>2857.01571686848</v>
       </c>
       <c r="E10" s="51" t="n">
         <f aca="false">E8*(1-E9)</f>
-        <v>3343.06382325337</v>
+        <v>3343.05857482964</v>
       </c>
       <c r="F10" s="51" t="n">
         <f aca="false">F8*(1-F9)</f>
-        <v>3696.79333673772</v>
+        <v>3696.788420408</v>
       </c>
       <c r="G10" s="51" t="n">
         <f aca="false">G8*(1-G9)</f>
-        <v>4058.49231337575</v>
+        <v>4058.48774993236</v>
       </c>
       <c r="H10" s="51" t="n">
         <f aca="false">H8*(1-H9)</f>
-        <v>4394.80966245297</v>
+        <v>4394.80539476454</v>
       </c>
       <c r="I10" s="51" t="n">
         <f aca="false">I8*(1-I9)</f>
-        <v>4739.76105352784</v>
+        <v>4739.7570224835</v>
       </c>
       <c r="J10" s="51" t="n">
         <f aca="false">J8*(1-J9)</f>
-        <v>5092.99493905576</v>
+        <v>5092.99109795646</v>
       </c>
       <c r="K10" s="51" t="n">
         <f aca="false">K8*(1-K9)</f>
-        <v>5444.07198571978</v>
+        <v>5444.06828843995</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3444,43 +3444,43 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">'Income Statement'!L11</f>
-        <v>729.87473097</v>
+        <v>729.877769666012</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">'Income Statement'!M11</f>
-        <v>1233.98025619857</v>
+        <v>1233.98518296023</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">'Income Statement'!N11</f>
-        <v>1737.74260515303</v>
+        <v>1737.74928764579</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">'Income Statement'!O11</f>
-        <v>1860.13911528768</v>
+        <v>1860.14584403606</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">'Income Statement'!P11</f>
-        <v>1869.93052683494</v>
+        <v>1869.93682982176</v>
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">'Income Statement'!Q11</f>
-        <v>1866.22876791152</v>
+        <v>1866.23461847997</v>
       </c>
       <c r="H11" s="9" t="n">
         <f aca="false">'Income Statement'!R11</f>
-        <v>1872.5857600267</v>
+        <v>1872.59123142213</v>
       </c>
       <c r="I11" s="9" t="n">
         <f aca="false">'Income Statement'!S11</f>
-        <v>1890.83084369675</v>
+        <v>1890.83601170232</v>
       </c>
       <c r="J11" s="9" t="n">
         <f aca="false">'Income Statement'!T11</f>
-        <v>1918.40397690476</v>
+        <v>1918.40890139105</v>
       </c>
       <c r="K11" s="9" t="n">
         <f aca="false">'Income Statement'!U11</f>
-        <v>1956.12560315075</v>
+        <v>1956.1303432531</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3534,43 +3534,43 @@
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">-Schedules!L12</f>
-        <v>489.373474054859</v>
+        <v>489.375689732458</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">-Schedules!M12</f>
-        <v>-507.136634733478</v>
+        <v>-507.135662715718</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">-Schedules!N12</f>
-        <v>-348.748327177056</v>
+        <v>-348.747615683452</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">-Schedules!O12</f>
-        <v>-274.445813681756</v>
+        <v>-274.445228803412</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">-Schedules!P12</f>
-        <v>-153.771485559746</v>
+        <v>-153.771116969411</v>
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">-Schedules!Q12</f>
-        <v>-174.874091581964</v>
+        <v>-174.873753836994</v>
       </c>
       <c r="H13" s="9" t="n">
         <f aca="false">-Schedules!R12</f>
-        <v>-177.048209415948</v>
+        <v>-177.047864773214</v>
       </c>
       <c r="I13" s="9" t="n">
         <f aca="false">-Schedules!S12</f>
-        <v>-181.437895126113</v>
+        <v>-181.437543097229</v>
       </c>
       <c r="J13" s="9" t="n">
         <f aca="false">-Schedules!T12</f>
-        <v>-183.668914688239</v>
+        <v>-183.668559697665</v>
       </c>
       <c r="K13" s="9" t="n">
         <f aca="false">-Schedules!U12</f>
-        <v>-192.940088074686</v>
+        <v>-192.939713550798</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3579,43 +3579,43 @@
       </c>
       <c r="B14" s="62" t="n">
         <f aca="false">B10+B11+B12+B13</f>
-        <v>-5106.32017732374</v>
+        <v>-5106.31729313302</v>
       </c>
       <c r="C14" s="62" t="n">
         <f aca="false">C10+C11+C12+C13</f>
-        <v>-5177.1212187183</v>
+        <v>-5177.11916281297</v>
       </c>
       <c r="D14" s="62" t="n">
         <f aca="false">D10+D11+D12+D13</f>
-        <v>742.92983402274</v>
+        <v>742.93201566475</v>
       </c>
       <c r="E14" s="62" t="n">
         <f aca="false">E10+E11+E12+E13</f>
-        <v>2927.39504868349</v>
+        <v>2927.39711388648</v>
       </c>
       <c r="F14" s="62" t="n">
         <f aca="false">F10+F11+F12+F13</f>
-        <v>3596.4128615686</v>
+        <v>3596.41461681603</v>
       </c>
       <c r="G14" s="62" t="n">
         <f aca="false">G10+G11+G12+G13</f>
-        <v>3791.9303947104</v>
+        <v>3791.93201958042</v>
       </c>
       <c r="H14" s="62" t="n">
         <f aca="false">H10+H11+H12+H13</f>
-        <v>3954.6099426443</v>
+        <v>3954.61149099402</v>
       </c>
       <c r="I14" s="62" t="n">
         <f aca="false">I10+I11+I12+I13</f>
-        <v>4160.63182515488</v>
+        <v>4160.63331414498</v>
       </c>
       <c r="J14" s="62" t="n">
         <f aca="false">J10+J11+J12+J13</f>
-        <v>4365.26149166322</v>
+        <v>4365.26293004078</v>
       </c>
       <c r="K14" s="62" t="n">
         <f aca="false">K10+K11+K12+K13</f>
-        <v>4577.98820455048</v>
+        <v>4577.98962189689</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3791,43 +3791,43 @@
       </c>
       <c r="B24" s="51" t="n">
         <f aca="false">B14*B21*B23</f>
-        <v>-3677.2753553481</v>
+        <v>-3677.27327832138</v>
       </c>
       <c r="C24" s="51" t="n">
         <f aca="false">C14*C21*C23</f>
-        <v>-4518.07009701959</v>
+        <v>-4518.06830283244</v>
       </c>
       <c r="D24" s="51" t="n">
         <f aca="false">D14*D21*D23</f>
-        <v>581.447636521486</v>
+        <v>581.449343964816</v>
       </c>
       <c r="E24" s="51" t="n">
         <f aca="false">E14*E21*E23</f>
-        <v>2054.67115786638</v>
+        <v>2054.67260738479</v>
       </c>
       <c r="F24" s="51" t="n">
         <f aca="false">F14*F21*F23</f>
-        <v>2263.75130011394</v>
+        <v>2263.75240494918</v>
       </c>
       <c r="G24" s="51" t="n">
         <f aca="false">G14*G21*G23</f>
-        <v>2140.51219918807</v>
+        <v>2140.51311641327</v>
       </c>
       <c r="H24" s="51" t="n">
         <f aca="false">H14*H21*H23</f>
-        <v>2001.97746411392</v>
+        <v>2001.97824794882</v>
       </c>
       <c r="I24" s="51" t="n">
         <f aca="false">I14*I21*I23</f>
-        <v>1888.91753022512</v>
+        <v>1888.9182062233</v>
       </c>
       <c r="J24" s="51" t="n">
         <f aca="false">J14*J21*J23</f>
-        <v>1777.3057856134</v>
+        <v>1777.30637124538</v>
       </c>
       <c r="K24" s="51" t="n">
         <f aca="false">K14*K21*K23</f>
-        <v>1671.57065988248</v>
+        <v>1671.57117740121</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="B31" s="51" t="n">
         <f aca="false">SUM(B24:K24)</f>
-        <v>6184.80828115711</v>
+        <v>6184.81989437695</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B32" s="51" t="n">
         <f aca="false">K10*(1+$B$28)*(1-$B$28/$B$29)/($B$27-$B$28)</f>
-        <v>50281.0283946773</v>
+        <v>50280.9942468864</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B33" s="51" t="n">
         <f aca="false">$B$32/(1+$B$27)^K22</f>
-        <v>18359.2198271103</v>
+        <v>18359.2073586541</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B34" s="62" t="n">
         <f aca="false">$B$31+$B$33</f>
-        <v>24544.0281082674</v>
+        <v>24544.027253031</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="B35" s="15" t="n">
         <f aca="false">$B$33/$B$34</f>
-        <v>0.748011685210146</v>
+        <v>0.748011203270923</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B40" s="51" t="n">
         <f aca="false">$B$34-$B$36-$B$37-$B$38+$B$39</f>
-        <v>26008.7181082674</v>
+        <v>26008.717253031</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="B43" s="62" t="n">
         <f aca="false">$B$40*$B$42</f>
-        <v>26790.3051644766</v>
+        <v>26790.3042835395</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B45" s="47" t="n">
         <f aca="false">$B$43/$B$44</f>
-        <v>115.301507056065</v>
+        <v>115.301503264642</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="B47" s="15" t="n">
         <f aca="false">$B$45/$B$46-1</f>
-        <v>-0.677433187701596</v>
+        <v>-0.677433198308457</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B52" s="46" t="n">
         <f aca="false">IF($B$50="Exit multiple",$B$68,$B$45)</f>
-        <v>115.301507056065</v>
+        <v>115.301503264642</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="B53" s="13" t="n">
         <f aca="false">IFERROR(Schedules!L22/Schedules!L23,0)</f>
-        <v>0.78837602904361</v>
+        <v>0.788374881761891</v>
       </c>
       <c r="C53" s="70" t="s">
         <v>320</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="B54" s="46" t="n">
         <f aca="false">$B$52*(1+$B$41)^($B$51/12)-$B$53*$B$51/12</f>
-        <v>128.73153636964</v>
+        <v>128.731533257959</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B64" s="83" t="n">
         <f aca="false">$B$32/$B$63</f>
-        <v>5.62697940334977</v>
+        <v>5.62697558185044</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="B68" s="47" t="n">
         <f aca="false">($B$31+$B$67-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
-        <v>178.553826483578</v>
+        <v>178.553877967152</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="B70" s="46" t="n">
         <f aca="false">($B$31+$B$69*$B$63/(1+$B$27)^K22-$B$36-$B$37-$B$38+$B$39)*$B$42/$B$44</f>
-        <v>236.410695006873</v>
+        <v>236.410746490447</v>
       </c>
     </row>
   </sheetData>
@@ -4312,23 +4312,23 @@
       </c>
       <c r="B9" s="46" t="n">
         <f aca="false">IF(B$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A9-B$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>135.69902817475</v>
+        <v>135.699014378473</v>
       </c>
       <c r="C9" s="46" t="n">
         <f aca="false">IF(C$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A9-C$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>137.349965815455</v>
+        <v>137.349950897963</v>
       </c>
       <c r="D9" s="46" t="n">
         <f aca="false">IF(D$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A9-D$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>139.193290901336</v>
+        <v>139.193274731971</v>
       </c>
       <c r="E9" s="46" t="n">
         <f aca="false">IF(E$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A9-E$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>141.277044885879</v>
+        <v>141.277027301356</v>
       </c>
       <c r="F9" s="46" t="n">
         <f aca="false">IF(F$8&gt;=$A9,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A9)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A9-F$8)/(1+$A9)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>143.666716889679</v>
+        <v>143.666697682237</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4338,23 +4338,23 @@
       </c>
       <c r="B10" s="46" t="n">
         <f aca="false">IF(B$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A10-B$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>124.123221410054</v>
+        <v>124.123213519133</v>
       </c>
       <c r="C10" s="46" t="n">
         <f aca="false">IF(C$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A10-C$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>125.207991545919</v>
+        <v>125.207982918288</v>
       </c>
       <c r="D10" s="46" t="n">
         <f aca="false">IF(D$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A10-D$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>126.392949001159</v>
+        <v>126.392939568778</v>
       </c>
       <c r="E10" s="46" t="n">
         <f aca="false">IF(E$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A10-E$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>127.701189338508</v>
+        <v>127.701179017651</v>
       </c>
       <c r="F10" s="46" t="n">
         <f aca="false">IF(F$8&gt;=$A10,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A10)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A10-F$8)/(1+$A10)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>129.16349777288</v>
+        <v>129.163486458912</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4364,23 +4364,23 @@
       </c>
       <c r="B11" s="46" t="n">
         <f aca="false">IF(B$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A11-B$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>113.934890342633</v>
+        <v>113.934887479332</v>
       </c>
       <c r="C11" s="46" t="n">
         <f aca="false">IF(C$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A11-C$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>114.598457737469</v>
+        <v>114.598454423514</v>
       </c>
       <c r="D11" s="47" t="n">
         <f aca="false">IF(D$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A11-D$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>115.301507056065</v>
+        <v>115.301503264642</v>
       </c>
       <c r="E11" s="46" t="n">
         <f aca="false">IF(E$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A11-E$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>116.052490355191</v>
+        <v>116.052486053747</v>
       </c>
       <c r="F11" s="46" t="n">
         <f aca="false">IF(F$8&gt;=$A11,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A11)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A11-F$8)/(1+$A11)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>116.862457558745</v>
+        <v>116.862452707221</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4390,23 +4390,23 @@
       </c>
       <c r="B12" s="46" t="n">
         <f aca="false">IF(B$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A12-B$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>104.902926393313</v>
+        <v>104.902927834298</v>
       </c>
       <c r="C12" s="46" t="n">
         <f aca="false">IF(C$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A12-C$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>105.251656697979</v>
+        <v>105.251657902128</v>
       </c>
       <c r="D12" s="46" t="n">
         <f aca="false">IF(D$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A12-D$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>105.599941918499</v>
+        <v>105.599942886115</v>
       </c>
       <c r="E12" s="46" t="n">
         <f aca="false">IF(E$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A12-E$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>105.947693120103</v>
+        <v>105.947693851547</v>
       </c>
       <c r="F12" s="46" t="n">
         <f aca="false">IF(F$8&gt;=$A12,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A12)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A12-F$8)/(1+$A12)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>106.294795983178</v>
+        <v>106.294796478891</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4416,23 +4416,23 @@
       </c>
       <c r="B13" s="46" t="n">
         <f aca="false">IF(B$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+B$8)*(1-B$8/DCF!$B$29)/($A13-B$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>96.8448211995322</v>
+        <v>96.844826342979</v>
       </c>
       <c r="C13" s="46" t="n">
         <f aca="false">IF(C$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+C$8)*(1-C$8/DCF!$B$29)/($A13-C$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>96.9577233000628</v>
+        <v>96.9577283668334</v>
       </c>
       <c r="D13" s="46" t="n">
         <f aca="false">IF(D$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+D$8)*(1-D$8/DCF!$B$29)/($A13-D$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>97.044156120143</v>
+        <v>97.0441611282137</v>
       </c>
       <c r="E13" s="46" t="n">
         <f aca="false">IF(E$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+E$8)*(1-E$8/DCF!$B$29)/($A13-E$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>97.0991609589645</v>
+        <v>97.0991659296792</v>
       </c>
       <c r="F13" s="46" t="n">
         <f aca="false">IF(F$8&gt;=$A13,NA(),(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A13)^DCF!$B$22:$K$22)+DCF!$K$10*(1+F$8)*(1-F$8/DCF!$B$29)/($A13-F$8)/(1+$A13)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44)</f>
-        <v>97.1164580144396</v>
+        <v>97.1164629734073</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4472,23 +4472,23 @@
       </c>
       <c r="B17" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>131.462439805433</v>
+        <v>131.462492947505</v>
       </c>
       <c r="C17" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>162.904774998597</v>
+        <v>162.904828140668</v>
       </c>
       <c r="D17" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>194.34711019176</v>
+        <v>194.347163333832</v>
       </c>
       <c r="E17" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>225.789445384923</v>
+        <v>225.789498526995</v>
       </c>
       <c r="F17" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A17)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A17)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>257.231780578086</v>
+        <v>257.231833720158</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4498,23 +4498,23 @@
       </c>
       <c r="B18" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>125.963076500692</v>
+        <v>125.963128801332</v>
       </c>
       <c r="C18" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>156.119449667511</v>
+        <v>156.119501968151</v>
       </c>
       <c r="D18" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>186.27582283433</v>
+        <v>186.27587513497</v>
       </c>
       <c r="E18" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>216.432196001149</v>
+        <v>216.432248301789</v>
       </c>
       <c r="F18" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A18)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A18)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>246.588569167967</v>
+        <v>246.588621468607</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4524,23 +4524,23 @@
       </c>
       <c r="B19" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>120.696957960283</v>
+        <v>120.697009443856</v>
       </c>
       <c r="C19" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>149.62539222193</v>
+        <v>149.625443705504</v>
       </c>
       <c r="D19" s="47" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>178.553826483578</v>
+        <v>178.553877967152</v>
       </c>
       <c r="E19" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>207.482260745226</v>
+        <v>207.482312228799</v>
       </c>
       <c r="F19" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A19)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A19)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>236.410695006873</v>
+        <v>236.410746490447</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4550,23 +4550,23 @@
       </c>
       <c r="B20" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>115.653080868212</v>
+        <v>115.653131558174</v>
       </c>
       <c r="C20" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>143.40873853744</v>
+        <v>143.408789227401</v>
       </c>
       <c r="D20" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>171.164396206667</v>
+        <v>171.164446896628</v>
       </c>
       <c r="E20" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>198.920053875894</v>
+        <v>198.920104565855</v>
       </c>
       <c r="F20" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A20)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A20)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>226.675711545121</v>
+        <v>226.675762235082</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4576,23 +4576,23 @@
       </c>
       <c r="B21" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+B$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>110.821012631689</v>
+        <v>110.821062550623</v>
       </c>
       <c r="C21" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+C$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>137.456348129428</v>
+        <v>137.456398048362</v>
       </c>
       <c r="D21" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+D$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>164.091683627167</v>
+        <v>164.091733546101</v>
       </c>
       <c r="E21" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+E$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>190.727019124905</v>
+        <v>190.727069043839</v>
       </c>
       <c r="F21" s="46" t="n">
         <f aca="false">(SUMPRODUCT(DCF!$B$14:$K$14,DCF!$B$21:$K$21,1/(1+$A21)^DCF!$B$22:$K$22)+F$16*DCF!$B$63/(1+$A21)^DCF!$K$22-DCF!$B$36-DCF!$B$37-DCF!$B$38+DCF!$B$39)*DCF!$B$42/DCF!$B$44</f>
-        <v>217.362354622644</v>
+        <v>217.362404541578</v>
       </c>
     </row>
   </sheetData>
@@ -5137,43 +5137,43 @@
       </c>
       <c r="L6" s="88" t="n">
         <f aca="false">('Balance Sheet'!L13-'Balance Sheet'!L22)</f>
-        <v>5.32287231180817E-007</v>
+        <v>0</v>
       </c>
       <c r="M6" s="88" t="n">
         <f aca="false">('Balance Sheet'!M13-'Balance Sheet'!M22)</f>
-        <v>5.32279955223203E-007</v>
+        <v>0</v>
       </c>
       <c r="N6" s="88" t="n">
         <f aca="false">('Balance Sheet'!N13-'Balance Sheet'!N22)</f>
-        <v>5.32294507138431E-007</v>
+        <v>0</v>
       </c>
       <c r="O6" s="88" t="n">
         <f aca="false">('Balance Sheet'!O13-'Balance Sheet'!O22)</f>
-        <v>5.32294507138431E-007</v>
+        <v>0</v>
       </c>
       <c r="P6" s="88" t="n">
         <f aca="false">('Balance Sheet'!P13-'Balance Sheet'!P22)</f>
-        <v>5.32294507138431E-007</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="88" t="n">
         <f aca="false">('Balance Sheet'!Q13-'Balance Sheet'!Q22)</f>
-        <v>5.32294507138431E-007</v>
+        <v>0</v>
       </c>
       <c r="R6" s="88" t="n">
         <f aca="false">('Balance Sheet'!R13-'Balance Sheet'!R22)</f>
-        <v>5.32287231180817E-007</v>
+        <v>0</v>
       </c>
       <c r="S6" s="88" t="n">
         <f aca="false">('Balance Sheet'!S13-'Balance Sheet'!S22)</f>
-        <v>5.32294507138431E-007</v>
+        <v>0</v>
       </c>
       <c r="T6" s="88" t="n">
         <f aca="false">('Balance Sheet'!T13-'Balance Sheet'!T22)</f>
-        <v>5.32287231180817E-007</v>
+        <v>0</v>
       </c>
       <c r="U6" s="88" t="n">
         <f aca="false">('Balance Sheet'!U13-'Balance Sheet'!U22)</f>
-        <v>5.32279955223203E-007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="D7" s="88" t="n">
         <f aca="false">('Balance Sheet'!D6-'Cash Flow'!D23)</f>
-        <v>7.87999999999984</v>
+        <v>7.87999999999973</v>
       </c>
       <c r="E7" s="88" t="n">
         <f aca="false">('Balance Sheet'!E6-'Cash Flow'!E23)</f>
@@ -5202,11 +5202,11 @@
       </c>
       <c r="G7" s="88" t="n">
         <f aca="false">('Balance Sheet'!G6-'Cash Flow'!G23)</f>
-        <v>53</v>
+        <v>53.0000000000011</v>
       </c>
       <c r="H7" s="88" t="n">
         <f aca="false">('Balance Sheet'!H6-'Cash Flow'!H23)</f>
-        <v>-17.3399999999992</v>
+        <v>-17.3399999999995</v>
       </c>
       <c r="I7" s="88" t="n">
         <f aca="false">('Balance Sheet'!I6-'Cash Flow'!I23)</f>
@@ -5214,11 +5214,11 @@
       </c>
       <c r="J7" s="88" t="n">
         <f aca="false">('Balance Sheet'!J6-'Cash Flow'!J23)</f>
-        <v>333.339999999999</v>
+        <v>333.339999999998</v>
       </c>
       <c r="K7" s="88" t="n">
         <f aca="false">('Balance Sheet'!K6-'Cash Flow'!K23)</f>
-        <v>-155.04</v>
+        <v>-155.039999999998</v>
       </c>
       <c r="L7" s="88" t="n">
         <f aca="false">('Balance Sheet'!L6-'Cash Flow'!L23)</f>
@@ -5502,43 +5502,43 @@
       </c>
       <c r="L11" s="88" t="n">
         <f aca="false">('Balance Sheet'!L6-Drivers!L29)</f>
-        <v>3323.80622844811</v>
+        <v>3323.81209652668</v>
       </c>
       <c r="M11" s="88" t="n">
         <f aca="false">('Balance Sheet'!M6-Drivers!M29)</f>
-        <v>1.55976022142568E-005</v>
+        <v>0</v>
       </c>
       <c r="N11" s="88" t="n">
         <f aca="false">('Balance Sheet'!N6-Drivers!N29)</f>
-        <v>4.67905548475756E-005</v>
+        <v>0</v>
       </c>
       <c r="O11" s="88" t="n">
         <f aca="false">('Balance Sheet'!O6-Drivers!O29)</f>
-        <v>0.00012698123566679</v>
+        <v>0</v>
       </c>
       <c r="P11" s="88" t="n">
         <f aca="false">('Balance Sheet'!P6-Drivers!P29)</f>
-        <v>0.000294910974957929</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="88" t="n">
         <f aca="false">('Balance Sheet'!Q6-Drivers!Q29)</f>
-        <v>2827.89145521328</v>
+        <v>2827.91694206513</v>
       </c>
       <c r="R11" s="88" t="n">
         <f aca="false">('Balance Sheet'!R6-Drivers!R29)</f>
-        <v>5924.43149620052</v>
+        <v>5924.4604721614</v>
       </c>
       <c r="S11" s="88" t="n">
         <f aca="false">('Balance Sheet'!S6-Drivers!S29)</f>
-        <v>9332.10078483102</v>
+        <v>9332.1331889244</v>
       </c>
       <c r="T11" s="88" t="n">
         <f aca="false">('Balance Sheet'!T6-Drivers!T29)</f>
-        <v>13072.4160370738</v>
+        <v>13072.4517556079</v>
       </c>
       <c r="U11" s="88" t="n">
         <f aca="false">('Balance Sheet'!U6-Drivers!U29)</f>
-        <v>17146.7518060995</v>
+        <v>17146.7907016149</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5591,19 +5591,19 @@
       </c>
       <c r="M12" s="88" t="n">
         <f aca="false">'Balance Sheet'!M18</f>
-        <v>3392.09243648074</v>
+        <v>3392.08254230954</v>
       </c>
       <c r="N12" s="88" t="n">
         <f aca="false">'Balance Sheet'!N18</f>
-        <v>4104.8176354869</v>
+        <v>4104.80350792532</v>
       </c>
       <c r="O12" s="88" t="n">
         <f aca="false">'Balance Sheet'!O18</f>
-        <v>2535.31710340578</v>
+        <v>2535.29876153588</v>
       </c>
       <c r="P12" s="88" t="n">
         <f aca="false">'Balance Sheet'!P18</f>
-        <v>12.1364265639545</v>
+        <v>12.1142147135079</v>
       </c>
       <c r="Q12" s="88" t="n">
         <f aca="false">'Balance Sheet'!Q18</f>
@@ -5672,43 +5672,43 @@
       </c>
       <c r="L13" s="88" t="n">
         <f aca="false">'Balance Sheet'!L10</f>
-        <v>17797.87772343</v>
+        <v>17797.874684734</v>
       </c>
       <c r="M13" s="88" t="n">
         <f aca="false">'Balance Sheet'!M10</f>
-        <v>25063.7157652637</v>
+        <v>25063.7077998061</v>
       </c>
       <c r="N13" s="88" t="n">
         <f aca="false">'Balance Sheet'!N10</f>
-        <v>26829.0585332768</v>
+        <v>26829.0438853264</v>
       </c>
       <c r="O13" s="88" t="n">
         <f aca="false">'Balance Sheet'!O10</f>
-        <v>26970.2814941649</v>
+        <v>26970.2601174661</v>
       </c>
       <c r="P13" s="88" t="n">
         <f aca="false">'Balance Sheet'!P10</f>
-        <v>26916.8904837743</v>
+        <v>26916.8628040887</v>
       </c>
       <c r="Q13" s="88" t="n">
         <f aca="false">'Balance Sheet'!Q10</f>
-        <v>27008.5783108577</v>
+        <v>27008.5447806036</v>
       </c>
       <c r="R13" s="88" t="n">
         <f aca="false">'Balance Sheet'!R10</f>
-        <v>27271.7298212504</v>
+        <v>27271.6908196009</v>
       </c>
       <c r="S13" s="88" t="n">
         <f aca="false">'Balance Sheet'!S10</f>
-        <v>27669.4211544973</v>
+        <v>27669.3769848422</v>
       </c>
       <c r="T13" s="88" t="n">
         <f aca="false">'Balance Sheet'!T10</f>
-        <v>28213.4856872016</v>
+        <v>28213.4365930602</v>
       </c>
       <c r="U13" s="88" t="n">
         <f aca="false">'Balance Sheet'!U10</f>
-        <v>28886.6293802962</v>
+        <v>28886.5755460525</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5757,43 +5757,43 @@
       </c>
       <c r="L14" s="88" t="n">
         <f aca="false">Schedules!L24</f>
-        <v>18775.813915891</v>
+        <v>18775.8119610341</v>
       </c>
       <c r="M14" s="88" t="n">
         <f aca="false">Schedules!M24</f>
-        <v>20841.5636526408</v>
+        <v>20841.5586824379</v>
       </c>
       <c r="N14" s="88" t="n">
         <f aca="false">Schedules!N24</f>
-        <v>22981.2544554766</v>
+        <v>22981.2454685029</v>
       </c>
       <c r="O14" s="88" t="n">
         <f aca="false">Schedules!O24</f>
-        <v>25583.3586458543</v>
+        <v>25583.3458012008</v>
       </c>
       <c r="P14" s="88" t="n">
         <f aca="false">Schedules!P24</f>
-        <v>28604.4102789833</v>
+        <v>28604.3940374203</v>
       </c>
       <c r="Q14" s="88" t="n">
         <f aca="false">Schedules!Q24</f>
-        <v>32076.4815214796</v>
+        <v>32076.4622698978</v>
       </c>
       <c r="R14" s="88" t="n">
         <f aca="false">Schedules!R24</f>
-        <v>35985.8609037257</v>
+        <v>35985.8389255991</v>
       </c>
       <c r="S14" s="88" t="n">
         <f aca="false">Schedules!S24</f>
-        <v>40352.9637332472</v>
+        <v>40352.9392550386</v>
       </c>
       <c r="T14" s="88" t="n">
         <f aca="false">Schedules!T24</f>
-        <v>45199.3901263997</v>
+        <v>45199.3632715408</v>
       </c>
       <c r="U14" s="88" t="n">
         <f aca="false">Schedules!U24</f>
-        <v>50538.4573068796</v>
+        <v>50538.4280801126</v>
       </c>
     </row>
   </sheetData>
@@ -6146,13 +6146,13 @@
         <v>5</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>2100001567</v>
+        <v>210.0001567</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>232.35</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>100</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6781,43 +6781,43 @@
       </c>
       <c r="L10" s="34" t="n">
         <f aca="false">'Income Statement'!L12</f>
-        <v>2147.55650263</v>
+        <v>2147.55346393399</v>
       </c>
       <c r="M10" s="34" t="n">
         <f aca="false">'Income Statement'!M12</f>
-        <v>3328.01725365247</v>
+        <v>3328.01232689081</v>
       </c>
       <c r="N10" s="34" t="n">
         <f aca="false">'Income Statement'!N12</f>
-        <v>3662.84734514465</v>
+        <v>3662.8406626519</v>
       </c>
       <c r="O10" s="34" t="n">
         <f aca="false">'Income Statement'!O12</f>
-        <v>4285.97926058124</v>
+        <v>4285.97253183287</v>
       </c>
       <c r="P10" s="34" t="n">
         <f aca="false">'Income Statement'!P12</f>
-        <v>4739.47863684324</v>
+        <v>4739.47233385641</v>
       </c>
       <c r="Q10" s="34" t="n">
         <f aca="false">'Income Statement'!Q12</f>
-        <v>5203.19527355865</v>
+        <v>5203.18942299021</v>
       </c>
       <c r="R10" s="34" t="n">
         <f aca="false">'Income Statement'!R12</f>
-        <v>5634.3713621192</v>
+        <v>5634.36589072376</v>
       </c>
       <c r="S10" s="34" t="n">
         <f aca="false">'Income Statement'!S12</f>
-        <v>6076.61673529211</v>
+        <v>6076.61156728654</v>
       </c>
       <c r="T10" s="34" t="n">
         <f aca="false">'Income Statement'!T12</f>
-        <v>6529.48069109713</v>
+        <v>6529.47576661084</v>
       </c>
       <c r="U10" s="34" t="n">
         <f aca="false">'Income Statement'!U12</f>
-        <v>6979.57946887151</v>
+        <v>6979.57472876916</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6866,43 +6866,43 @@
       </c>
       <c r="L11" s="34" t="n">
         <f aca="false">'Income Statement'!L18</f>
-        <v>1526.49308623925</v>
+        <v>1526.49086481146</v>
       </c>
       <c r="M11" s="34" t="n">
         <f aca="false">'Income Statement'!M18</f>
-        <v>2347.44288054327</v>
+        <v>2347.43945614069</v>
       </c>
       <c r="N11" s="34" t="n">
         <f aca="false">'Income Statement'!N18</f>
-        <v>2431.46681502389</v>
+        <v>2431.46225689205</v>
       </c>
       <c r="O11" s="34" t="n">
         <f aca="false">'Income Statement'!O18</f>
-        <v>2956.93656265893</v>
+        <v>2956.93219624757</v>
       </c>
       <c r="P11" s="34" t="n">
         <f aca="false">'Income Statement'!P18</f>
-        <v>3433.01317924968</v>
+        <v>3433.00935934038</v>
       </c>
       <c r="Q11" s="34" t="n">
         <f aca="false">'Income Statement'!Q18</f>
-        <v>3945.5354008047</v>
+        <v>3945.53208236083</v>
       </c>
       <c r="R11" s="34" t="n">
         <f aca="false">'Income Statement'!R18</f>
-        <v>4442.47635944327</v>
+        <v>4442.47347238776</v>
       </c>
       <c r="S11" s="34" t="n">
         <f aca="false">'Income Statement'!S18</f>
-        <v>4962.61648578567</v>
+        <v>4962.61401072679</v>
       </c>
       <c r="T11" s="34" t="n">
         <f aca="false">'Income Statement'!T18</f>
-        <v>5507.30213294144</v>
+        <v>5507.30001875247</v>
       </c>
       <c r="U11" s="34" t="n">
         <f aca="false">'Income Statement'!U18</f>
-        <v>6067.12090646413</v>
+        <v>6067.11910064979</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6911,39 +6911,39 @@
       </c>
       <c r="B12" s="35" t="n">
         <f aca="false">'Income Statement'!B19</f>
-        <v>5.46003393773728E-006</v>
+        <v>54.6003393773728</v>
       </c>
       <c r="C12" s="35" t="n">
         <f aca="false">'Income Statement'!C19</f>
-        <v>4.4091582935266E-006</v>
+        <v>44.091582935266</v>
       </c>
       <c r="D12" s="35" t="n">
         <f aca="false">'Income Statement'!D19</f>
-        <v>4.39334541261736E-006</v>
+        <v>43.9334541261736</v>
       </c>
       <c r="E12" s="35" t="n">
         <f aca="false">'Income Statement'!E19</f>
-        <v>3.1774160175674E-006</v>
+        <v>31.774160175674</v>
       </c>
       <c r="F12" s="35" t="n">
         <f aca="false">'Income Statement'!F19</f>
-        <v>4.86207057661374E-006</v>
+        <v>48.6207057661374</v>
       </c>
       <c r="G12" s="35" t="n">
         <f aca="false">'Income Statement'!G19</f>
-        <v>5.40191143494138E-006</v>
+        <v>54.0191143494139</v>
       </c>
       <c r="H12" s="35" t="n">
         <f aca="false">'Income Statement'!H19</f>
-        <v>3.96759287897949E-007</v>
+        <v>3.96759287897949</v>
       </c>
       <c r="I12" s="35" t="n">
         <f aca="false">'Income Statement'!I19</f>
-        <v>5.50432922605529E-007</v>
+        <v>5.50432922605529</v>
       </c>
       <c r="J12" s="35" t="n">
         <f aca="false">'Income Statement'!J19</f>
-        <v>7.1575184686517E-007</v>
+        <v>7.1575184686517</v>
       </c>
       <c r="K12" s="35" t="n">
         <f aca="false">'Income Statement'!K19</f>
@@ -6951,43 +6951,43 @@
       </c>
       <c r="L12" s="36" t="n">
         <f aca="false">'Income Statement'!L19</f>
-        <v>6.56980024204542</v>
+        <v>6.56979068134909</v>
       </c>
       <c r="M12" s="36" t="n">
         <f aca="false">'Income Statement'!M19</f>
-        <v>10.1030466130547</v>
+        <v>10.103031874933</v>
       </c>
       <c r="N12" s="36" t="n">
         <f aca="false">'Income Statement'!N19</f>
-        <v>10.4646731871052</v>
+        <v>10.4646535695806</v>
       </c>
       <c r="O12" s="36" t="n">
         <f aca="false">'Income Statement'!O19</f>
-        <v>12.7262171838129</v>
+        <v>12.7261983914249</v>
       </c>
       <c r="P12" s="36" t="n">
         <f aca="false">'Income Statement'!P19</f>
-        <v>14.7751804572829</v>
+        <v>14.7751640169588</v>
       </c>
       <c r="Q12" s="36" t="n">
         <f aca="false">'Income Statement'!Q19</f>
-        <v>16.9810002186559</v>
+        <v>16.9809859365648</v>
       </c>
       <c r="R12" s="36" t="n">
         <f aca="false">'Income Statement'!R19</f>
-        <v>19.1197605312816</v>
+        <v>19.1197481058221</v>
       </c>
       <c r="S12" s="36" t="n">
         <f aca="false">'Income Statement'!S19</f>
-        <v>21.3583666270096</v>
+        <v>21.3583559747226</v>
       </c>
       <c r="T12" s="36" t="n">
         <f aca="false">'Income Statement'!T19</f>
-        <v>23.7026130102924</v>
+        <v>23.7026039111361</v>
       </c>
       <c r="U12" s="36" t="n">
         <f aca="false">'Income Statement'!U19</f>
-        <v>26.1119901289612</v>
+        <v>26.1119823570036</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D14" s="30" t="n">
         <f aca="false">(((('Income Statement'!D12*(1-Drivers!D22))+'Income Statement'!D11)-Schedules!D7)-Schedules!D12)</f>
-        <v>-51.5103720405863</v>
+        <v>-51.5103720405862</v>
       </c>
       <c r="E14" s="30" t="n">
         <f aca="false">(((('Income Statement'!E12*(1-Drivers!E22))+'Income Statement'!E11)-Schedules!E7)-Schedules!E12)</f>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G14" s="30" t="n">
         <f aca="false">(((('Income Statement'!G12*(1-Drivers!G22))+'Income Statement'!G11)-Schedules!G7)-Schedules!G12)</f>
-        <v>-939.766439269449</v>
+        <v>-939.76643926945</v>
       </c>
       <c r="H14" s="30" t="n">
         <f aca="false">(((('Income Statement'!H12*(1-Drivers!H22))+'Income Statement'!H11)-Schedules!H7)-Schedules!H12)</f>
@@ -7053,51 +7053,51 @@
       </c>
       <c r="J14" s="30" t="n">
         <f aca="false">(((('Income Statement'!J12*(1-Drivers!J22))+'Income Statement'!J11)-Schedules!J7)-Schedules!J12)</f>
-        <v>-305.499506556322</v>
+        <v>-305.499506556321</v>
       </c>
       <c r="K14" s="30" t="n">
         <f aca="false">(((('Income Statement'!K12*(1-Drivers!K22))+'Income Statement'!K11)-Schedules!K7)-Schedules!K12)</f>
-        <v>-572.355687832383</v>
+        <v>-572.355687832385</v>
       </c>
       <c r="L14" s="31" t="n">
         <f aca="false">(((('Income Statement'!L12*(1-Drivers!L22))+'Income Statement'!L11)-Schedules!L7)-Schedules!L12)</f>
-        <v>-5106.32017732374</v>
+        <v>-5106.31729313302</v>
       </c>
       <c r="M14" s="31" t="n">
         <f aca="false">(((('Income Statement'!M12*(1-Drivers!M22))+'Income Statement'!M11)-Schedules!M7)-Schedules!M12)</f>
-        <v>-5177.1212187183</v>
+        <v>-5177.11916281297</v>
       </c>
       <c r="N14" s="31" t="n">
         <f aca="false">(((('Income Statement'!N12*(1-Drivers!N22))+'Income Statement'!N11)-Schedules!N7)-Schedules!N12)</f>
-        <v>742.92983402274</v>
+        <v>742.93201566475</v>
       </c>
       <c r="O14" s="31" t="n">
         <f aca="false">(((('Income Statement'!O12*(1-Drivers!O22))+'Income Statement'!O11)-Schedules!O7)-Schedules!O12)</f>
-        <v>2927.39504868349</v>
+        <v>2927.39711388648</v>
       </c>
       <c r="P14" s="31" t="n">
         <f aca="false">(((('Income Statement'!P12*(1-Drivers!P22))+'Income Statement'!P11)-Schedules!P7)-Schedules!P12)</f>
-        <v>3596.4128615686</v>
+        <v>3596.41461681603</v>
       </c>
       <c r="Q14" s="31" t="n">
         <f aca="false">(((('Income Statement'!Q12*(1-Drivers!Q22))+'Income Statement'!Q11)-Schedules!Q7)-Schedules!Q12)</f>
-        <v>3791.9303947104</v>
+        <v>3791.93201958042</v>
       </c>
       <c r="R14" s="31" t="n">
         <f aca="false">(((('Income Statement'!R12*(1-Drivers!R22))+'Income Statement'!R11)-Schedules!R7)-Schedules!R12)</f>
-        <v>3954.6099426443</v>
+        <v>3954.61149099402</v>
       </c>
       <c r="S14" s="31" t="n">
         <f aca="false">(((('Income Statement'!S12*(1-Drivers!S22))+'Income Statement'!S11)-Schedules!S7)-Schedules!S12)</f>
-        <v>4160.63182515488</v>
+        <v>4160.63331414498</v>
       </c>
       <c r="T14" s="31" t="n">
         <f aca="false">(((('Income Statement'!T12*(1-Drivers!T22))+'Income Statement'!T11)-Schedules!T7)-Schedules!T12)</f>
-        <v>4365.26149166322</v>
+        <v>4365.26293004078</v>
       </c>
       <c r="U14" s="31" t="n">
         <f aca="false">(((('Income Statement'!U12*(1-Drivers!U22))+'Income Statement'!U11)-Schedules!U7)-Schedules!U12)</f>
-        <v>4577.98820455048</v>
+        <v>4577.98962189689</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7126,19 +7126,19 @@
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">(((('Income Statement'!G18+'Income Statement'!G11)-Schedules!G7)-Schedules!G12)+('Balance Sheet'!G19-'Balance Sheet'!F19))</f>
-        <v>-387.11</v>
+        <v>-387.110000000001</v>
       </c>
       <c r="H15" s="9" t="n">
         <f aca="false">(((('Income Statement'!H18+'Income Statement'!H11)-Schedules!H7)-Schedules!H12)+('Balance Sheet'!H19-'Balance Sheet'!G19))</f>
-        <v>601.089999999999</v>
+        <v>601.09</v>
       </c>
       <c r="I15" s="9" t="n">
         <f aca="false">(((('Income Statement'!I18+'Income Statement'!I11)-Schedules!I7)-Schedules!I12)+('Balance Sheet'!I19-'Balance Sheet'!H19))</f>
-        <v>-393.76</v>
+        <v>-393.760000000001</v>
       </c>
       <c r="J15" s="9" t="n">
         <f aca="false">(((('Income Statement'!J18+'Income Statement'!J11)-Schedules!J7)-Schedules!J12)+('Balance Sheet'!J19-'Balance Sheet'!I19))</f>
-        <v>50.8600000000013</v>
+        <v>50.8600000000019</v>
       </c>
       <c r="K15" s="9" t="n">
         <f aca="false">(((('Income Statement'!K18+'Income Statement'!K11)-Schedules!K7)-Schedules!K12)+('Balance Sheet'!K19-'Balance Sheet'!J19))</f>
@@ -7146,43 +7146,43 @@
       </c>
       <c r="L15" s="34" t="n">
         <f aca="false">(((('Income Statement'!L18+'Income Statement'!L11)-Schedules!L7)-Schedules!L12)+('Balance Sheet'!L19-'Balance Sheet'!K19))</f>
-        <v>-5254.92116313589</v>
+        <v>-5254.91813019007</v>
       </c>
       <c r="M15" s="34" t="n">
         <f aca="false">(((('Income Statement'!M18+'Income Statement'!M11)-Schedules!M7)-Schedules!M12)+('Balance Sheet'!M19-'Balance Sheet'!L19))</f>
-        <v>-2033.43935954321</v>
+        <v>-2033.44677933758</v>
       </c>
       <c r="N15" s="34" t="n">
         <f aca="false">(((('Income Statement'!N18+'Income Statement'!N11)-Schedules!N7)-Schedules!N12)+('Balance Sheet'!N19-'Balance Sheet'!M19))</f>
-        <v>1030.10091883996</v>
+        <v>1030.09952130409</v>
       </c>
       <c r="O15" s="34" t="n">
         <f aca="false">(((('Income Statement'!O18+'Income Statement'!O11)-Schedules!O7)-Schedules!O12)+('Balance Sheet'!O19-'Balance Sheet'!N19))</f>
-        <v>961.767256007925</v>
+        <v>961.76598891498</v>
       </c>
       <c r="P15" s="34" t="n">
         <f aca="false">(((('Income Statement'!P18+'Income Statement'!P11)-Schedules!P7)-Schedules!P12)+('Balance Sheet'!P19-'Balance Sheet'!O19))</f>
-        <v>794.452027238724</v>
+        <v>794.451008926041</v>
       </c>
       <c r="Q15" s="34" t="n">
         <f aca="false">(((('Income Statement'!Q18+'Income Statement'!Q11)-Schedules!Q7)-Schedules!Q12)+('Balance Sheet'!Q19-'Balance Sheet'!P19))</f>
-        <v>3651.83705557539</v>
+        <v>3651.86213729538</v>
       </c>
       <c r="R15" s="34" t="n">
         <f aca="false">(((('Income Statement'!R18+'Income Statement'!R11)-Schedules!R7)-Schedules!R12)+('Balance Sheet'!R19-'Balance Sheet'!Q19))</f>
-        <v>3987.27663963459</v>
+        <v>3987.27956861725</v>
       </c>
       <c r="S15" s="34" t="n">
         <f aca="false">(((('Income Statement'!S18+'Income Statement'!S11)-Schedules!S7)-Schedules!S12)+('Balance Sheet'!S19-'Balance Sheet'!R19))</f>
-        <v>4368.4872574127</v>
+        <v>4368.49030238827</v>
       </c>
       <c r="T15" s="34" t="n">
         <f aca="false">(((('Income Statement'!T18+'Income Statement'!T11)-Schedules!T7)-Schedules!T12)+('Balance Sheet'!T19-'Balance Sheet'!S19))</f>
-        <v>4769.5686855489</v>
+        <v>4769.57185083679</v>
       </c>
       <c r="U15" s="34" t="n">
         <f aca="false">(((('Income Statement'!U18+'Income Statement'!U11)-Schedules!U7)-Schedules!U12)+('Balance Sheet'!U19-'Balance Sheet'!T19))</f>
-        <v>5191.03712529483</v>
+        <v>5191.04043410673</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">IFERROR((D14)/('Income Statement'!D10),0)</f>
-        <v>-0.0971215793513704</v>
+        <v>-0.0971215793513701</v>
       </c>
       <c r="E16" s="19" t="n">
         <f aca="false">IFERROR((E14)/('Income Statement'!E10),0)</f>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="G16" s="19" t="n">
         <f aca="false">IFERROR((G14)/('Income Statement'!G10),0)</f>
-        <v>-0.84707141439248</v>
+        <v>-0.847071414392481</v>
       </c>
       <c r="H16" s="19" t="n">
         <f aca="false">IFERROR((H14)/('Income Statement'!H10),0)</f>
@@ -7231,43 +7231,43 @@
       </c>
       <c r="L16" s="33" t="n">
         <f aca="false">IFERROR((L14)/('Income Statement'!L10),0)</f>
-        <v>-1.77461067277536</v>
+        <v>-1.77460967042622</v>
       </c>
       <c r="M16" s="33" t="n">
         <f aca="false">IFERROR((M14)/('Income Statement'!M10),0)</f>
-        <v>-1.13483648501319</v>
+        <v>-1.13483603435417</v>
       </c>
       <c r="N16" s="33" t="n">
         <f aca="false">IFERROR((N14)/('Income Statement'!N10),0)</f>
-        <v>0.137564569956249</v>
+        <v>0.137564973919895</v>
       </c>
       <c r="O16" s="33" t="n">
         <f aca="false">IFERROR((O14)/('Income Statement'!O10),0)</f>
-        <v>0.476299815535138</v>
+        <v>0.476300151552582</v>
       </c>
       <c r="P16" s="33" t="n">
         <f aca="false">IFERROR((P14)/('Income Statement'!P10),0)</f>
-        <v>0.544135303550669</v>
+        <v>0.544135569118649</v>
       </c>
       <c r="Q16" s="33" t="n">
         <f aca="false">IFERROR((Q14)/('Income Statement'!Q10),0)</f>
-        <v>0.536384629421921</v>
+        <v>0.536384859266674</v>
       </c>
       <c r="R16" s="33" t="n">
         <f aca="false">IFERROR((R14)/('Income Statement'!R10),0)</f>
-        <v>0.526792664231157</v>
+        <v>0.526792870486462</v>
       </c>
       <c r="S16" s="33" t="n">
         <f aca="false">IFERROR((S14)/('Income Statement'!S10),0)</f>
-        <v>0.522203853104346</v>
+        <v>0.522204039988551</v>
       </c>
       <c r="T16" s="33" t="n">
         <f aca="false">IFERROR((T14)/('Income Statement'!T10),0)</f>
-        <v>0.51672834836365</v>
+        <v>0.51672851862847</v>
       </c>
       <c r="U16" s="33" t="n">
         <f aca="false">IFERROR((U14)/('Income Statement'!U10),0)</f>
-        <v>0.512325347317493</v>
+        <v>0.512325505933561</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7341,43 +7341,43 @@
       </c>
       <c r="L18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!L19-'Balance Sheet'!L6)-'Balance Sheet'!L12)</f>
-        <v>2549.75377155189</v>
+        <v>2549.74790347332</v>
       </c>
       <c r="M18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!M19-'Balance Sheet'!M6)-'Balance Sheet'!M12)</f>
-        <v>9265.65242088314</v>
+        <v>9265.64254230954</v>
       </c>
       <c r="N18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!N19-'Balance Sheet'!N6)-'Balance Sheet'!N12)</f>
-        <v>9978.37758869635</v>
+        <v>9978.36350792532</v>
       </c>
       <c r="O18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!O19-'Balance Sheet'!O6)-'Balance Sheet'!O12)</f>
-        <v>8398.87697642454</v>
+        <v>8398.85876153588</v>
       </c>
       <c r="P18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!P19-'Balance Sheet'!P6)-'Balance Sheet'!P12)</f>
-        <v>5860.69613165298</v>
+        <v>5860.67421471351</v>
       </c>
       <c r="Q18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!Q19-'Balance Sheet'!Q6)-'Balance Sheet'!Q12)</f>
-        <v>3005.66854478672</v>
+        <v>3005.64305793487</v>
       </c>
       <c r="R18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!R19-'Balance Sheet'!R6)-'Balance Sheet'!R12)</f>
-        <v>-105.871496200515</v>
+        <v>-105.900472161399</v>
       </c>
       <c r="S18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!S19-'Balance Sheet'!S6)-'Balance Sheet'!S12)</f>
-        <v>-3528.54078483102</v>
+        <v>-3528.5731889244</v>
       </c>
       <c r="T18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!T19-'Balance Sheet'!T6)-'Balance Sheet'!T12)</f>
-        <v>-7278.8560370738</v>
+        <v>-7278.89175560785</v>
       </c>
       <c r="U18" s="34" t="n">
         <f aca="false">(('Balance Sheet'!U19-'Balance Sheet'!U6)-'Balance Sheet'!U12)</f>
-        <v>-11363.1918060995</v>
+        <v>-11363.2307016149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7426,43 +7426,43 @@
       </c>
       <c r="L19" s="38" t="n">
         <f aca="false">IFERROR((L18)/('Income Statement'!L10),0)</f>
-        <v>0.886121531516793</v>
+        <v>0.886119492170552</v>
       </c>
       <c r="M19" s="38" t="n">
         <f aca="false">IFERROR((M18)/('Income Statement'!M10),0)</f>
-        <v>2.03105161738365</v>
+        <v>2.03104945197835</v>
       </c>
       <c r="N19" s="38" t="n">
         <f aca="false">IFERROR((N18)/('Income Statement'!N10),0)</f>
-        <v>1.84764584619988</v>
+        <v>1.84764323893454</v>
       </c>
       <c r="O19" s="38" t="n">
         <f aca="false">IFERROR((O18)/('Income Statement'!O10),0)</f>
-        <v>1.36653355220109</v>
+        <v>1.36653058856005</v>
       </c>
       <c r="P19" s="38" t="n">
         <f aca="false">IFERROR((P18)/('Income Statement'!P10),0)</f>
-        <v>0.886720126794431</v>
+        <v>0.886716810773448</v>
       </c>
       <c r="Q19" s="38" t="n">
         <f aca="false">IFERROR((Q18)/('Income Statement'!Q10),0)</f>
-        <v>0.425164557558731</v>
+        <v>0.42516095233549</v>
       </c>
       <c r="R19" s="38" t="n">
         <f aca="false">IFERROR((R18)/('Income Statement'!R10),0)</f>
-        <v>-0.014103117212191</v>
+        <v>-0.0141069770931536</v>
       </c>
       <c r="S19" s="38" t="n">
         <f aca="false">IFERROR((S18)/('Income Statement'!S10),0)</f>
-        <v>-0.442869658049112</v>
+        <v>-0.442873725109868</v>
       </c>
       <c r="T19" s="38" t="n">
         <f aca="false">IFERROR((T18)/('Income Statement'!T10),0)</f>
-        <v>-0.861618774773757</v>
+        <v>-0.861623002877651</v>
       </c>
       <c r="U19" s="38" t="n">
         <f aca="false">IFERROR((U18)/('Income Statement'!U10),0)</f>
-        <v>-1.27166146538092</v>
+        <v>-1.27166581820088</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7511,43 +7511,43 @@
       </c>
       <c r="L20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!L12)/('Income Statement'!L14),0)</f>
-        <v>4.44698280440997</v>
+        <v>4.446976512129</v>
       </c>
       <c r="M20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!M12)/('Income Statement'!M14),0)</f>
-        <v>5.53150558319938</v>
+        <v>5.53150057823468</v>
       </c>
       <c r="N20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!N12)/('Income Statement'!N14),0)</f>
-        <v>4.91448741761059</v>
+        <v>4.91448399545523</v>
       </c>
       <c r="O20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!O12)/('Income Statement'!O14),0)</f>
-        <v>5.99455168060185</v>
+        <v>5.99455179758531</v>
       </c>
       <c r="P20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!P12)/('Income Statement'!P14),0)</f>
-        <v>8.30234447280542</v>
+        <v>8.30235407447244</v>
       </c>
       <c r="Q20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!Q12)/('Income Statement'!Q14),0)</f>
-        <v>10.8157858906448</v>
+        <v>10.8157912074701</v>
       </c>
       <c r="R20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!R12)/('Income Statement'!R14),0)</f>
-        <v>11.748078421531</v>
+        <v>11.7480670132693</v>
       </c>
       <c r="S20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!S12)/('Income Statement'!S14),0)</f>
-        <v>12.6979925902992</v>
+        <v>12.6979817909845</v>
       </c>
       <c r="T20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!T12)/('Income Statement'!T14),0)</f>
-        <v>13.6693125926303</v>
+        <v>13.6693022833353</v>
       </c>
       <c r="U20" s="38" t="n">
         <f aca="false">IFERROR(('Income Statement'!U12)/('Income Statement'!U14),0)</f>
-        <v>14.6330274095874</v>
+        <v>14.6330174717326</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7596,43 +7596,43 @@
       </c>
       <c r="L21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!L15+'Balance Sheet'!L16)+'Balance Sheet'!L19)-'Balance Sheet'!L6)</f>
-        <v>21350.9276874429</v>
+        <v>21350.9198645074</v>
       </c>
       <c r="M21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!M15+'Balance Sheet'!M16)+'Balance Sheet'!M19)-'Balance Sheet'!M6)</f>
-        <v>30132.5760735239</v>
+        <v>30132.5612247474</v>
       </c>
       <c r="N21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!N15+'Balance Sheet'!N16)+'Balance Sheet'!N19)-'Balance Sheet'!N6)</f>
-        <v>32984.992044173</v>
+        <v>32984.9689764282</v>
       </c>
       <c r="O21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!O15+'Balance Sheet'!O16)+'Balance Sheet'!O19)-'Balance Sheet'!O6)</f>
-        <v>34007.5956222788</v>
+        <v>34007.5645627367</v>
       </c>
       <c r="P21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!P15+'Balance Sheet'!P16)+'Balance Sheet'!P19)-'Balance Sheet'!P6)</f>
-        <v>34490.4664106363</v>
+        <v>34490.4282521338</v>
       </c>
       <c r="Q21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!Q15+'Balance Sheet'!Q16)+'Balance Sheet'!Q19)-'Balance Sheet'!Q6)</f>
-        <v>35107.5100662663</v>
+        <v>35107.4653278327</v>
       </c>
       <c r="R21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!R15+'Balance Sheet'!R16)+'Balance Sheet'!R19)-'Balance Sheet'!R6)</f>
-        <v>35905.3494075252</v>
+        <v>35905.2984534377</v>
       </c>
       <c r="S21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!S15+'Balance Sheet'!S16)+'Balance Sheet'!S19)-'Balance Sheet'!S6)</f>
-        <v>36849.7829484162</v>
+        <v>36849.7260661142</v>
       </c>
       <c r="T21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!T15+'Balance Sheet'!T16)+'Balance Sheet'!T19)-'Balance Sheet'!T6)</f>
-        <v>37945.8940893259</v>
+        <v>37945.831515933</v>
       </c>
       <c r="U21" s="34" t="n">
         <f aca="false">((('Balance Sheet'!U15+'Balance Sheet'!U16)+'Balance Sheet'!U19)-'Balance Sheet'!U6)</f>
-        <v>39200.62550078</v>
+        <v>39200.5573784977</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7681,43 +7681,43 @@
       </c>
       <c r="L22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!L12*(1-Drivers!L22)))/(AVERAGE(K21,L21)),0)</f>
-        <v>0.0910138606201785</v>
+        <v>0.091013751182264</v>
       </c>
       <c r="M22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!M12*(1-Drivers!M22)))/(AVERAGE(L21,M21)),0)</f>
-        <v>0.100842144307087</v>
+        <v>0.100842039429094</v>
       </c>
       <c r="N22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!N12*(1-Drivers!N22)))/(AVERAGE(M21,N21)),0)</f>
-        <v>0.0905301333500452</v>
+        <v>0.0905300225709803</v>
       </c>
       <c r="O22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!O12*(1-Drivers!O22)))/(AVERAGE(N21,O21)),0)</f>
-        <v>0.0998039914474745</v>
+        <v>0.0998039153982804</v>
       </c>
       <c r="P22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!P12*(1-Drivers!P22)))/(AVERAGE(O21,P21)),0)</f>
-        <v>0.107938625620133</v>
+        <v>0.107938591146731</v>
       </c>
       <c r="Q22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!Q12*(1-Drivers!Q22)))/(AVERAGE(P21,Q21)),0)</f>
-        <v>0.116626733098272</v>
+        <v>0.116626740873105</v>
       </c>
       <c r="R22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!R12*(1-Drivers!R22)))/(AVERAGE(Q21,R21)),0)</f>
-        <v>0.123775037226179</v>
+        <v>0.123775083822992</v>
       </c>
       <c r="S22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!S12*(1-Drivers!S22)))/(AVERAGE(R21,S21)),0)</f>
-        <v>0.130293517448073</v>
+        <v>0.130293599755705</v>
       </c>
       <c r="T22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!T12*(1-Drivers!T22)))/(AVERAGE(S21,T21)),0)</f>
-        <v>0.13618420584617</v>
+        <v>0.136184320636147</v>
       </c>
       <c r="U22" s="33" t="n">
         <f aca="false">IFERROR((('Income Statement'!U12*(1-Drivers!U22)))/(AVERAGE(T21,U21)),0)</f>
-        <v>0.141135906445169</v>
+        <v>0.141136049696111</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7766,43 +7766,43 @@
       </c>
       <c r="L23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!L18)/(AVERAGE(Schedules!K24,Schedules!L24)),0)</f>
-        <v>0.102955986003387</v>
+        <v>0.102955842964007</v>
       </c>
       <c r="M23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!M18)/(AVERAGE(Schedules!L24,Schedules!M24)),0)</f>
-        <v>0.118505717673138</v>
+        <v>0.118505565513974</v>
       </c>
       <c r="N23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!N18)/(AVERAGE(Schedules!M24,Schedules!N24)),0)</f>
-        <v>0.110968071885523</v>
+        <v>0.110967899202308</v>
       </c>
       <c r="O23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!O18)/(AVERAGE(Schedules!N24,Schedules!O24)),0)</f>
-        <v>0.121773298450426</v>
+        <v>0.121773173373425</v>
       </c>
       <c r="P23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!P18)/(AVERAGE(Schedules!O24,Schedules!P24)),0)</f>
-        <v>0.126708046755404</v>
+        <v>0.126707973780209</v>
       </c>
       <c r="Q23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!Q18)/(AVERAGE(Schedules!P24,Schedules!Q24)),0)</f>
-        <v>0.130042103328963</v>
+        <v>0.130042070018877</v>
       </c>
       <c r="R23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!R18)/(AVERAGE(Schedules!Q24,Schedules!R24)),0)</f>
-        <v>0.130541389001566</v>
+        <v>0.130541383243201</v>
       </c>
       <c r="S23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!S18)/(AVERAGE(Schedules!R24,Schedules!S24)),0)</f>
-        <v>0.130015532971204</v>
+        <v>0.130015547248711</v>
       </c>
       <c r="T23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!T18)/(AVERAGE(Schedules!S24,Schedules!T24)),0)</f>
-        <v>0.128746945805289</v>
+        <v>0.128746973631515</v>
       </c>
       <c r="U23" s="33" t="n">
         <f aca="false">IFERROR(('Income Statement'!U18)/(AVERAGE(Schedules!T24,Schedules!U24)),0)</f>
-        <v>0.12674446040146</v>
+        <v>0.126744496922114</v>
       </c>
     </row>
   </sheetData>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="B44" s="45" t="n">
         <f aca="false">DCF!B45</f>
-        <v>115.301507056065</v>
+        <v>115.301503264642</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9245,34 +9245,34 @@
         <v>0.0644885555181021</v>
       </c>
       <c r="L12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
       <c r="M12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
       <c r="N12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
       <c r="O12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
       <c r="P12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
       <c r="Q12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
       <c r="R12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
       <c r="S12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
       <c r="T12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
       <c r="U12" s="48" t="n">
-        <v>0.069333</v>
+        <v>0.0693332886548905</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9395,34 +9395,34 @@
         <v>0.594698439225283</v>
       </c>
       <c r="L14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
       <c r="M14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
       <c r="N14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
       <c r="O14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
       <c r="P14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
       <c r="Q14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
       <c r="R14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
       <c r="S14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
       <c r="T14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
       <c r="U14" s="48" t="n">
-        <v>0.360375</v>
+        <v>0.36037459732784</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H19" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!H9)/('Income Statement'!H6),0)</f>
-        <v>0.26555838659797</v>
+        <v>0.265558386597971</v>
       </c>
       <c r="I19" s="19" t="n">
         <f aca="false">IFERROR(('Balance Sheet'!I9)/('Income Statement'!I6),0)</f>
@@ -9720,34 +9720,34 @@
         <v>0.550449133068728</v>
       </c>
       <c r="L19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
       <c r="M19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
       <c r="N19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
       <c r="O19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
       <c r="P19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
       <c r="Q19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
       <c r="R19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
       <c r="S19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
       <c r="T19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
       <c r="U19" s="48" t="n">
-        <v>0.367134</v>
+        <v>0.367134141667002</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9795,34 +9795,34 @@
         <v>0.385008505177713</v>
       </c>
       <c r="L20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
       <c r="M20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
       <c r="N20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
       <c r="O20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
       <c r="P20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
       <c r="Q20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
       <c r="R20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
       <c r="S20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
       <c r="T20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
       <c r="U20" s="48" t="n">
-        <v>0.336825</v>
+        <v>0.336825488945708</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!D17)/('Income Statement'!D16),0)</f>
-        <v>0.060315670800451</v>
+        <v>0.0603156708004508</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IFERROR(('Income Statement'!E17)/('Income Statement'!E16),0)</f>
@@ -11005,43 +11005,43 @@
       </c>
       <c r="L11" s="34" t="n">
         <f aca="false">MIN((Drivers!L12*'Balance Sheet'!K10),('Balance Sheet'!K10+Schedules!L7))</f>
-        <v>729.87473097</v>
+        <v>729.877769666012</v>
       </c>
       <c r="M11" s="34" t="n">
         <f aca="false">MIN((Drivers!M12*'Balance Sheet'!L10),('Balance Sheet'!L10+Schedules!M7))</f>
-        <v>1233.98025619857</v>
+        <v>1233.98518296023</v>
       </c>
       <c r="N11" s="34" t="n">
         <f aca="false">MIN((Drivers!N12*'Balance Sheet'!M10),('Balance Sheet'!M10+Schedules!N7))</f>
-        <v>1737.74260515303</v>
+        <v>1737.74928764579</v>
       </c>
       <c r="O11" s="34" t="n">
         <f aca="false">MIN((Drivers!O12*'Balance Sheet'!N10),('Balance Sheet'!N10+Schedules!O7))</f>
-        <v>1860.13911528768</v>
+        <v>1860.14584403606</v>
       </c>
       <c r="P11" s="34" t="n">
         <f aca="false">MIN((Drivers!P12*'Balance Sheet'!O10),('Balance Sheet'!O10+Schedules!P7))</f>
-        <v>1869.93052683494</v>
+        <v>1869.93682982176</v>
       </c>
       <c r="Q11" s="34" t="n">
         <f aca="false">MIN((Drivers!Q12*'Balance Sheet'!P10),('Balance Sheet'!P10+Schedules!Q7))</f>
-        <v>1866.22876791152</v>
+        <v>1866.23461847997</v>
       </c>
       <c r="R11" s="34" t="n">
         <f aca="false">MIN((Drivers!R12*'Balance Sheet'!Q10),('Balance Sheet'!Q10+Schedules!R7))</f>
-        <v>1872.5857600267</v>
+        <v>1872.59123142213</v>
       </c>
       <c r="S11" s="34" t="n">
         <f aca="false">MIN((Drivers!S12*'Balance Sheet'!R10),('Balance Sheet'!R10+Schedules!S7))</f>
-        <v>1890.83084369675</v>
+        <v>1890.83601170232</v>
       </c>
       <c r="T11" s="34" t="n">
         <f aca="false">MIN((Drivers!T12*'Balance Sheet'!S10),('Balance Sheet'!S10+Schedules!T7))</f>
-        <v>1918.40397690476</v>
+        <v>1918.40890139105</v>
       </c>
       <c r="U11" s="34" t="n">
         <f aca="false">MIN((Drivers!U12*'Balance Sheet'!T10),('Balance Sheet'!T10+Schedules!U7))</f>
-        <v>1956.12560315075</v>
+        <v>1956.1303432531</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11090,43 +11090,43 @@
       </c>
       <c r="L12" s="61" t="n">
         <f aca="false">(L10-L11)</f>
-        <v>2147.55650263</v>
+        <v>2147.55346393399</v>
       </c>
       <c r="M12" s="61" t="n">
         <f aca="false">(M10-M11)</f>
-        <v>3328.01725365247</v>
+        <v>3328.01232689081</v>
       </c>
       <c r="N12" s="61" t="n">
         <f aca="false">(N10-N11)</f>
-        <v>3662.84734514465</v>
+        <v>3662.8406626519</v>
       </c>
       <c r="O12" s="61" t="n">
         <f aca="false">(O10-O11)</f>
-        <v>4285.97926058124</v>
+        <v>4285.97253183287</v>
       </c>
       <c r="P12" s="61" t="n">
         <f aca="false">(P10-P11)</f>
-        <v>4739.47863684324</v>
+        <v>4739.47233385641</v>
       </c>
       <c r="Q12" s="61" t="n">
         <f aca="false">(Q10-Q11)</f>
-        <v>5203.19527355865</v>
+        <v>5203.18942299021</v>
       </c>
       <c r="R12" s="61" t="n">
         <f aca="false">(R10-R11)</f>
-        <v>5634.3713621192</v>
+        <v>5634.36589072376</v>
       </c>
       <c r="S12" s="61" t="n">
         <f aca="false">(S10-S11)</f>
-        <v>6076.61673529211</v>
+        <v>6076.61156728654</v>
       </c>
       <c r="T12" s="61" t="n">
         <f aca="false">(T10-T11)</f>
-        <v>6529.48069109713</v>
+        <v>6529.47576661084</v>
       </c>
       <c r="U12" s="61" t="n">
         <f aca="false">(U10-U11)</f>
-        <v>6979.57946887151</v>
+        <v>6979.57472876916</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11165,43 +11165,43 @@
       </c>
       <c r="L13" s="34" t="n">
         <f aca="false">((L6*Drivers!L9)+(Drivers!L24*AVERAGE('Balance Sheet'!K6,'Balance Sheet'!L6)))</f>
-        <v>292.410315624448</v>
+        <v>292.410506337117</v>
       </c>
       <c r="M13" s="34" t="n">
         <f aca="false">((M6*Drivers!M9)+(Drivers!M24*AVERAGE('Balance Sheet'!L6,'Balance Sheet'!M6)))</f>
-        <v>283.172536167008</v>
+        <v>283.172726372957</v>
       </c>
       <c r="N13" s="34" t="n">
         <f aca="false">((N6*Drivers!N9)+(Drivers!N24*AVERAGE('Balance Sheet'!M6,'Balance Sheet'!N6)))</f>
-        <v>199.734054840742</v>
+        <v>199.734052814079</v>
       </c>
       <c r="O13" s="34" t="n">
         <f aca="false">((O6*Drivers!O9)+(Drivers!O24*AVERAGE('Balance Sheet'!N6,'Balance Sheet'!O6)))</f>
-        <v>219.944166383775</v>
+        <v>219.944160736191</v>
       </c>
       <c r="P13" s="34" t="n">
         <f aca="false">((P6*Drivers!P9)+(Drivers!P24*AVERAGE('Balance Sheet'!O6,'Balance Sheet'!P6)))</f>
-        <v>232.680584460008</v>
+        <v>232.680570748706</v>
       </c>
       <c r="Q13" s="34" t="n">
         <f aca="false">((Q6*Drivers!Q9)+(Drivers!Q24*AVERAGE('Balance Sheet'!P6,'Balance Sheet'!Q6)))</f>
-        <v>336.257620351468</v>
+        <v>336.258439089933</v>
       </c>
       <c r="R13" s="34" t="n">
         <f aca="false">((R6*Drivers!R9)+(Drivers!R24*AVERAGE('Balance Sheet'!Q6,'Balance Sheet'!R6)))</f>
-        <v>540.71054998756</v>
+        <v>540.712320029774</v>
       </c>
       <c r="S13" s="34" t="n">
         <f aca="false">((S6*Drivers!S9)+(Drivers!S24*AVERAGE('Balance Sheet'!R6,'Balance Sheet'!S6)))</f>
-        <v>764.261492638239</v>
+        <v>764.263487491387</v>
       </c>
       <c r="T13" s="34" t="n">
         <f aca="false">((T6*Drivers!T9)+(Drivers!T24*AVERAGE('Balance Sheet'!S6,'Balance Sheet'!T6)))</f>
-        <v>1008.8374690842</v>
+        <v>1008.83968307181</v>
       </c>
       <c r="U13" s="34" t="n">
         <f aca="false">((U6*Drivers!U9)+(Drivers!U24*AVERAGE('Balance Sheet'!T6,'Balance Sheet'!U6)))</f>
-        <v>1275.75506762001</v>
+        <v>1275.75749257673</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11244,23 +11244,23 @@
       </c>
       <c r="M14" s="34" t="n">
         <f aca="false">(Drivers!M23*AVERAGE('Balance Sheet'!L19,'Balance Sheet'!M19))</f>
-        <v>601.647635276826</v>
+        <v>601.647288980834</v>
       </c>
       <c r="N14" s="34" t="n">
         <f aca="false">(Drivers!N23*AVERAGE('Balance Sheet'!M19,'Balance Sheet'!N19))</f>
-        <v>745.316252518868</v>
+        <v>745.31541175822</v>
       </c>
       <c r="O14" s="34" t="n">
         <f aca="false">(Drivers!O23*AVERAGE('Balance Sheet'!N19,'Balance Sheet'!O19))</f>
-        <v>714.979115861244</v>
+        <v>714.977979431142</v>
       </c>
       <c r="P14" s="34" t="n">
         <f aca="false">(Drivers!P23*AVERAGE('Balance Sheet'!O19,'Balance Sheet'!P19))</f>
-        <v>570.860273548941</v>
+        <v>570.858854168729</v>
       </c>
       <c r="Q14" s="34" t="n">
         <f aca="false">(Drivers!Q23*AVERAGE('Balance Sheet'!P19,'Balance Sheet'!Q19))</f>
-        <v>481.074174929739</v>
+        <v>481.073397514973</v>
       </c>
       <c r="R14" s="34" t="n">
         <f aca="false">(Drivers!R23*AVERAGE('Balance Sheet'!Q19,'Balance Sheet'!R19))</f>
@@ -11390,43 +11390,43 @@
       </c>
       <c r="L16" s="61" t="n">
         <f aca="false">(((L12+L13)-L14)+L15)</f>
-        <v>1957.04241825445</v>
+        <v>1957.03957027111</v>
       </c>
       <c r="M16" s="61" t="n">
         <f aca="false">(((M12+M13)-M14)+M15)</f>
-        <v>3009.54215454265</v>
+        <v>3009.53776428293</v>
       </c>
       <c r="N16" s="61" t="n">
         <f aca="false">(((N12+N13)-N14)+N15)</f>
-        <v>3117.26514746653</v>
+        <v>3117.25930370776</v>
       </c>
       <c r="O16" s="61" t="n">
         <f aca="false">(((O12+O13)-O14)+O15)</f>
-        <v>3790.94431110378</v>
+        <v>3790.93871313792</v>
       </c>
       <c r="P16" s="61" t="n">
         <f aca="false">(((P12+P13)-P14)+P15)</f>
-        <v>4401.2989477543</v>
+        <v>4401.29405043639</v>
       </c>
       <c r="Q16" s="61" t="n">
         <f aca="false">(((Q12+Q13)-Q14)+Q15)</f>
-        <v>5058.37871898038</v>
+        <v>5058.37446456517</v>
       </c>
       <c r="R16" s="61" t="n">
         <f aca="false">(((R12+R13)-R14)+R15)</f>
-        <v>5695.48251210676</v>
+        <v>5695.47881075354</v>
       </c>
       <c r="S16" s="61" t="n">
         <f aca="false">(((S12+S13)-S14)+S15)</f>
-        <v>6362.32882793035</v>
+        <v>6362.32565477793</v>
       </c>
       <c r="T16" s="61" t="n">
         <f aca="false">(((T12+T13)-T14)+T15)</f>
-        <v>7060.64376018133</v>
+        <v>7060.64104968266</v>
       </c>
       <c r="U16" s="61" t="n">
         <f aca="false">(((U12+U13)-U14)+U15)</f>
-        <v>7778.36013649152</v>
+        <v>7778.35782134589</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11465,43 +11465,43 @@
       </c>
       <c r="L17" s="34" t="n">
         <f aca="false">(L16*Drivers!L22)</f>
-        <v>430.549332015194</v>
+        <v>430.548705459643</v>
       </c>
       <c r="M17" s="34" t="n">
         <f aca="false">(M16*Drivers!M22)</f>
-        <v>662.099273999383</v>
+        <v>662.098308142245</v>
       </c>
       <c r="N17" s="34" t="n">
         <f aca="false">(N16*Drivers!N22)</f>
-        <v>685.798332442636</v>
+        <v>685.797046815707</v>
       </c>
       <c r="O17" s="34" t="n">
         <f aca="false">(O16*Drivers!O22)</f>
-        <v>834.007748442262</v>
+        <v>834.006516890341</v>
       </c>
       <c r="P17" s="34" t="n">
         <f aca="false">(P16*Drivers!P22)</f>
-        <v>968.285768504626</v>
+        <v>968.284691096006</v>
       </c>
       <c r="Q17" s="34" t="n">
         <f aca="false">(Q16*Drivers!Q22)</f>
-        <v>1112.84331817568</v>
+        <v>1112.84238220434</v>
       </c>
       <c r="R17" s="34" t="n">
         <f aca="false">(R16*Drivers!R22)</f>
-        <v>1253.00615266349</v>
+        <v>1253.00533836578</v>
       </c>
       <c r="S17" s="34" t="n">
         <f aca="false">(S16*Drivers!S22)</f>
-        <v>1399.71234214468</v>
+        <v>1399.71164405114</v>
       </c>
       <c r="T17" s="34" t="n">
         <f aca="false">(T16*Drivers!T22)</f>
-        <v>1553.34162723989</v>
+        <v>1553.34103093018</v>
       </c>
       <c r="U17" s="34" t="n">
         <f aca="false">(U16*Drivers!U22)</f>
-        <v>1711.23923002739</v>
+        <v>1711.2387206961</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11540,43 +11540,43 @@
       </c>
       <c r="L18" s="61" t="n">
         <f aca="false">(L16-L17)</f>
-        <v>1526.49308623925</v>
+        <v>1526.49086481146</v>
       </c>
       <c r="M18" s="61" t="n">
         <f aca="false">(M16-M17)</f>
-        <v>2347.44288054327</v>
+        <v>2347.43945614069</v>
       </c>
       <c r="N18" s="61" t="n">
         <f aca="false">(N16-N17)</f>
-        <v>2431.46681502389</v>
+        <v>2431.46225689205</v>
       </c>
       <c r="O18" s="61" t="n">
         <f aca="false">(O16-O17)</f>
-        <v>2956.93656265893</v>
+        <v>2956.93219624757</v>
       </c>
       <c r="P18" s="61" t="n">
         <f aca="false">(P16-P17)</f>
-        <v>3433.01317924968</v>
+        <v>3433.00935934038</v>
       </c>
       <c r="Q18" s="61" t="n">
         <f aca="false">(Q16-Q17)</f>
-        <v>3945.5354008047</v>
+        <v>3945.53208236083</v>
       </c>
       <c r="R18" s="61" t="n">
         <f aca="false">(R16-R17)</f>
-        <v>4442.47635944327</v>
+        <v>4442.47347238776</v>
       </c>
       <c r="S18" s="61" t="n">
         <f aca="false">(S16-S17)</f>
-        <v>4962.61648578567</v>
+        <v>4962.61401072679</v>
       </c>
       <c r="T18" s="61" t="n">
         <f aca="false">(T16-T17)</f>
-        <v>5507.30213294144</v>
+        <v>5507.30001875247</v>
       </c>
       <c r="U18" s="61" t="n">
         <f aca="false">(U16-U17)</f>
-        <v>6067.12090646413</v>
+        <v>6067.11910064979</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11585,39 +11585,39 @@
       </c>
       <c r="B19" s="35" t="n">
         <f aca="false">IFERROR((B18)/(Schedules!B23),0)</f>
-        <v>5.46003393773728E-006</v>
+        <v>54.6003393773728</v>
       </c>
       <c r="C19" s="35" t="n">
         <f aca="false">IFERROR((C18)/(Schedules!C23),0)</f>
-        <v>4.4091582935266E-006</v>
+        <v>44.091582935266</v>
       </c>
       <c r="D19" s="35" t="n">
         <f aca="false">IFERROR((D18)/(Schedules!D23),0)</f>
-        <v>4.39334541261736E-006</v>
+        <v>43.9334541261736</v>
       </c>
       <c r="E19" s="35" t="n">
         <f aca="false">IFERROR((E18)/(Schedules!E23),0)</f>
-        <v>3.1774160175674E-006</v>
+        <v>31.774160175674</v>
       </c>
       <c r="F19" s="35" t="n">
         <f aca="false">IFERROR((F18)/(Schedules!F23),0)</f>
-        <v>4.86207057661374E-006</v>
+        <v>48.6207057661374</v>
       </c>
       <c r="G19" s="35" t="n">
         <f aca="false">IFERROR((G18)/(Schedules!G23),0)</f>
-        <v>5.40191143494138E-006</v>
+        <v>54.0191143494139</v>
       </c>
       <c r="H19" s="35" t="n">
         <f aca="false">IFERROR((H18)/(Schedules!H23),0)</f>
-        <v>3.96759287897949E-007</v>
+        <v>3.96759287897949</v>
       </c>
       <c r="I19" s="35" t="n">
         <f aca="false">IFERROR((I18)/(Schedules!I23),0)</f>
-        <v>5.50432922605529E-007</v>
+        <v>5.50432922605529</v>
       </c>
       <c r="J19" s="35" t="n">
         <f aca="false">IFERROR((J18)/(Schedules!J23),0)</f>
-        <v>7.1575184686517E-007</v>
+        <v>7.1575184686517</v>
       </c>
       <c r="K19" s="35" t="n">
         <f aca="false">IFERROR((K18)/(Schedules!K23),0)</f>
@@ -11625,43 +11625,43 @@
       </c>
       <c r="L19" s="36" t="n">
         <f aca="false">IFERROR((L18)/(Schedules!L23),0)</f>
-        <v>6.56980024204542</v>
+        <v>6.56979068134909</v>
       </c>
       <c r="M19" s="36" t="n">
         <f aca="false">IFERROR((M18)/(Schedules!M23),0)</f>
-        <v>10.1030466130547</v>
+        <v>10.103031874933</v>
       </c>
       <c r="N19" s="36" t="n">
         <f aca="false">IFERROR((N18)/(Schedules!N23),0)</f>
-        <v>10.4646731871052</v>
+        <v>10.4646535695806</v>
       </c>
       <c r="O19" s="36" t="n">
         <f aca="false">IFERROR((O18)/(Schedules!O23),0)</f>
-        <v>12.7262171838129</v>
+        <v>12.7261983914249</v>
       </c>
       <c r="P19" s="36" t="n">
         <f aca="false">IFERROR((P18)/(Schedules!P23),0)</f>
-        <v>14.7751804572829</v>
+        <v>14.7751640169588</v>
       </c>
       <c r="Q19" s="36" t="n">
         <f aca="false">IFERROR((Q18)/(Schedules!Q23),0)</f>
-        <v>16.9810002186559</v>
+        <v>16.9809859365648</v>
       </c>
       <c r="R19" s="36" t="n">
         <f aca="false">IFERROR((R18)/(Schedules!R23),0)</f>
-        <v>19.1197605312816</v>
+        <v>19.1197481058221</v>
       </c>
       <c r="S19" s="36" t="n">
         <f aca="false">IFERROR((S18)/(Schedules!S23),0)</f>
-        <v>21.3583666270096</v>
+        <v>21.3583559747226</v>
       </c>
       <c r="T19" s="36" t="n">
         <f aca="false">IFERROR((T18)/(Schedules!T23),0)</f>
-        <v>23.7026130102924</v>
+        <v>23.7026039111361</v>
       </c>
       <c r="U19" s="36" t="n">
         <f aca="false">IFERROR((U18)/(Schedules!U23),0)</f>
-        <v>26.1119901289612</v>
+        <v>26.1119823570036</v>
       </c>
     </row>
   </sheetData>
@@ -11824,43 +11824,43 @@
       </c>
       <c r="L6" s="34" t="n">
         <f aca="false">(K6+'Cash Flow'!L21)</f>
-        <v>4323.80622844811</v>
+        <v>4323.81209652668</v>
       </c>
       <c r="M6" s="34" t="n">
         <f aca="false">(L6+'Cash Flow'!M21)</f>
-        <v>1000.0000155976</v>
+        <v>1000</v>
       </c>
       <c r="N6" s="34" t="n">
         <f aca="false">(M6+'Cash Flow'!N21)</f>
-        <v>1000.00004679055</v>
+        <v>1000</v>
       </c>
       <c r="O6" s="34" t="n">
         <f aca="false">(N6+'Cash Flow'!O21)</f>
-        <v>1000.00012698124</v>
+        <v>1000</v>
       </c>
       <c r="P6" s="34" t="n">
         <f aca="false">(O6+'Cash Flow'!P21)</f>
-        <v>1000.00029491098</v>
+        <v>1000</v>
       </c>
       <c r="Q6" s="34" t="n">
         <f aca="false">(P6+'Cash Flow'!Q21)</f>
-        <v>3827.89145521328</v>
+        <v>3827.91694206513</v>
       </c>
       <c r="R6" s="34" t="n">
         <f aca="false">(Q6+'Cash Flow'!R21)</f>
-        <v>6924.43149620052</v>
+        <v>6924.4604721614</v>
       </c>
       <c r="S6" s="34" t="n">
         <f aca="false">(R6+'Cash Flow'!S21)</f>
-        <v>10332.100784831</v>
+        <v>10332.1331889244</v>
       </c>
       <c r="T6" s="34" t="n">
         <f aca="false">(S6+'Cash Flow'!T21)</f>
-        <v>14072.4160370738</v>
+        <v>14072.4517556079</v>
       </c>
       <c r="U6" s="34" t="n">
         <f aca="false">(T6+'Cash Flow'!U21)</f>
-        <v>18146.7518060995</v>
+        <v>18146.7907016149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12039,7 +12039,7 @@
         <v>848.39</v>
       </c>
       <c r="I9" s="54" t="n">
-        <v>680.85</v>
+        <v>680.850000000001</v>
       </c>
       <c r="J9" s="54" t="n">
         <v>1656.24</v>
@@ -12049,43 +12049,43 @@
       </c>
       <c r="L9" s="34" t="n">
         <f aca="false">('Income Statement'!L6*Drivers!L19)</f>
-        <v>2342.3566264224</v>
+        <v>2342.35753027397</v>
       </c>
       <c r="M9" s="34" t="n">
         <f aca="false">('Income Statement'!M6*Drivers!M19)</f>
-        <v>3369.94847843391</v>
+        <v>3369.94977880515</v>
       </c>
       <c r="N9" s="34" t="n">
         <f aca="false">('Income Statement'!N6*Drivers!N19)</f>
-        <v>4122.12097882035</v>
+        <v>4122.12256943447</v>
       </c>
       <c r="O9" s="34" t="n">
         <f aca="false">('Income Statement'!O6*Drivers!O19)</f>
-        <v>4740.43912564341</v>
+        <v>4740.44095484963</v>
       </c>
       <c r="P9" s="34" t="n">
         <f aca="false">('Income Statement'!P6*Drivers!P19)</f>
-        <v>5130.1032217713</v>
+        <v>5130.10520133827</v>
       </c>
       <c r="Q9" s="34" t="n">
         <f aca="false">('Income Statement'!Q6*Drivers!Q19)</f>
-        <v>5487.15840600658</v>
+        <v>5487.16052335142</v>
       </c>
       <c r="R9" s="34" t="n">
         <f aca="false">('Income Statement'!R6*Drivers!R19)</f>
-        <v>5851.50572416541</v>
+        <v>5851.50798210195</v>
       </c>
       <c r="S9" s="34" t="n">
         <f aca="false">('Income Statement'!S6*Drivers!S19)</f>
-        <v>6223.66148822233</v>
+        <v>6223.66388976364</v>
       </c>
       <c r="T9" s="34" t="n">
         <f aca="false">('Income Statement'!T6*Drivers!T19)</f>
-        <v>6598.94827596214</v>
+        <v>6598.95082231638</v>
       </c>
       <c r="U9" s="34" t="n">
         <f aca="false">('Income Statement'!U6*Drivers!U19)</f>
-        <v>6994.88517251987</v>
+        <v>6994.88787165537</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12124,43 +12124,43 @@
       </c>
       <c r="L10" s="34" t="n">
         <f aca="false">((K10+Schedules!L7)-'Income Statement'!L11)</f>
-        <v>17797.87772343</v>
+        <v>17797.874684734</v>
       </c>
       <c r="M10" s="34" t="n">
         <f aca="false">((L10+Schedules!M7)-'Income Statement'!M11)</f>
-        <v>25063.7157652637</v>
+        <v>25063.7077998061</v>
       </c>
       <c r="N10" s="34" t="n">
         <f aca="false">((M10+Schedules!N7)-'Income Statement'!N11)</f>
-        <v>26829.0585332768</v>
+        <v>26829.0438853264</v>
       </c>
       <c r="O10" s="34" t="n">
         <f aca="false">((N10+Schedules!O7)-'Income Statement'!O11)</f>
-        <v>26970.2814941649</v>
+        <v>26970.2601174661</v>
       </c>
       <c r="P10" s="34" t="n">
         <f aca="false">((O10+Schedules!P7)-'Income Statement'!P11)</f>
-        <v>26916.8904837743</v>
+        <v>26916.8628040887</v>
       </c>
       <c r="Q10" s="34" t="n">
         <f aca="false">((P10+Schedules!Q7)-'Income Statement'!Q11)</f>
-        <v>27008.5783108577</v>
+        <v>27008.5447806036</v>
       </c>
       <c r="R10" s="34" t="n">
         <f aca="false">((Q10+Schedules!R7)-'Income Statement'!R11)</f>
-        <v>27271.7298212504</v>
+        <v>27271.6908196009</v>
       </c>
       <c r="S10" s="34" t="n">
         <f aca="false">((R10+Schedules!S7)-'Income Statement'!S11)</f>
-        <v>27669.4211544973</v>
+        <v>27669.3769848422</v>
       </c>
       <c r="T10" s="34" t="n">
         <f aca="false">((S10+Schedules!T7)-'Income Statement'!T11)</f>
-        <v>28213.4856872016</v>
+        <v>28213.4365930602</v>
       </c>
       <c r="U10" s="34" t="n">
         <f aca="false">((T10+Schedules!U7)-'Income Statement'!U11)</f>
-        <v>28886.6293802962</v>
+        <v>28886.5755460525</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12199,43 +12199,43 @@
       </c>
       <c r="L11" s="34" t="n">
         <f aca="false">('Income Statement'!L6*Drivers!L14)</f>
-        <v>2299.2334386</v>
+        <v>2299.23086950587</v>
       </c>
       <c r="M11" s="34" t="n">
         <f aca="false">('Income Statement'!M6*Drivers!M14)</f>
-        <v>3307.90714811382</v>
+        <v>3307.9034519581</v>
       </c>
       <c r="N11" s="34" t="n">
         <f aca="false">('Income Statement'!N6*Drivers!N14)</f>
-        <v>4046.23202357282</v>
+        <v>4046.22750243515</v>
       </c>
       <c r="O11" s="34" t="n">
         <f aca="false">('Income Statement'!O6*Drivers!O14)</f>
-        <v>4653.16682710875</v>
+        <v>4653.16162780042</v>
       </c>
       <c r="P11" s="34" t="n">
         <f aca="false">('Income Statement'!P6*Drivers!P14)</f>
-        <v>5035.65714029709</v>
+        <v>5035.65151360561</v>
       </c>
       <c r="Q11" s="34" t="n">
         <f aca="false">('Income Statement'!Q6*Drivers!Q14)</f>
-        <v>5386.13887726176</v>
+        <v>5386.13285895257</v>
       </c>
       <c r="R11" s="34" t="n">
         <f aca="false">('Income Statement'!R6*Drivers!R14)</f>
-        <v>5743.77849871194</v>
+        <v>5743.77208078702</v>
       </c>
       <c r="S11" s="34" t="n">
         <f aca="false">('Income Statement'!S6*Drivers!S14)</f>
-        <v>6109.08281123002</v>
+        <v>6109.07598512507</v>
       </c>
       <c r="T11" s="34" t="n">
         <f aca="false">('Income Statement'!T6*Drivers!T14)</f>
-        <v>6477.46050474719</v>
+        <v>6477.45326702811</v>
       </c>
       <c r="U11" s="34" t="n">
         <f aca="false">('Income Statement'!U6*Drivers!U14)</f>
-        <v>6866.10813503203</v>
+        <v>6866.1004630498</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12359,43 +12359,43 @@
       </c>
       <c r="L13" s="61" t="n">
         <f aca="false">((((((L6+L7)+L8)+L9)+L10)+L11)+L12)</f>
-        <v>28073.2218209115</v>
+        <v>28073.2229850515</v>
       </c>
       <c r="M13" s="61" t="n">
         <f aca="false">((((((M6+M7)+M8)+M9)+M10)+M11)+M12)</f>
-        <v>34553.2034678524</v>
+        <v>34553.1930910127</v>
       </c>
       <c r="N13" s="61" t="n">
         <f aca="false">((((((N6+N7)+N8)+N9)+N10)+N11)+N12)</f>
-        <v>38181.9001594058</v>
+        <v>38181.8825341412</v>
       </c>
       <c r="O13" s="61" t="n">
         <f aca="false">((((((O6+O7)+O8)+O9)+O10)+O11)+O12)</f>
-        <v>39838.63882718</v>
+        <v>39838.6139533979</v>
       </c>
       <c r="P13" s="61" t="n">
         <f aca="false">((((((P6+P7)+P8)+P9)+P10)+P11)+P12)</f>
-        <v>40721.6076167843</v>
+        <v>40721.5759950632</v>
       </c>
       <c r="Q13" s="61" t="n">
         <f aca="false">((((((Q6+Q7)+Q8)+Q9)+Q10)+Q11)+Q12)</f>
-        <v>44530.6298401017</v>
+        <v>44530.6178957351</v>
       </c>
       <c r="R13" s="61" t="n">
         <f aca="false">((((((R6+R7)+R8)+R9)+R10)+R11)+R12)</f>
-        <v>48798.8030499775</v>
+        <v>48798.7888643005</v>
       </c>
       <c r="S13" s="61" t="n">
         <f aca="false">((((((S6+S7)+S8)+S9)+S10)+S11)+S12)</f>
-        <v>53531.7432288415</v>
+        <v>53531.7270387162</v>
       </c>
       <c r="T13" s="61" t="n">
         <f aca="false">((((((T6+T7)+T8)+T9)+T10)+T11)+T12)</f>
-        <v>58751.0661495462</v>
+        <v>58751.0480825741</v>
       </c>
       <c r="U13" s="61" t="n">
         <f aca="false">((((((U6+U7)+U8)+U9)+U10)+U11)+U12)</f>
-        <v>64485.4558683077</v>
+        <v>64485.4359567327</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12534,43 +12534,43 @@
       </c>
       <c r="L16" s="34" t="n">
         <f aca="false">(((K16+'Income Statement'!L18)-Schedules!L22)+Drivers!L27)</f>
-        <v>18358.773915891</v>
+        <v>18358.7719610341</v>
       </c>
       <c r="M16" s="34" t="n">
         <f aca="false">(((L16+'Income Statement'!M18)-Schedules!M22)+Drivers!M27)</f>
-        <v>20424.5236526408</v>
+        <v>20424.5186824379</v>
       </c>
       <c r="N16" s="34" t="n">
         <f aca="false">(((M16+'Income Statement'!N18)-Schedules!N22)+Drivers!N27)</f>
-        <v>22564.2144554766</v>
+        <v>22564.2054685029</v>
       </c>
       <c r="O16" s="34" t="n">
         <f aca="false">(((N16+'Income Statement'!O18)-Schedules!O22)+Drivers!O27)</f>
-        <v>25166.3186458543</v>
+        <v>25166.3058012008</v>
       </c>
       <c r="P16" s="34" t="n">
         <f aca="false">(((O16+'Income Statement'!P18)-Schedules!P22)+Drivers!P27)</f>
-        <v>28187.3702789833</v>
+        <v>28187.3540374203</v>
       </c>
       <c r="Q16" s="34" t="n">
         <f aca="false">(((P16+'Income Statement'!Q18)-Schedules!Q22)+Drivers!Q27)</f>
-        <v>31659.4415214796</v>
+        <v>31659.4222698978</v>
       </c>
       <c r="R16" s="34" t="n">
         <f aca="false">(((Q16+'Income Statement'!R18)-Schedules!R22)+Drivers!R27)</f>
-        <v>35568.8209037257</v>
+        <v>35568.7989255991</v>
       </c>
       <c r="S16" s="34" t="n">
         <f aca="false">(((R16+'Income Statement'!S18)-Schedules!S22)+Drivers!S27)</f>
-        <v>39935.9237332472</v>
+        <v>39935.8992550386</v>
       </c>
       <c r="T16" s="34" t="n">
         <f aca="false">(((S16+'Income Statement'!T18)-Schedules!T22)+Drivers!T27)</f>
-        <v>44782.3501263997</v>
+        <v>44782.3232715408</v>
       </c>
       <c r="U16" s="34" t="n">
         <f aca="false">(((T16+'Income Statement'!U18)-Schedules!U22)+Drivers!U27)</f>
-        <v>50121.4173068796</v>
+        <v>50121.3880801126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12688,19 +12688,19 @@
       </c>
       <c r="M18" s="34" t="n">
         <f aca="false">((L18+Schedules!M18)-Schedules!M19)</f>
-        <v>3392.09243648074</v>
+        <v>3392.08254230954</v>
       </c>
       <c r="N18" s="34" t="n">
         <f aca="false">((M18+Schedules!N18)-Schedules!N19)</f>
-        <v>4104.8176354869</v>
+        <v>4104.80350792532</v>
       </c>
       <c r="O18" s="34" t="n">
         <f aca="false">((N18+Schedules!O18)-Schedules!O19)</f>
-        <v>2535.31710340578</v>
+        <v>2535.29876153588</v>
       </c>
       <c r="P18" s="34" t="n">
         <f aca="false">((O18+Schedules!P18)-Schedules!P19)</f>
-        <v>12.1364265639545</v>
+        <v>12.1142147135079</v>
       </c>
       <c r="Q18" s="34" t="n">
         <f aca="false">((P18+Schedules!Q18)-Schedules!Q19)</f>
@@ -12773,19 +12773,19 @@
       </c>
       <c r="M19" s="57" t="n">
         <f aca="false">(M17+M18)</f>
-        <v>10291.0124364807</v>
+        <v>10291.0025423095</v>
       </c>
       <c r="N19" s="57" t="n">
         <f aca="false">(N17+N18)</f>
-        <v>11003.7376354869</v>
+        <v>11003.7235079253</v>
       </c>
       <c r="O19" s="57" t="n">
         <f aca="false">(O17+O18)</f>
-        <v>9424.23710340578</v>
+        <v>9424.21876153588</v>
       </c>
       <c r="P19" s="57" t="n">
         <f aca="false">(P17+P18)</f>
-        <v>6886.05642656396</v>
+        <v>6886.03421471351</v>
       </c>
       <c r="Q19" s="57" t="n">
         <f aca="false">(Q17+Q18)</f>
@@ -12919,43 +12919,43 @@
       </c>
       <c r="L21" s="34" t="n">
         <f aca="false">('Income Statement'!L6*Drivers!L20)</f>
-        <v>2148.98176332</v>
+        <v>2148.98488284916</v>
       </c>
       <c r="M21" s="34" t="n">
         <f aca="false">('Income Statement'!M6*Drivers!M20)</f>
-        <v>3091.74006288848</v>
+        <v>3091.74455095509</v>
       </c>
       <c r="N21" s="34" t="n">
         <f aca="false">('Income Statement'!N6*Drivers!N20)</f>
-        <v>3781.81644492519</v>
+        <v>3781.82193472826</v>
       </c>
       <c r="O21" s="34" t="n">
         <f aca="false">('Income Statement'!O6*Drivers!O20)</f>
-        <v>4349.08891166397</v>
+        <v>4349.0952249375</v>
       </c>
       <c r="P21" s="34" t="n">
         <f aca="false">('Income Statement'!P6*Drivers!P20)</f>
-        <v>4706.58402020275</v>
+        <v>4706.59085242737</v>
       </c>
       <c r="Q21" s="34" t="n">
         <f aca="false">('Income Statement'!Q6*Drivers!Q20)</f>
-        <v>5034.16226800886</v>
+        <v>5034.16957575631</v>
       </c>
       <c r="R21" s="34" t="n">
         <f aca="false">('Income Statement'!R6*Drivers!R20)</f>
-        <v>5368.43064260465</v>
+        <v>5368.43843558653</v>
       </c>
       <c r="S21" s="34" t="n">
         <f aca="false">('Income Statement'!S6*Drivers!S20)</f>
-        <v>5709.86283147431</v>
+        <v>5709.87112008983</v>
       </c>
       <c r="T21" s="34" t="n">
         <f aca="false">('Income Statement'!T6*Drivers!T20)</f>
-        <v>6054.16756021221</v>
+        <v>6054.17634863125</v>
       </c>
       <c r="U21" s="34" t="n">
         <f aca="false">('Income Statement'!U6*Drivers!U20)</f>
-        <v>6417.41761382494</v>
+        <v>6417.42692954913</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13004,43 +13004,43 @@
       </c>
       <c r="L22" s="61" t="n">
         <f aca="false">((((L15+L16)+L19)+L20)+L21)</f>
-        <v>28073.2218203792</v>
+        <v>28073.2229850515</v>
       </c>
       <c r="M22" s="61" t="n">
         <f aca="false">((((M15+M16)+M19)+M20)+M21)</f>
-        <v>34553.2034673201</v>
+        <v>34553.1930910126</v>
       </c>
       <c r="N22" s="61" t="n">
         <f aca="false">((((N15+N16)+N19)+N20)+N21)</f>
-        <v>38181.9001588735</v>
+        <v>38181.8825341412</v>
       </c>
       <c r="O22" s="61" t="n">
         <f aca="false">((((O15+O16)+O19)+O20)+O21)</f>
-        <v>39838.6388266477</v>
+        <v>39838.6139533979</v>
       </c>
       <c r="P22" s="61" t="n">
         <f aca="false">((((P15+P16)+P19)+P20)+P21)</f>
-        <v>40721.607616252</v>
+        <v>40721.5759950632</v>
       </c>
       <c r="Q22" s="61" t="n">
         <f aca="false">((((Q15+Q16)+Q19)+Q20)+Q21)</f>
-        <v>44530.6298395694</v>
+        <v>44530.6178957351</v>
       </c>
       <c r="R22" s="61" t="n">
         <f aca="false">((((R15+R16)+R19)+R20)+R21)</f>
-        <v>48798.8030494452</v>
+        <v>48798.7888643005</v>
       </c>
       <c r="S22" s="61" t="n">
         <f aca="false">((((S15+S16)+S19)+S20)+S21)</f>
-        <v>53531.7432283092</v>
+        <v>53531.7270387161</v>
       </c>
       <c r="T22" s="61" t="n">
         <f aca="false">((((T15+T16)+T19)+T20)+T21)</f>
-        <v>58751.0661490139</v>
+        <v>58751.0480825741</v>
       </c>
       <c r="U22" s="61" t="n">
         <f aca="false">((((U15+U16)+U19)+U20)+U21)</f>
-        <v>64485.4558677754</v>
+        <v>64485.4359567327</v>
       </c>
     </row>
   </sheetData>
@@ -13213,43 +13213,43 @@
       </c>
       <c r="L6" s="34" t="n">
         <f aca="false">'Income Statement'!L18</f>
-        <v>1526.49308623925</v>
+        <v>1526.49086481146</v>
       </c>
       <c r="M6" s="34" t="n">
         <f aca="false">'Income Statement'!M18</f>
-        <v>2347.44288054327</v>
+        <v>2347.43945614069</v>
       </c>
       <c r="N6" s="34" t="n">
         <f aca="false">'Income Statement'!N18</f>
-        <v>2431.46681502389</v>
+        <v>2431.46225689205</v>
       </c>
       <c r="O6" s="34" t="n">
         <f aca="false">'Income Statement'!O18</f>
-        <v>2956.93656265893</v>
+        <v>2956.93219624757</v>
       </c>
       <c r="P6" s="34" t="n">
         <f aca="false">'Income Statement'!P18</f>
-        <v>3433.01317924968</v>
+        <v>3433.00935934038</v>
       </c>
       <c r="Q6" s="34" t="n">
         <f aca="false">'Income Statement'!Q18</f>
-        <v>3945.5354008047</v>
+        <v>3945.53208236083</v>
       </c>
       <c r="R6" s="34" t="n">
         <f aca="false">'Income Statement'!R18</f>
-        <v>4442.47635944327</v>
+        <v>4442.47347238776</v>
       </c>
       <c r="S6" s="34" t="n">
         <f aca="false">'Income Statement'!S18</f>
-        <v>4962.61648578567</v>
+        <v>4962.61401072679</v>
       </c>
       <c r="T6" s="34" t="n">
         <f aca="false">'Income Statement'!T18</f>
-        <v>5507.30213294144</v>
+        <v>5507.30001875247</v>
       </c>
       <c r="U6" s="34" t="n">
         <f aca="false">'Income Statement'!U18</f>
-        <v>6067.12090646413</v>
+        <v>6067.11910064979</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13298,43 +13298,43 @@
       </c>
       <c r="L7" s="34" t="n">
         <f aca="false">'Income Statement'!L11</f>
-        <v>729.87473097</v>
+        <v>729.877769666012</v>
       </c>
       <c r="M7" s="34" t="n">
         <f aca="false">'Income Statement'!M11</f>
-        <v>1233.98025619857</v>
+        <v>1233.98518296023</v>
       </c>
       <c r="N7" s="34" t="n">
         <f aca="false">'Income Statement'!N11</f>
-        <v>1737.74260515303</v>
+        <v>1737.74928764579</v>
       </c>
       <c r="O7" s="34" t="n">
         <f aca="false">'Income Statement'!O11</f>
-        <v>1860.13911528768</v>
+        <v>1860.14584403606</v>
       </c>
       <c r="P7" s="34" t="n">
         <f aca="false">'Income Statement'!P11</f>
-        <v>1869.93052683494</v>
+        <v>1869.93682982176</v>
       </c>
       <c r="Q7" s="34" t="n">
         <f aca="false">'Income Statement'!Q11</f>
-        <v>1866.22876791152</v>
+        <v>1866.23461847997</v>
       </c>
       <c r="R7" s="34" t="n">
         <f aca="false">'Income Statement'!R11</f>
-        <v>1872.5857600267</v>
+        <v>1872.59123142213</v>
       </c>
       <c r="S7" s="34" t="n">
         <f aca="false">'Income Statement'!S11</f>
-        <v>1890.83084369675</v>
+        <v>1890.83601170232</v>
       </c>
       <c r="T7" s="34" t="n">
         <f aca="false">'Income Statement'!T11</f>
-        <v>1918.40397690476</v>
+        <v>1918.40890139105</v>
       </c>
       <c r="U7" s="34" t="n">
         <f aca="false">'Income Statement'!U11</f>
-        <v>1956.12560315075</v>
+        <v>1956.1303432531</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13371,11 +13371,11 @@
       </c>
       <c r="I8" s="9" t="n">
         <f aca="false">-(Schedules!I12)</f>
-        <v>42.37</v>
+        <v>42.3699999999993</v>
       </c>
       <c r="J8" s="9" t="n">
         <f aca="false">-(Schedules!J12)</f>
-        <v>29.6000000000006</v>
+        <v>29.6000000000013</v>
       </c>
       <c r="K8" s="9" t="n">
         <f aca="false">-(Schedules!K12)</f>
@@ -13383,43 +13383,43 @@
       </c>
       <c r="L8" s="34" t="n">
         <f aca="false">-(Schedules!L12)</f>
-        <v>489.373474054859</v>
+        <v>489.375689732458</v>
       </c>
       <c r="M8" s="34" t="n">
         <f aca="false">-(Schedules!M12)</f>
-        <v>-507.136634733478</v>
+        <v>-507.135662715718</v>
       </c>
       <c r="N8" s="34" t="n">
         <f aca="false">-(Schedules!N12)</f>
-        <v>-348.748327177056</v>
+        <v>-348.747615683452</v>
       </c>
       <c r="O8" s="34" t="n">
         <f aca="false">-(Schedules!O12)</f>
-        <v>-274.445813681756</v>
+        <v>-274.445228803412</v>
       </c>
       <c r="P8" s="34" t="n">
         <f aca="false">-(Schedules!P12)</f>
-        <v>-153.771485559746</v>
+        <v>-153.771116969411</v>
       </c>
       <c r="Q8" s="34" t="n">
         <f aca="false">-(Schedules!Q12)</f>
-        <v>-174.874091581964</v>
+        <v>-174.873753836994</v>
       </c>
       <c r="R8" s="34" t="n">
         <f aca="false">-(Schedules!R12)</f>
-        <v>-177.048209415948</v>
+        <v>-177.047864773214</v>
       </c>
       <c r="S8" s="34" t="n">
         <f aca="false">-(Schedules!S12)</f>
-        <v>-181.437895126113</v>
+        <v>-181.437543097229</v>
       </c>
       <c r="T8" s="34" t="n">
         <f aca="false">-(Schedules!T12)</f>
-        <v>-183.668914688239</v>
+        <v>-183.668559697665</v>
       </c>
       <c r="U8" s="34" t="n">
         <f aca="false">-(Schedules!U12)</f>
-        <v>-192.940088074686</v>
+        <v>-192.939713550798</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13464,47 +13464,47 @@
       </c>
       <c r="K9" s="60" t="n">
         <f aca="false">((K6+K7)+K8)</f>
-        <v>950.629999999999</v>
+        <v>950.629999999998</v>
       </c>
       <c r="L9" s="61" t="n">
         <f aca="false">((L6+L7)+L8)</f>
-        <v>2745.74129126411</v>
+        <v>2745.74432420993</v>
       </c>
       <c r="M9" s="61" t="n">
         <f aca="false">((M6+M7)+M8)</f>
-        <v>3074.28650200836</v>
+        <v>3074.2889763852</v>
       </c>
       <c r="N9" s="61" t="n">
         <f aca="false">((N6+N7)+N8)</f>
-        <v>3820.46109299987</v>
+        <v>3820.46392885439</v>
       </c>
       <c r="O9" s="61" t="n">
         <f aca="false">((O6+O7)+O8)</f>
-        <v>4542.62986426485</v>
+        <v>4542.63281148022</v>
       </c>
       <c r="P9" s="61" t="n">
         <f aca="false">((P6+P7)+P8)</f>
-        <v>5149.17222052487</v>
+        <v>5149.17507219273</v>
       </c>
       <c r="Q9" s="61" t="n">
         <f aca="false">((Q6+Q7)+Q8)</f>
-        <v>5636.89007713425</v>
+        <v>5636.8929470038</v>
       </c>
       <c r="R9" s="61" t="n">
         <f aca="false">((R6+R7)+R8)</f>
-        <v>6138.01391005402</v>
+        <v>6138.01683903667</v>
       </c>
       <c r="S9" s="61" t="n">
         <f aca="false">((S6+S7)+S8)</f>
-        <v>6672.00943435631</v>
+        <v>6672.01247933188</v>
       </c>
       <c r="T9" s="61" t="n">
         <f aca="false">((T6+T7)+T8)</f>
-        <v>7242.03719515796</v>
+        <v>7242.04036044585</v>
       </c>
       <c r="U9" s="61" t="n">
         <f aca="false">((U6+U7)+U8)</f>
-        <v>7830.30642154019</v>
+        <v>7830.30973035209</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">(-(Schedules!G7)-('Balance Sheet'!G11-'Balance Sheet'!F11))</f>
-        <v>-534.05</v>
+        <v>-534.050000000001</v>
       </c>
       <c r="H11" s="9" t="n">
         <f aca="false">(-(Schedules!H7)-('Balance Sheet'!H11-'Balance Sheet'!G11))</f>
@@ -13578,43 +13578,43 @@
       </c>
       <c r="L11" s="34" t="n">
         <f aca="false">(-(Schedules!L7)-('Balance Sheet'!L11-'Balance Sheet'!K11))</f>
-        <v>-7111.455893</v>
+        <v>-7111.45332390587</v>
       </c>
       <c r="M11" s="34" t="n">
         <f aca="false">(-(Schedules!M7)-('Balance Sheet'!M11-'Balance Sheet'!L11))</f>
-        <v>-9508.49200754614</v>
+        <v>-9508.49088048454</v>
       </c>
       <c r="N11" s="34" t="n">
         <f aca="false">(-(Schedules!N7)-('Balance Sheet'!N11-'Balance Sheet'!M11))</f>
-        <v>-4241.41024862507</v>
+        <v>-4241.40942364311</v>
       </c>
       <c r="O11" s="34" t="n">
         <f aca="false">(-(Schedules!O7)-('Balance Sheet'!O11-'Balance Sheet'!N11))</f>
-        <v>-2608.29687971173</v>
+        <v>-2608.29620154108</v>
       </c>
       <c r="P11" s="34" t="n">
         <f aca="false">(-(Schedules!P7)-('Balance Sheet'!P11-'Balance Sheet'!O11))</f>
-        <v>-2199.02982963266</v>
+        <v>-2199.02940224951</v>
       </c>
       <c r="Q11" s="34" t="n">
         <f aca="false">(-(Schedules!Q7)-('Balance Sheet'!Q11-'Balance Sheet'!P11))</f>
-        <v>-2308.39833195959</v>
+        <v>-2308.39794034186</v>
       </c>
       <c r="R11" s="34" t="n">
         <f aca="false">(-(Schedules!R7)-('Balance Sheet'!R11-'Balance Sheet'!Q11))</f>
-        <v>-2493.37689186961</v>
+        <v>-2493.37649225388</v>
       </c>
       <c r="S11" s="34" t="n">
         <f aca="false">(-(Schedules!S7)-('Balance Sheet'!S11-'Balance Sheet'!R11))</f>
-        <v>-2653.82648946169</v>
+        <v>-2653.82608128166</v>
       </c>
       <c r="T11" s="34" t="n">
         <f aca="false">(-(Schedules!T7)-('Balance Sheet'!T11-'Balance Sheet'!S11))</f>
-        <v>-2830.84620312623</v>
+        <v>-2830.8457915121</v>
       </c>
       <c r="U11" s="34" t="n">
         <f aca="false">(-(Schedules!U7)-('Balance Sheet'!U11-'Balance Sheet'!T11))</f>
-        <v>-3017.91692653019</v>
+        <v>-3017.91649226704</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="G13" s="60" t="n">
         <f aca="false">(G11+G12)</f>
-        <v>-521.55</v>
+        <v>-521.550000000001</v>
       </c>
       <c r="H13" s="60" t="n">
         <f aca="false">(H11+H12)</f>
@@ -13748,43 +13748,43 @@
       </c>
       <c r="L13" s="61" t="n">
         <f aca="false">(L11+L12)</f>
-        <v>-7111.455893</v>
+        <v>-7111.45332390587</v>
       </c>
       <c r="M13" s="61" t="n">
         <f aca="false">(M11+M12)</f>
-        <v>-9508.49200754614</v>
+        <v>-9508.49088048454</v>
       </c>
       <c r="N13" s="61" t="n">
         <f aca="false">(N11+N12)</f>
-        <v>-4241.41024862507</v>
+        <v>-4241.40942364311</v>
       </c>
       <c r="O13" s="61" t="n">
         <f aca="false">(O11+O12)</f>
-        <v>-2608.29687971173</v>
+        <v>-2608.29620154108</v>
       </c>
       <c r="P13" s="61" t="n">
         <f aca="false">(P11+P12)</f>
-        <v>-2199.02982963266</v>
+        <v>-2199.02940224951</v>
       </c>
       <c r="Q13" s="61" t="n">
         <f aca="false">(Q11+Q12)</f>
-        <v>-2308.39833195959</v>
+        <v>-2308.39794034186</v>
       </c>
       <c r="R13" s="61" t="n">
         <f aca="false">(R11+R12)</f>
-        <v>-2493.37689186961</v>
+        <v>-2493.37649225388</v>
       </c>
       <c r="S13" s="61" t="n">
         <f aca="false">(S11+S12)</f>
-        <v>-2653.82648946169</v>
+        <v>-2653.82608128166</v>
       </c>
       <c r="T13" s="61" t="n">
         <f aca="false">(T11+T12)</f>
-        <v>-2830.84620312623</v>
+        <v>-2830.8457915121</v>
       </c>
       <c r="U13" s="61" t="n">
         <f aca="false">(U11+U12)</f>
-        <v>-3017.91692653019</v>
+        <v>-3017.91649226704</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13947,23 +13947,23 @@
       </c>
       <c r="M16" s="34" t="n">
         <f aca="false">('Balance Sheet'!M18-'Balance Sheet'!L18)</f>
-        <v>3392.09243648074</v>
+        <v>3392.08254230954</v>
       </c>
       <c r="N16" s="34" t="n">
         <f aca="false">('Balance Sheet'!N18-'Balance Sheet'!M18)</f>
-        <v>712.725199006156</v>
+        <v>712.720965615774</v>
       </c>
       <c r="O16" s="34" t="n">
         <f aca="false">('Balance Sheet'!O18-'Balance Sheet'!N18)</f>
-        <v>-1569.50053208112</v>
+        <v>-1569.50474638943</v>
       </c>
       <c r="P16" s="34" t="n">
         <f aca="false">('Balance Sheet'!P18-'Balance Sheet'!O18)</f>
-        <v>-2523.18067684183</v>
+        <v>-2523.18454682237</v>
       </c>
       <c r="Q16" s="34" t="n">
         <f aca="false">('Balance Sheet'!Q18-'Balance Sheet'!P18)</f>
-        <v>-12.1364265639545</v>
+        <v>-12.1142147135079</v>
       </c>
       <c r="R16" s="34" t="n">
         <f aca="false">('Balance Sheet'!R18-'Balance Sheet'!Q18)</f>
@@ -14028,43 +14028,43 @@
       </c>
       <c r="L17" s="34" t="n">
         <f aca="false">-(Schedules!L22)</f>
-        <v>-183.179169816</v>
+        <v>-183.178903777375</v>
       </c>
       <c r="M17" s="34" t="n">
         <f aca="false">-(Schedules!M22)</f>
-        <v>-281.69314379348</v>
+        <v>-281.692734736883</v>
       </c>
       <c r="N17" s="34" t="n">
         <f aca="false">-(Schedules!N22)</f>
-        <v>-291.776012188</v>
+        <v>-291.775470827046</v>
       </c>
       <c r="O17" s="34" t="n">
         <f aca="false">-(Schedules!O22)</f>
-        <v>-354.832372281323</v>
+        <v>-354.831863549709</v>
       </c>
       <c r="P17" s="34" t="n">
         <f aca="false">-(Schedules!P22)</f>
-        <v>-411.961546120644</v>
+        <v>-411.961123120846</v>
       </c>
       <c r="Q17" s="34" t="n">
         <f aca="false">-(Schedules!Q22)</f>
-        <v>-473.46415830841</v>
+        <v>-473.4638498833</v>
       </c>
       <c r="R17" s="34" t="n">
         <f aca="false">-(Schedules!R22)</f>
-        <v>-533.096977197171</v>
+        <v>-533.096816686531</v>
       </c>
       <c r="S17" s="34" t="n">
         <f aca="false">-(Schedules!S22)</f>
-        <v>-595.513656264118</v>
+        <v>-595.513681287214</v>
       </c>
       <c r="T17" s="34" t="n">
         <f aca="false">-(Schedules!T22)</f>
-        <v>-660.875739788952</v>
+        <v>-660.876002250295</v>
       </c>
       <c r="U17" s="34" t="n">
         <f aca="false">-(Schedules!U22)</f>
-        <v>-728.053725984277</v>
+        <v>-728.05429207797</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14198,43 +14198,43 @@
       </c>
       <c r="L19" s="61" t="n">
         <f aca="false">(((L15+L16)+L17)+L18)</f>
-        <v>6371.820830184</v>
+        <v>6371.82109622263</v>
       </c>
       <c r="M19" s="61" t="n">
         <f aca="false">(((M15+M16)+M17)+M18)</f>
-        <v>3110.39929268727</v>
+        <v>3110.38980757266</v>
       </c>
       <c r="N19" s="61" t="n">
         <f aca="false">(((N15+N16)+N17)+N18)</f>
-        <v>420.949186818156</v>
+        <v>420.945494788728</v>
       </c>
       <c r="O19" s="61" t="n">
         <f aca="false">(((O15+O16)+O17)+O18)</f>
-        <v>-1934.33290436244</v>
+        <v>-1934.33660993914</v>
       </c>
       <c r="P19" s="61" t="n">
         <f aca="false">(((P15+P16)+P17)+P18)</f>
-        <v>-2950.14222296247</v>
+        <v>-2950.14566994322</v>
       </c>
       <c r="Q19" s="61" t="n">
         <f aca="false">(((Q15+Q16)+Q17)+Q18)</f>
-        <v>-500.600584872365</v>
+        <v>-500.578064596808</v>
       </c>
       <c r="R19" s="61" t="n">
         <f aca="false">(((R15+R16)+R17)+R18)</f>
-        <v>-548.096977197171</v>
+        <v>-548.096816686531</v>
       </c>
       <c r="S19" s="61" t="n">
         <f aca="false">(((S15+S16)+S17)+S18)</f>
-        <v>-610.513656264118</v>
+        <v>-610.513681287214</v>
       </c>
       <c r="T19" s="61" t="n">
         <f aca="false">(((T15+T16)+T17)+T18)</f>
-        <v>-670.875739788952</v>
+        <v>-670.876002250295</v>
       </c>
       <c r="U19" s="61" t="n">
         <f aca="false">(((U15+U16)+U17)+U18)</f>
-        <v>-738.053725984277</v>
+        <v>-738.05429207797</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14288,15 +14288,15 @@
       </c>
       <c r="G21" s="62" t="n">
         <f aca="false">((G9+G13)+G19)</f>
-        <v>670.76</v>
+        <v>670.759999999999</v>
       </c>
       <c r="H21" s="62" t="n">
         <f aca="false">((H9+H13)+H19)</f>
-        <v>610.739999999999</v>
+        <v>610.74</v>
       </c>
       <c r="I21" s="62" t="n">
         <f aca="false">((I9+I13)+I19)</f>
-        <v>-530.08</v>
+        <v>-530.080000000001</v>
       </c>
       <c r="J21" s="62" t="n">
         <f aca="false">((J9+J13)+J19)</f>
@@ -14304,47 +14304,47 @@
       </c>
       <c r="K21" s="62" t="n">
         <f aca="false">((K9+K13)+K19)</f>
-        <v>-9.33000000000061</v>
+        <v>-9.33000000000243</v>
       </c>
       <c r="L21" s="63" t="n">
         <f aca="false">((L9+L13)+L19)</f>
-        <v>2006.10622844811</v>
+        <v>2006.11209652668</v>
       </c>
       <c r="M21" s="63" t="n">
         <f aca="false">((M9+M13)+M19)</f>
-        <v>-3323.80621285051</v>
+        <v>-3323.81209652668</v>
       </c>
       <c r="N21" s="63" t="n">
         <f aca="false">((N9+N13)+N19)</f>
-        <v>3.11929526333188E-005</v>
+        <v>0</v>
       </c>
       <c r="O21" s="63" t="n">
         <f aca="false">((O9+O13)+O19)</f>
-        <v>8.01906808192143E-005</v>
+        <v>0</v>
       </c>
       <c r="P21" s="63" t="n">
         <f aca="false">((P9+P13)+P19)</f>
-        <v>0.000167929739291139</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="63" t="n">
         <f aca="false">((Q9+Q13)+Q19)</f>
-        <v>2827.8911603023</v>
+        <v>2827.91694206513</v>
       </c>
       <c r="R21" s="63" t="n">
         <f aca="false">((R9+R13)+R19)</f>
-        <v>3096.54004098724</v>
+        <v>3096.54353009627</v>
       </c>
       <c r="S21" s="63" t="n">
         <f aca="false">((S9+S13)+S19)</f>
-        <v>3407.6692886305</v>
+        <v>3407.672716763</v>
       </c>
       <c r="T21" s="63" t="n">
         <f aca="false">((T9+T13)+T19)</f>
-        <v>3740.31525224278</v>
+        <v>3740.31856668346</v>
       </c>
       <c r="U21" s="63" t="n">
         <f aca="false">((U9+U13)+U19)</f>
-        <v>4074.33576902572</v>
+        <v>4074.33894600708</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14397,39 +14397,39 @@
       </c>
       <c r="M22" s="34" t="n">
         <f aca="false">'Balance Sheet'!L6</f>
-        <v>4323.80622844811</v>
+        <v>4323.81209652668</v>
       </c>
       <c r="N22" s="34" t="n">
         <f aca="false">'Balance Sheet'!M6</f>
-        <v>1000.0000155976</v>
+        <v>1000</v>
       </c>
       <c r="O22" s="34" t="n">
         <f aca="false">'Balance Sheet'!N6</f>
-        <v>1000.00004679055</v>
+        <v>1000</v>
       </c>
       <c r="P22" s="34" t="n">
         <f aca="false">'Balance Sheet'!O6</f>
-        <v>1000.00012698124</v>
+        <v>1000</v>
       </c>
       <c r="Q22" s="34" t="n">
         <f aca="false">'Balance Sheet'!P6</f>
-        <v>1000.00029491098</v>
+        <v>1000</v>
       </c>
       <c r="R22" s="34" t="n">
         <f aca="false">'Balance Sheet'!Q6</f>
-        <v>3827.89145521328</v>
+        <v>3827.91694206513</v>
       </c>
       <c r="S22" s="34" t="n">
         <f aca="false">'Balance Sheet'!R6</f>
-        <v>6924.43149620052</v>
+        <v>6924.4604721614</v>
       </c>
       <c r="T22" s="34" t="n">
         <f aca="false">'Balance Sheet'!S6</f>
-        <v>10332.100784831</v>
+        <v>10332.1331889244</v>
       </c>
       <c r="U22" s="34" t="n">
         <f aca="false">'Balance Sheet'!T6</f>
-        <v>14072.4160370738</v>
+        <v>14072.4517556079</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="D23" s="60" t="n">
         <f aca="false">(D22+D21)</f>
-        <v>93.8800000000002</v>
+        <v>93.8800000000003</v>
       </c>
       <c r="E23" s="60" t="n">
         <f aca="false">(E22+E21)</f>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="G23" s="60" t="n">
         <f aca="false">(G22+G21)</f>
-        <v>985.24</v>
+        <v>985.239999999999</v>
       </c>
       <c r="H23" s="60" t="n">
         <f aca="false">(H22+H21)</f>
@@ -14478,43 +14478,43 @@
       </c>
       <c r="L23" s="61" t="n">
         <f aca="false">(L22+L21)</f>
-        <v>4323.80622844811</v>
+        <v>4323.81209652668</v>
       </c>
       <c r="M23" s="61" t="n">
         <f aca="false">(M22+M21)</f>
-        <v>1000.0000155976</v>
+        <v>1000</v>
       </c>
       <c r="N23" s="61" t="n">
         <f aca="false">(N22+N21)</f>
-        <v>1000.00004679055</v>
+        <v>1000</v>
       </c>
       <c r="O23" s="61" t="n">
         <f aca="false">(O22+O21)</f>
-        <v>1000.00012698124</v>
+        <v>1000</v>
       </c>
       <c r="P23" s="61" t="n">
         <f aca="false">(P22+P21)</f>
-        <v>1000.00029491098</v>
+        <v>1000</v>
       </c>
       <c r="Q23" s="61" t="n">
         <f aca="false">(Q22+Q21)</f>
-        <v>3827.89145521328</v>
+        <v>3827.91694206513</v>
       </c>
       <c r="R23" s="61" t="n">
         <f aca="false">(R22+R21)</f>
-        <v>6924.43149620052</v>
+        <v>6924.4604721614</v>
       </c>
       <c r="S23" s="61" t="n">
         <f aca="false">(S22+S21)</f>
-        <v>10332.100784831</v>
+        <v>10332.1331889244</v>
       </c>
       <c r="T23" s="61" t="n">
         <f aca="false">(T22+T21)</f>
-        <v>14072.4160370738</v>
+        <v>14072.4517556079</v>
       </c>
       <c r="U23" s="61" t="n">
         <f aca="false">(U22+U21)</f>
-        <v>18146.7518060995</v>
+        <v>18146.7907016149</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14801,11 +14801,11 @@
       </c>
       <c r="I28" s="64" t="n">
         <f aca="false">(I9-I25)</f>
-        <v>-168.45</v>
+        <v>-168.450000000001</v>
       </c>
       <c r="J28" s="64" t="n">
         <f aca="false">(J9-J25)</f>
-        <v>-21.2099999999996</v>
+        <v>-21.2099999999987</v>
       </c>
       <c r="K28" s="64" t="n">
         <f aca="false">(K9-K25)</f>
@@ -14813,43 +14813,43 @@
       </c>
       <c r="L28" s="65" t="n">
         <f aca="false">(L9-L25)</f>
-        <v>2745.74129126411</v>
+        <v>2745.74432420993</v>
       </c>
       <c r="M28" s="65" t="n">
         <f aca="false">(M9-M25)</f>
-        <v>3074.28650200836</v>
+        <v>3074.2889763852</v>
       </c>
       <c r="N28" s="65" t="n">
         <f aca="false">(N9-N25)</f>
-        <v>3820.46109299987</v>
+        <v>3820.46392885439</v>
       </c>
       <c r="O28" s="65" t="n">
         <f aca="false">(O9-O25)</f>
-        <v>4542.62986426485</v>
+        <v>4542.63281148022</v>
       </c>
       <c r="P28" s="65" t="n">
         <f aca="false">(P9-P25)</f>
-        <v>5149.17222052487</v>
+        <v>5149.17507219273</v>
       </c>
       <c r="Q28" s="65" t="n">
         <f aca="false">(Q9-Q25)</f>
-        <v>5636.89007713425</v>
+        <v>5636.8929470038</v>
       </c>
       <c r="R28" s="65" t="n">
         <f aca="false">(R9-R25)</f>
-        <v>6138.01391005402</v>
+        <v>6138.01683903667</v>
       </c>
       <c r="S28" s="65" t="n">
         <f aca="false">(S9-S25)</f>
-        <v>6672.00943435631</v>
+        <v>6672.01247933188</v>
       </c>
       <c r="T28" s="65" t="n">
         <f aca="false">(T9-T25)</f>
-        <v>7242.03719515796</v>
+        <v>7242.04036044585</v>
       </c>
       <c r="U28" s="65" t="n">
         <f aca="false">(U9-U25)</f>
-        <v>7830.30642154019</v>
+        <v>7830.30973035209</v>
       </c>
     </row>
   </sheetData>
@@ -15026,39 +15026,39 @@
       </c>
       <c r="M6" s="34" t="n">
         <f aca="false">'Balance Sheet'!L10</f>
-        <v>17797.87772343</v>
+        <v>17797.874684734</v>
       </c>
       <c r="N6" s="34" t="n">
         <f aca="false">'Balance Sheet'!M10</f>
-        <v>25063.7157652637</v>
+        <v>25063.7077998061</v>
       </c>
       <c r="O6" s="34" t="n">
         <f aca="false">'Balance Sheet'!N10</f>
-        <v>26829.0585332768</v>
+        <v>26829.0438853264</v>
       </c>
       <c r="P6" s="34" t="n">
         <f aca="false">'Balance Sheet'!O10</f>
-        <v>26970.2814941649</v>
+        <v>26970.2601174661</v>
       </c>
       <c r="Q6" s="34" t="n">
         <f aca="false">'Balance Sheet'!P10</f>
-        <v>26916.8904837743</v>
+        <v>26916.8628040887</v>
       </c>
       <c r="R6" s="34" t="n">
         <f aca="false">'Balance Sheet'!Q10</f>
-        <v>27008.5783108577</v>
+        <v>27008.5447806036</v>
       </c>
       <c r="S6" s="34" t="n">
         <f aca="false">'Balance Sheet'!R10</f>
-        <v>27271.7298212504</v>
+        <v>27271.6908196009</v>
       </c>
       <c r="T6" s="34" t="n">
         <f aca="false">'Balance Sheet'!S10</f>
-        <v>27669.4211544973</v>
+        <v>27669.3769848422</v>
       </c>
       <c r="U6" s="34" t="n">
         <f aca="false">'Balance Sheet'!T10</f>
-        <v>28213.4856872016</v>
+        <v>28213.4365930602</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15182,43 +15182,43 @@
       </c>
       <c r="L8" s="34" t="n">
         <f aca="false">'Income Statement'!L11</f>
-        <v>729.87473097</v>
+        <v>729.877769666012</v>
       </c>
       <c r="M8" s="34" t="n">
         <f aca="false">'Income Statement'!M11</f>
-        <v>1233.98025619857</v>
+        <v>1233.98518296023</v>
       </c>
       <c r="N8" s="34" t="n">
         <f aca="false">'Income Statement'!N11</f>
-        <v>1737.74260515303</v>
+        <v>1737.74928764579</v>
       </c>
       <c r="O8" s="34" t="n">
         <f aca="false">'Income Statement'!O11</f>
-        <v>1860.13911528768</v>
+        <v>1860.14584403606</v>
       </c>
       <c r="P8" s="34" t="n">
         <f aca="false">'Income Statement'!P11</f>
-        <v>1869.93052683494</v>
+        <v>1869.93682982176</v>
       </c>
       <c r="Q8" s="34" t="n">
         <f aca="false">'Income Statement'!Q11</f>
-        <v>1866.22876791152</v>
+        <v>1866.23461847997</v>
       </c>
       <c r="R8" s="34" t="n">
         <f aca="false">'Income Statement'!R11</f>
-        <v>1872.5857600267</v>
+        <v>1872.59123142213</v>
       </c>
       <c r="S8" s="34" t="n">
         <f aca="false">'Income Statement'!S11</f>
-        <v>1890.83084369675</v>
+        <v>1890.83601170232</v>
       </c>
       <c r="T8" s="34" t="n">
         <f aca="false">'Income Statement'!T11</f>
-        <v>1918.40397690476</v>
+        <v>1918.40890139105</v>
       </c>
       <c r="U8" s="34" t="n">
         <f aca="false">'Income Statement'!U11</f>
-        <v>1956.12560315075</v>
+        <v>1956.1303432531</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15267,43 +15267,43 @@
       </c>
       <c r="L9" s="61" t="n">
         <f aca="false">((L6+L7)-L8)</f>
-        <v>17797.87772343</v>
+        <v>17797.874684734</v>
       </c>
       <c r="M9" s="61" t="n">
         <f aca="false">((M6+M7)-M8)</f>
-        <v>25063.7157652637</v>
+        <v>25063.7077998061</v>
       </c>
       <c r="N9" s="61" t="n">
         <f aca="false">((N6+N7)-N8)</f>
-        <v>26829.0585332768</v>
+        <v>26829.0438853264</v>
       </c>
       <c r="O9" s="61" t="n">
         <f aca="false">((O6+O7)-O8)</f>
-        <v>26970.2814941649</v>
+        <v>26970.2601174661</v>
       </c>
       <c r="P9" s="61" t="n">
         <f aca="false">((P6+P7)-P8)</f>
-        <v>26916.8904837743</v>
+        <v>26916.8628040887</v>
       </c>
       <c r="Q9" s="61" t="n">
         <f aca="false">((Q6+Q7)-Q8)</f>
-        <v>27008.5783108577</v>
+        <v>27008.5447806036</v>
       </c>
       <c r="R9" s="61" t="n">
         <f aca="false">((R6+R7)-R8)</f>
-        <v>27271.7298212504</v>
+        <v>27271.6908196009</v>
       </c>
       <c r="S9" s="61" t="n">
         <f aca="false">((S6+S7)-S8)</f>
-        <v>27669.4211544973</v>
+        <v>27669.3769848422</v>
       </c>
       <c r="T9" s="61" t="n">
         <f aca="false">((T6+T7)-T8)</f>
-        <v>28213.4856872016</v>
+        <v>28213.4365930602</v>
       </c>
       <c r="U9" s="61" t="n">
         <f aca="false">((U6+U7)-U8)</f>
-        <v>28886.6293802962</v>
+        <v>28886.5755460525</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="I11" s="30" t="n">
         <f aca="false">(((('Balance Sheet'!I7+'Balance Sheet'!I8)+'Balance Sheet'!I9)-'Balance Sheet'!I20)-'Balance Sheet'!I21)</f>
-        <v>560.63</v>
+        <v>560.630000000001</v>
       </c>
       <c r="J11" s="30" t="n">
         <f aca="false">(((('Balance Sheet'!J7+'Balance Sheet'!J8)+'Balance Sheet'!J9)-'Balance Sheet'!J20)-'Balance Sheet'!J21)</f>
@@ -15377,43 +15377,43 @@
       </c>
       <c r="L11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!L7+'Balance Sheet'!L8)+'Balance Sheet'!L9)-'Balance Sheet'!L20)-'Balance Sheet'!L21)</f>
-        <v>1228.45652594514</v>
+        <v>1228.45431026754</v>
       </c>
       <c r="M11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!M7+'Balance Sheet'!M8)+'Balance Sheet'!M9)-'Balance Sheet'!M20)-'Balance Sheet'!M21)</f>
-        <v>1735.59316067862</v>
+        <v>1735.58997298326</v>
       </c>
       <c r="N11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!N7+'Balance Sheet'!N8)+'Balance Sheet'!N9)-'Balance Sheet'!N20)-'Balance Sheet'!N21)</f>
-        <v>2084.34148785568</v>
+        <v>2084.33758866671</v>
       </c>
       <c r="O11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!O7+'Balance Sheet'!O8)+'Balance Sheet'!O9)-'Balance Sheet'!O20)-'Balance Sheet'!O21)</f>
-        <v>2358.78730153743</v>
+        <v>2358.78281747013</v>
       </c>
       <c r="P11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!P7+'Balance Sheet'!P8)+'Balance Sheet'!P9)-'Balance Sheet'!P20)-'Balance Sheet'!P21)</f>
-        <v>2512.55878709718</v>
+        <v>2512.55393443954</v>
       </c>
       <c r="Q11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!Q7+'Balance Sheet'!Q8)+'Balance Sheet'!Q9)-'Balance Sheet'!Q20)-'Balance Sheet'!Q21)</f>
-        <v>2687.43287867914</v>
+        <v>2687.42768827653</v>
       </c>
       <c r="R11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!R7+'Balance Sheet'!R8)+'Balance Sheet'!R9)-'Balance Sheet'!R20)-'Balance Sheet'!R21)</f>
-        <v>2864.48108809509</v>
+        <v>2864.47555304975</v>
       </c>
       <c r="S11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!S7+'Balance Sheet'!S8)+'Balance Sheet'!S9)-'Balance Sheet'!S20)-'Balance Sheet'!S21)</f>
-        <v>3045.9189832212</v>
+        <v>3045.91309614697</v>
       </c>
       <c r="T11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!T7+'Balance Sheet'!T8)+'Balance Sheet'!T9)-'Balance Sheet'!T20)-'Balance Sheet'!T21)</f>
-        <v>3229.58789790944</v>
+        <v>3229.58165584464</v>
       </c>
       <c r="U11" s="31" t="n">
         <f aca="false">(((('Balance Sheet'!U7+'Balance Sheet'!U8)+'Balance Sheet'!U9)-'Balance Sheet'!U20)-'Balance Sheet'!U21)</f>
-        <v>3422.52798598413</v>
+        <v>3422.52136939544</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15450,11 +15450,11 @@
       </c>
       <c r="I12" s="51" t="n">
         <f aca="false">(I11-H11)</f>
-        <v>-42.37</v>
+        <v>-42.3699999999993</v>
       </c>
       <c r="J12" s="51" t="n">
         <f aca="false">(J11-I11)</f>
-        <v>-29.6000000000006</v>
+        <v>-29.6000000000013</v>
       </c>
       <c r="K12" s="51" t="n">
         <f aca="false">(K11-J11)</f>
@@ -15462,43 +15462,43 @@
       </c>
       <c r="L12" s="57" t="n">
         <f aca="false">(L11-K11)</f>
-        <v>-489.373474054859</v>
+        <v>-489.375689732458</v>
       </c>
       <c r="M12" s="57" t="n">
         <f aca="false">(M11-L11)</f>
-        <v>507.136634733478</v>
+        <v>507.135662715718</v>
       </c>
       <c r="N12" s="57" t="n">
         <f aca="false">(N11-M11)</f>
-        <v>348.748327177056</v>
+        <v>348.747615683452</v>
       </c>
       <c r="O12" s="57" t="n">
         <f aca="false">(O11-N11)</f>
-        <v>274.445813681756</v>
+        <v>274.445228803412</v>
       </c>
       <c r="P12" s="57" t="n">
         <f aca="false">(P11-O11)</f>
-        <v>153.771485559746</v>
+        <v>153.771116969411</v>
       </c>
       <c r="Q12" s="57" t="n">
         <f aca="false">(Q11-P11)</f>
-        <v>174.874091581964</v>
+        <v>174.873753836994</v>
       </c>
       <c r="R12" s="57" t="n">
         <f aca="false">(R11-Q11)</f>
-        <v>177.048209415948</v>
+        <v>177.047864773214</v>
       </c>
       <c r="S12" s="57" t="n">
         <f aca="false">(S11-R11)</f>
-        <v>181.437895126113</v>
+        <v>181.437543097229</v>
       </c>
       <c r="T12" s="57" t="n">
         <f aca="false">(T11-S11)</f>
-        <v>183.668914688239</v>
+        <v>183.668559697665</v>
       </c>
       <c r="U12" s="57" t="n">
         <f aca="false">(U11-T11)</f>
-        <v>192.940088074686</v>
+        <v>192.939713550798</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="G13" s="49" t="n">
         <f aca="false">(IFERROR((G11)/('Income Statement'!G6),0)*365)</f>
-        <v>76.67045744503</v>
+        <v>76.6704574450301</v>
       </c>
       <c r="H13" s="49" t="n">
         <f aca="false">(IFERROR((H11)/('Income Statement'!H6),0)*365)</f>
@@ -15547,43 +15547,43 @@
       </c>
       <c r="L13" s="66" t="n">
         <f aca="false">(IFERROR((L11)/('Income Statement'!L6),0)*365)</f>
-        <v>70.278785</v>
+        <v>70.2786582432723</v>
       </c>
       <c r="M13" s="66" t="n">
         <f aca="false">(IFERROR((M11)/('Income Statement'!M6),0)*365)</f>
-        <v>69.014785</v>
+        <v>69.0146582432723</v>
       </c>
       <c r="N13" s="66" t="n">
         <f aca="false">(IFERROR((N11)/('Income Statement'!N6),0)*365)</f>
-        <v>67.758785</v>
+        <v>67.7586582432723</v>
       </c>
       <c r="O13" s="66" t="n">
         <f aca="false">(IFERROR((O11)/('Income Statement'!O6),0)*365)</f>
-        <v>66.678785</v>
+        <v>66.6786582432723</v>
       </c>
       <c r="P13" s="66" t="n">
         <f aca="false">(IFERROR((P11)/('Income Statement'!P6),0)*365)</f>
-        <v>65.630785</v>
+        <v>65.6306582432722</v>
       </c>
       <c r="Q13" s="66" t="n">
         <f aca="false">(IFERROR((Q11)/('Income Statement'!Q6),0)*365)</f>
-        <v>65.6307850000001</v>
+        <v>65.6306582432723</v>
       </c>
       <c r="R13" s="66" t="n">
         <f aca="false">(IFERROR((R11)/('Income Statement'!R6),0)*365)</f>
-        <v>65.598785</v>
+        <v>65.5986582432723</v>
       </c>
       <c r="S13" s="66" t="n">
         <f aca="false">(IFERROR((S11)/('Income Statement'!S6),0)*365)</f>
-        <v>65.582785</v>
+        <v>65.5826582432723</v>
       </c>
       <c r="T13" s="66" t="n">
         <f aca="false">(IFERROR((T11)/('Income Statement'!T6),0)*365)</f>
-        <v>65.582785</v>
+        <v>65.5826582432723</v>
       </c>
       <c r="U13" s="66" t="n">
         <f aca="false">(IFERROR((U11)/('Income Statement'!U6),0)*365)</f>
-        <v>65.566785</v>
+        <v>65.5666582432723</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15742,43 +15742,43 @@
       </c>
       <c r="L16" s="34" t="n">
         <f aca="false">(('Cash Flow'!L15+'Cash Flow'!L17)+'Cash Flow'!L18)</f>
-        <v>6371.820830184</v>
+        <v>6371.82109622263</v>
       </c>
       <c r="M16" s="34" t="n">
         <f aca="false">(('Cash Flow'!M15+'Cash Flow'!M17)+'Cash Flow'!M18)</f>
-        <v>-281.69314379348</v>
+        <v>-281.692734736883</v>
       </c>
       <c r="N16" s="34" t="n">
         <f aca="false">(('Cash Flow'!N15+'Cash Flow'!N17)+'Cash Flow'!N18)</f>
-        <v>-291.776012188</v>
+        <v>-291.775470827046</v>
       </c>
       <c r="O16" s="34" t="n">
         <f aca="false">(('Cash Flow'!O15+'Cash Flow'!O17)+'Cash Flow'!O18)</f>
-        <v>-364.832372281323</v>
+        <v>-364.831863549709</v>
       </c>
       <c r="P16" s="34" t="n">
         <f aca="false">(('Cash Flow'!P15+'Cash Flow'!P17)+'Cash Flow'!P18)</f>
-        <v>-426.961546120644</v>
+        <v>-426.961123120846</v>
       </c>
       <c r="Q16" s="34" t="n">
         <f aca="false">(('Cash Flow'!Q15+'Cash Flow'!Q17)+'Cash Flow'!Q18)</f>
-        <v>-488.46415830841</v>
+        <v>-488.4638498833</v>
       </c>
       <c r="R16" s="34" t="n">
         <f aca="false">(('Cash Flow'!R15+'Cash Flow'!R17)+'Cash Flow'!R18)</f>
-        <v>-548.096977197171</v>
+        <v>-548.096816686531</v>
       </c>
       <c r="S16" s="34" t="n">
         <f aca="false">(('Cash Flow'!S15+'Cash Flow'!S17)+'Cash Flow'!S18)</f>
-        <v>-610.513656264118</v>
+        <v>-610.513681287214</v>
       </c>
       <c r="T16" s="34" t="n">
         <f aca="false">(('Cash Flow'!T15+'Cash Flow'!T17)+'Cash Flow'!T18)</f>
-        <v>-670.875739788952</v>
+        <v>-670.876002250295</v>
       </c>
       <c r="U16" s="34" t="n">
         <f aca="false">(('Cash Flow'!U15+'Cash Flow'!U17)+'Cash Flow'!U18)</f>
-        <v>-738.053725984277</v>
+        <v>-738.05429207797</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="D17" s="9" t="n">
         <f aca="false">((('Balance Sheet'!C6+'Cash Flow'!D9)+'Cash Flow'!D13)+D16)</f>
-        <v>93.8800000000002</v>
+        <v>93.8800000000003</v>
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">((('Balance Sheet'!D6+'Cash Flow'!E9)+'Cash Flow'!E13)+E16)</f>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="G17" s="9" t="n">
         <f aca="false">((('Balance Sheet'!F6+'Cash Flow'!G9)+'Cash Flow'!G13)+G16)</f>
-        <v>985.24</v>
+        <v>985.239999999999</v>
       </c>
       <c r="H17" s="9" t="n">
         <f aca="false">((('Balance Sheet'!G6+'Cash Flow'!H9)+'Cash Flow'!H13)+H16)</f>
@@ -15827,43 +15827,43 @@
       </c>
       <c r="L17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!K6+'Cash Flow'!L9)+'Cash Flow'!L13)+L16)</f>
-        <v>4323.80622400886</v>
+        <v>4323.81209652668</v>
       </c>
       <c r="M17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!L6+'Cash Flow'!M9)+'Cash Flow'!M13)+M16)</f>
-        <v>-2392.09243648074</v>
+        <v>-2392.08254230954</v>
       </c>
       <c r="N17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!M6+'Cash Flow'!N9)+'Cash Flow'!N13)+N16)</f>
-        <v>287.274800993844</v>
+        <v>287.279034384226</v>
       </c>
       <c r="O17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!N6+'Cash Flow'!O9)+'Cash Flow'!O13)+O16)</f>
-        <v>2569.50053208112</v>
+        <v>2569.50474638943</v>
       </c>
       <c r="P17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!O6+'Cash Flow'!P9)+'Cash Flow'!P13)+P16)</f>
-        <v>3523.18067684183</v>
+        <v>3523.18454682237</v>
       </c>
       <c r="Q17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!P6+'Cash Flow'!Q9)+'Cash Flow'!Q13)+Q16)</f>
-        <v>3840.02713354262</v>
+        <v>3840.03115677864</v>
       </c>
       <c r="R17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!Q6+'Cash Flow'!R9)+'Cash Flow'!R13)+R16)</f>
-        <v>6924.42994673367</v>
+        <v>6924.4604721614</v>
       </c>
       <c r="S17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!R6+'Cash Flow'!S9)+'Cash Flow'!S13)+S16)</f>
-        <v>10332.0981012463</v>
+        <v>10332.1331889244</v>
       </c>
       <c r="T17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!S6+'Cash Flow'!T9)+'Cash Flow'!T13)+T16)</f>
-        <v>14072.411735707</v>
+        <v>14072.4517556078</v>
       </c>
       <c r="U17" s="34" t="n">
         <f aca="false">((('Balance Sheet'!T6+'Cash Flow'!U9)+'Cash Flow'!U13)+U16)</f>
-        <v>18146.7452828377</v>
+        <v>18146.7907016149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15916,11 +15916,11 @@
       </c>
       <c r="M18" s="34" t="n">
         <f aca="false">MAX((Drivers!M29-M17),0)</f>
-        <v>3392.09243648074</v>
+        <v>3392.08254230954</v>
       </c>
       <c r="N18" s="34" t="n">
         <f aca="false">MAX((Drivers!N29-N17),0)</f>
-        <v>712.725199006156</v>
+        <v>712.720965615774</v>
       </c>
       <c r="O18" s="34" t="n">
         <f aca="false">MAX((Drivers!O29-O17),0)</f>
@@ -16009,15 +16009,15 @@
       </c>
       <c r="O19" s="34" t="n">
         <f aca="false">MIN('Balance Sheet'!N18,MAX((O17-Drivers!O29),0))</f>
-        <v>1569.50053208112</v>
+        <v>1569.50474638943</v>
       </c>
       <c r="P19" s="34" t="n">
         <f aca="false">MIN('Balance Sheet'!O18,MAX((P17-Drivers!P29),0))</f>
-        <v>2523.18067684183</v>
+        <v>2523.18454682237</v>
       </c>
       <c r="Q19" s="34" t="n">
         <f aca="false">MIN('Balance Sheet'!P18,MAX((Q17-Drivers!Q29),0))</f>
-        <v>12.1364265639545</v>
+        <v>12.1142147135079</v>
       </c>
       <c r="R19" s="34" t="n">
         <f aca="false">MIN('Balance Sheet'!Q18,MAX((R17-Drivers!R29),0))</f>
@@ -16086,23 +16086,23 @@
       </c>
       <c r="M20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!L19,'Balance Sheet'!M19)</f>
-        <v>8594.96621824037</v>
+        <v>8594.96127115477</v>
       </c>
       <c r="N20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!M19,'Balance Sheet'!N19)</f>
-        <v>10647.3750359838</v>
+        <v>10647.3630251174</v>
       </c>
       <c r="O20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!N19,'Balance Sheet'!O19)</f>
-        <v>10213.9873694463</v>
+        <v>10213.9711347306</v>
       </c>
       <c r="P20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!O19,'Balance Sheet'!P19)</f>
-        <v>8155.14676498487</v>
+        <v>8155.1264881247</v>
       </c>
       <c r="Q20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!P19,'Balance Sheet'!Q19)</f>
-        <v>6872.48821328198</v>
+        <v>6872.47710735675</v>
       </c>
       <c r="R20" s="34" t="n">
         <f aca="false">AVERAGE('Balance Sheet'!Q19,'Balance Sheet'!R19)</f>
@@ -16182,43 +16182,43 @@
       </c>
       <c r="L22" s="34" t="n">
         <f aca="false">('Income Statement'!L18*Drivers!L28)</f>
-        <v>183.179170348283</v>
+        <v>183.178903777375</v>
       </c>
       <c r="M22" s="34" t="n">
         <f aca="false">('Income Statement'!M18*Drivers!M28)</f>
-        <v>281.69314379348</v>
+        <v>281.692734736883</v>
       </c>
       <c r="N22" s="34" t="n">
         <f aca="false">('Income Statement'!N18*Drivers!N28)</f>
-        <v>291.776012188</v>
+        <v>291.775470827046</v>
       </c>
       <c r="O22" s="34" t="n">
         <f aca="false">('Income Statement'!O18*Drivers!O28)</f>
-        <v>354.832372281323</v>
+        <v>354.831863549709</v>
       </c>
       <c r="P22" s="34" t="n">
         <f aca="false">('Income Statement'!P18*Drivers!P28)</f>
-        <v>411.961546120644</v>
+        <v>411.961123120846</v>
       </c>
       <c r="Q22" s="34" t="n">
         <f aca="false">('Income Statement'!Q18*Drivers!Q28)</f>
-        <v>473.46415830841</v>
+        <v>473.4638498833</v>
       </c>
       <c r="R22" s="34" t="n">
         <f aca="false">('Income Statement'!R18*Drivers!R28)</f>
-        <v>533.096977197171</v>
+        <v>533.096816686531</v>
       </c>
       <c r="S22" s="34" t="n">
         <f aca="false">('Income Statement'!S18*Drivers!S28)</f>
-        <v>595.513656264118</v>
+        <v>595.513681287214</v>
       </c>
       <c r="T22" s="34" t="n">
         <f aca="false">('Income Statement'!T18*Drivers!T28)</f>
-        <v>660.875739788952</v>
+        <v>660.876002250295</v>
       </c>
       <c r="U22" s="34" t="n">
         <f aca="false">('Income Statement'!U18*Drivers!U28)</f>
-        <v>728.053725984277</v>
+        <v>728.05429207797</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16226,31 +16226,31 @@
         <v>251</v>
       </c>
       <c r="B23" s="67" t="n">
-        <v>56847632</v>
+        <v>5.6847632</v>
       </c>
       <c r="C23" s="67" t="n">
-        <v>60710000</v>
+        <v>6.071</v>
       </c>
       <c r="D23" s="67" t="n">
-        <v>60710000</v>
+        <v>6.071</v>
       </c>
       <c r="E23" s="67" t="n">
-        <v>59929200</v>
+        <v>5.99292</v>
       </c>
       <c r="F23" s="67" t="n">
-        <v>59929200</v>
+        <v>5.99292</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>60709992</v>
+        <v>6.0709992</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1864707450</v>
+        <v>186.470745</v>
       </c>
       <c r="I23" s="67" t="n">
-        <v>2100001567</v>
+        <v>210.0001567</v>
       </c>
       <c r="J23" s="67" t="n">
-        <v>2100001567</v>
+        <v>210.0001567</v>
       </c>
       <c r="K23" s="67" t="n">
         <v>232.35</v>
@@ -16342,43 +16342,43 @@
       </c>
       <c r="L24" s="31" t="n">
         <f aca="false">('Balance Sheet'!L15+'Balance Sheet'!L16)</f>
-        <v>18775.813915891</v>
+        <v>18775.8119610341</v>
       </c>
       <c r="M24" s="31" t="n">
         <f aca="false">('Balance Sheet'!M15+'Balance Sheet'!M16)</f>
-        <v>20841.5636526408</v>
+        <v>20841.5586824379</v>
       </c>
       <c r="N24" s="31" t="n">
         <f aca="false">('Balance Sheet'!N15+'Balance Sheet'!N16)</f>
-        <v>22981.2544554766</v>
+        <v>22981.2454685029</v>
       </c>
       <c r="O24" s="31" t="n">
         <f aca="false">('Balance Sheet'!O15+'Balance Sheet'!O16)</f>
-        <v>25583.3586458543</v>
+        <v>25583.3458012008</v>
       </c>
       <c r="P24" s="31" t="n">
         <f aca="false">('Balance Sheet'!P15+'Balance Sheet'!P16)</f>
-        <v>28604.4102789833</v>
+        <v>28604.3940374203</v>
       </c>
       <c r="Q24" s="31" t="n">
         <f aca="false">('Balance Sheet'!Q15+'Balance Sheet'!Q16)</f>
-        <v>32076.4815214796</v>
+        <v>32076.4622698978</v>
       </c>
       <c r="R24" s="31" t="n">
         <f aca="false">('Balance Sheet'!R15+'Balance Sheet'!R16)</f>
-        <v>35985.8609037257</v>
+        <v>35985.8389255991</v>
       </c>
       <c r="S24" s="31" t="n">
         <f aca="false">('Balance Sheet'!S15+'Balance Sheet'!S16)</f>
-        <v>40352.9637332472</v>
+        <v>40352.9392550386</v>
       </c>
       <c r="T24" s="31" t="n">
         <f aca="false">('Balance Sheet'!T15+'Balance Sheet'!T16)</f>
-        <v>45199.3901263997</v>
+        <v>45199.3632715408</v>
       </c>
       <c r="U24" s="31" t="n">
         <f aca="false">('Balance Sheet'!U15+'Balance Sheet'!U16)</f>
-        <v>50538.4573068796</v>
+        <v>50538.4280801126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16387,39 +16387,39 @@
       </c>
       <c r="B25" s="69" t="n">
         <f aca="false">IFERROR((B24)/(B23),0)</f>
-        <v>3.26175415714765E-005</v>
+        <v>326.175415714765</v>
       </c>
       <c r="C25" s="69" t="n">
         <f aca="false">IFERROR((C24)/(C23),0)</f>
-        <v>4.30418382474057E-005</v>
+        <v>430.418382474057</v>
       </c>
       <c r="D25" s="69" t="n">
         <f aca="false">IFERROR((D24)/(D23),0)</f>
-        <v>4.75649810574864E-005</v>
+        <v>475.649810574864</v>
       </c>
       <c r="E25" s="69" t="n">
         <f aca="false">IFERROR((E24)/(E23),0)</f>
-        <v>4.25205075322214E-005</v>
+        <v>425.205075322214</v>
       </c>
       <c r="F25" s="69" t="n">
         <f aca="false">IFERROR((F24)/(F23),0)</f>
-        <v>4.82430935170167E-005</v>
+        <v>482.430935170167</v>
       </c>
       <c r="G25" s="69" t="n">
         <f aca="false">IFERROR((G24)/(G23),0)</f>
-        <v>5.38975528114054E-005</v>
+        <v>538.975528114054</v>
       </c>
       <c r="H25" s="69" t="n">
         <f aca="false">IFERROR((H24)/(H23),0)</f>
-        <v>2.14222343563866E-006</v>
+        <v>21.4222343563866</v>
       </c>
       <c r="I25" s="69" t="n">
         <f aca="false">IFERROR((I24)/(I23),0)</f>
-        <v>3.82207333848147E-006</v>
+        <v>38.2207333848147</v>
       </c>
       <c r="J25" s="69" t="n">
         <f aca="false">IFERROR((J24)/(J23),0)</f>
-        <v>4.61756798298618E-006</v>
+        <v>46.1756798298618</v>
       </c>
       <c r="K25" s="69" t="n">
         <f aca="false">IFERROR((K24)/(K23),0)</f>
@@ -16427,43 +16427,43 @@
       </c>
       <c r="L25" s="68" t="n">
         <f aca="false">IFERROR((L24)/(L23),0)</f>
-        <v>80.8083232876736</v>
+        <v>80.808314874259</v>
       </c>
       <c r="M25" s="68" t="n">
         <f aca="false">IFERROR((M24)/(M23),0)</f>
-        <v>89.6990043152174</v>
+        <v>89.6989829242001</v>
       </c>
       <c r="N25" s="68" t="n">
         <f aca="false">IFERROR((N24)/(N23),0)</f>
-        <v>98.9079167440355</v>
+        <v>98.907878065431</v>
       </c>
       <c r="O25" s="68" t="n">
         <f aca="false">IFERROR((O24)/(O23),0)</f>
-        <v>110.106987931372</v>
+        <v>110.106932649885</v>
       </c>
       <c r="P25" s="68" t="n">
         <f aca="false">IFERROR((P24)/(P23),0)</f>
-        <v>123.109146886091</v>
+        <v>123.109076984809</v>
       </c>
       <c r="Q25" s="68" t="n">
         <f aca="false">IFERROR((Q24)/(Q23),0)</f>
-        <v>138.052427464943</v>
+        <v>138.052344608986</v>
       </c>
       <c r="R25" s="68" t="n">
         <f aca="false">IFERROR((R24)/(R23),0)</f>
-        <v>154.877817532712</v>
+        <v>154.877722942109</v>
       </c>
       <c r="S25" s="68" t="n">
         <f aca="false">IFERROR((S24)/(S23),0)</f>
-        <v>173.673181550451</v>
+        <v>173.673076199865</v>
       </c>
       <c r="T25" s="68" t="n">
         <f aca="false">IFERROR((T24)/(T23),0)</f>
-        <v>194.531483221002</v>
+        <v>194.531367641665</v>
       </c>
       <c r="U25" s="68" t="n">
         <f aca="false">IFERROR((U24)/(U23),0)</f>
-        <v>217.510037903506</v>
+        <v>217.509912115828</v>
       </c>
     </row>
   </sheetData>
